--- a/research/traditional_assets/database/data/spain/spain_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_publishing_newspapers.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,118 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.05860000000000001</v>
+        <v>-0.0214</v>
       </c>
       <c r="G2">
-        <v>0.1708917387414256</v>
+        <v>0.140406748159268</v>
       </c>
       <c r="H2">
-        <v>0.1708917387414256</v>
+        <v>0.1403245407105583</v>
       </c>
       <c r="I2">
-        <v>0.09841932597673725</v>
+        <v>0.06948316534419902</v>
       </c>
       <c r="J2">
-        <v>0.04920966298836862</v>
+        <v>0.05211237400814926</v>
       </c>
       <c r="K2">
-        <v>-36.9</v>
+        <v>-45.05</v>
       </c>
       <c r="L2">
-        <v>-0.0366835669549657</v>
+        <v>-0.03220387447280006</v>
       </c>
       <c r="M2">
-        <v>2.39</v>
+        <v>8.732000000000001</v>
       </c>
       <c r="N2">
-        <v>0.007079383886255924</v>
+        <v>0.02109688330514617</v>
       </c>
       <c r="O2">
-        <v>-0.06476964769647697</v>
+        <v>-0.1938290788013319</v>
       </c>
       <c r="P2">
-        <v>2.39</v>
+        <v>8.18</v>
       </c>
       <c r="Q2">
-        <v>0.007079383886255924</v>
+        <v>0.01976322783280985</v>
       </c>
       <c r="R2">
-        <v>-0.06476964769647697</v>
+        <v>-0.1815760266370699</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.5520000000000005</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.06321575813101242</v>
       </c>
       <c r="U2">
-        <v>140.4</v>
+        <v>160.6</v>
       </c>
       <c r="V2">
-        <v>0.4158767772511848</v>
+        <v>0.3880164290891519</v>
       </c>
       <c r="W2">
-        <v>0.07877882152006832</v>
+        <v>0.02374040922393585</v>
       </c>
       <c r="X2">
-        <v>0.2486721136380646</v>
+        <v>0.2052425102279534</v>
       </c>
       <c r="Y2">
-        <v>-0.1698932921179963</v>
+        <v>-0.1815021010040175</v>
       </c>
       <c r="Z2">
-        <v>3.312150148172539</v>
+        <v>2.251206952043773</v>
       </c>
       <c r="AA2">
-        <v>0.1629897925584459</v>
+        <v>0.07866203508942124</v>
       </c>
       <c r="AB2">
-        <v>0.1223827163513814</v>
+        <v>0.1135729208166852</v>
       </c>
       <c r="AC2">
-        <v>0.0406070762070645</v>
+        <v>-0.03491088572726393</v>
       </c>
       <c r="AD2">
-        <v>991.3</v>
+        <v>1076</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>991.3</v>
+        <v>1076</v>
       </c>
       <c r="AG2">
-        <v>850.9</v>
+        <v>915.4</v>
       </c>
       <c r="AH2">
-        <v>0.7459553013770787</v>
+        <v>0.7221961205450029</v>
       </c>
       <c r="AI2">
-        <v>1.797461468721668</v>
+        <v>1.200624860522205</v>
       </c>
       <c r="AJ2">
-        <v>0.7159444678165755</v>
+        <v>0.6886331151733995</v>
       </c>
       <c r="AK2">
-        <v>2.069812697640477</v>
+        <v>1.244426318651441</v>
       </c>
       <c r="AL2">
-        <v>95.7</v>
+        <v>98.7</v>
       </c>
       <c r="AM2">
-        <v>91.54000000000001</v>
+        <v>92.77000000000001</v>
       </c>
       <c r="AN2">
-        <v>6.693450371370695</v>
+        <v>6.737633061991234</v>
       </c>
       <c r="AO2">
-        <v>1.03448275862069</v>
+        <v>0.9848024316109423</v>
       </c>
       <c r="AP2">
-        <v>5.74544226873734</v>
+        <v>5.731997495303695</v>
       </c>
       <c r="AQ2">
-        <v>1.081494428665064</v>
+        <v>1.047752506198124</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +775,10 @@
         <v>0.07877882152006832</v>
       </c>
       <c r="X3">
-        <v>0.2486721136380646</v>
+        <v>0.2486172242810162</v>
       </c>
       <c r="Y3">
-        <v>-0.1698932921179963</v>
+        <v>-0.1698384027609479</v>
       </c>
       <c r="Z3">
         <v>3.312150148172539</v>
@@ -787,10 +787,10 @@
         <v>0.1629897925584459</v>
       </c>
       <c r="AB3">
-        <v>0.1223827163513814</v>
+        <v>0.1223687720012124</v>
       </c>
       <c r="AC3">
-        <v>0.0406070762070645</v>
+        <v>0.04062102055723343</v>
       </c>
       <c r="AD3">
         <v>991.3</v>
@@ -833,6 +833,137 @@
       </c>
       <c r="AQ3">
         <v>1.081494428665064</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Vocento, S.A. (BME:VOC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Publishing &amp; Newspapers</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0158</v>
+      </c>
+      <c r="G4">
+        <v>0.06237913486005088</v>
+      </c>
+      <c r="H4">
+        <v>0.06208651399491094</v>
+      </c>
+      <c r="I4">
+        <v>-0.004580152671755725</v>
+      </c>
+      <c r="J4">
+        <v>-0.004580152671755725</v>
+      </c>
+      <c r="K4">
+        <v>-8.15</v>
+      </c>
+      <c r="L4">
+        <v>-0.02073791348600509</v>
+      </c>
+      <c r="M4">
+        <v>6.342000000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.08311926605504588</v>
+      </c>
+      <c r="O4">
+        <v>-0.778159509202454</v>
+      </c>
+      <c r="P4">
+        <v>5.79</v>
+      </c>
+      <c r="Q4">
+        <v>0.07588466579292268</v>
+      </c>
+      <c r="R4">
+        <v>-0.7104294478527607</v>
+      </c>
+      <c r="S4">
+        <v>0.5520000000000005</v>
+      </c>
+      <c r="T4">
+        <v>0.08703878902554406</v>
+      </c>
+      <c r="U4">
+        <v>20.2</v>
+      </c>
+      <c r="V4">
+        <v>0.2647444298820446</v>
+      </c>
+      <c r="W4">
+        <v>-0.03129800307219662</v>
+      </c>
+      <c r="X4">
+        <v>0.1618677961748905</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1931657992470871</v>
+      </c>
+      <c r="Z4">
+        <v>1.237016052880076</v>
+      </c>
+      <c r="AA4">
+        <v>-0.0056657223796034</v>
+      </c>
+      <c r="AB4">
+        <v>0.1047770696321579</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1104427920117613</v>
+      </c>
+      <c r="AD4">
+        <v>84.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>84.7</v>
+      </c>
+      <c r="AG4">
+        <v>64.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.5260869565217392</v>
+      </c>
+      <c r="AI4">
+        <v>0.2457209167391935</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4580965909090909</v>
+      </c>
+      <c r="AK4">
+        <v>0.1987673343605547</v>
+      </c>
+      <c r="AL4">
+        <v>3</v>
+      </c>
+      <c r="AM4">
+        <v>1.23</v>
+      </c>
+      <c r="AN4">
+        <v>7.301724137931035</v>
+      </c>
+      <c r="AO4">
+        <v>-0.6</v>
+      </c>
+      <c r="AP4">
+        <v>5.560344827586207</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.463414634146341</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1258,49 @@
         <v>0.749216300940439</v>
       </c>
       <c r="F2">
-        <v>4.57750309619185</v>
+        <v>4.50758024321435</v>
       </c>
       <c r="G2">
         <v>6.6934503713707</v>
       </c>
       <c r="H2">
-        <v>3.40973666441594</v>
+        <v>3.58919648885888</v>
       </c>
       <c r="I2">
         <v>0.745955301377079</v>
       </c>
       <c r="J2">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="K2">
         <v>337.6</v>
       </c>
       <c r="L2">
-        <v>1038.22762157896</v>
+        <v>1026.49988820623</v>
       </c>
       <c r="M2">
         <v>1188.5</v>
       </c>
       <c r="N2">
-        <v>1402.80962157896</v>
+        <v>1417.65988820623</v>
       </c>
       <c r="O2">
         <v>991.3</v>
       </c>
       <c r="P2">
-        <v>504.982</v>
+        <v>531.5599999999999</v>
       </c>
       <c r="Q2">
-        <v>0.122382716351381</v>
+        <v>0.122368772001212</v>
       </c>
       <c r="R2">
-        <v>0.106744028971655</v>
+        <v>0.105821800487758</v>
       </c>
       <c r="S2">
         <v>0.0793732333250682</v>
       </c>
       <c r="T2">
-        <v>0.0552982333250682</v>
+        <v>0.0533482333250682</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1313,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.248672113638065</v>
+        <v>0.248617224281016</v>
       </c>
       <c r="X2">
-        <v>0.138275323077627</v>
+        <v>0.140804178596218</v>
       </c>
       <c r="Y2">
         <v>3.13751795602054</v>
       </c>
       <c r="Z2">
-        <v>1.43017678202184</v>
+        <v>1.46968442793405</v>
       </c>
       <c r="AA2">
         <v>991.3</v>
@@ -1224,7 +1355,7 @@
         <v>337.6</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1409,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1091532600089824</v>
+        <v>0.1091361190641455</v>
       </c>
       <c r="C2">
-        <v>1505.293882843854</v>
+        <v>1505.345349482586</v>
       </c>
       <c r="D2">
-        <v>1364.893882843854</v>
+        <v>1364.945349482586</v>
       </c>
       <c r="E2">
         <v>-991.3</v>
@@ -1460,19 +1591,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1091532600089824</v>
+        <v>0.1091361190641455</v>
       </c>
       <c r="T2">
         <v>0.9797896186226994</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1491,13 +1622,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1090433591922106</v>
+        <v>0.1090157610997358</v>
       </c>
       <c r="C3">
-        <v>1493.68979760522</v>
+        <v>1493.901964184944</v>
       </c>
       <c r="D3">
-        <v>1366.57879760522</v>
+        <v>1366.790964184944</v>
       </c>
       <c r="E3">
         <v>-978.011</v>
@@ -1524,37 +1655,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M3">
-        <v>0.8974191635424416</v>
+        <v>0.8788145635424416</v>
       </c>
       <c r="N3">
-        <v>169.5359141697909</v>
+        <v>169.5545187697909</v>
       </c>
       <c r="O3">
-        <v>42.38397854244772</v>
+        <v>42.38862969244772</v>
       </c>
       <c r="P3">
-        <v>127.1519356273432</v>
+        <v>127.1658890773432</v>
       </c>
       <c r="Q3">
-        <v>203.5519356273432</v>
+        <v>203.5658890773432</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1096332089484444</v>
+        <v>0.1096159381479648</v>
       </c>
       <c r="T3">
         <v>0.987212267248629</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1562,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>189.9149697902267</v>
+        <v>193.9354903795952</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,13 +1704,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1089334583754388</v>
+        <v>0.1088954031353261</v>
       </c>
       <c r="C4">
-        <v>1482.089877447391</v>
+        <v>1482.463576751423</v>
       </c>
       <c r="D4">
-        <v>1368.26787744739</v>
+        <v>1368.641576751423</v>
       </c>
       <c r="E4">
         <v>-964.722</v>
@@ -1606,37 +1737,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M4">
-        <v>1.794838327084883</v>
+        <v>1.757629127084883</v>
       </c>
       <c r="N4">
-        <v>168.6384950062485</v>
+        <v>168.6757042062484</v>
       </c>
       <c r="O4">
-        <v>42.15962375156212</v>
+        <v>42.16892605156211</v>
       </c>
       <c r="P4">
-        <v>126.4788712546863</v>
+        <v>126.5067781546863</v>
       </c>
       <c r="Q4">
-        <v>202.8788712546863</v>
+        <v>202.9067781546863</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1101229527642219</v>
+        <v>0.1101055494579845</v>
       </c>
       <c r="T4">
         <v>0.9947863984995775</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1644,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>94.95748489511337</v>
+        <v>96.9677451897976</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,13 +1786,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.108823557558667</v>
+        <v>0.1087750451709165</v>
       </c>
       <c r="C5">
-        <v>1470.494137833492</v>
+        <v>1471.030207510627</v>
       </c>
       <c r="D5">
-        <v>1369.961137833492</v>
+        <v>1370.497207510627</v>
       </c>
       <c r="E5">
         <v>-951.433</v>
@@ -1688,37 +1819,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M5">
-        <v>2.692257490627325</v>
+        <v>2.636443690627325</v>
       </c>
       <c r="N5">
-        <v>167.741075842706</v>
+        <v>167.796889642706</v>
       </c>
       <c r="O5">
-        <v>41.9352689606765</v>
+        <v>41.94922241067651</v>
       </c>
       <c r="P5">
-        <v>125.8058068820295</v>
+        <v>125.8476672320295</v>
       </c>
       <c r="Q5">
-        <v>202.2058068820295</v>
+        <v>202.2476672320295</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.110622794390634</v>
+        <v>0.1106052558465613</v>
       </c>
       <c r="T5">
         <v>1.002516697405185</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1726,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.30498993007558</v>
+        <v>64.64516345986507</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,13 +1868,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1087136567418953</v>
+        <v>0.1086546872065068</v>
       </c>
       <c r="C6">
-        <v>1458.90259430329</v>
+        <v>1459.601876901557</v>
       </c>
       <c r="D6">
-        <v>1371.65859430329</v>
+        <v>1372.357876901557</v>
       </c>
       <c r="E6">
         <v>-938.144</v>
@@ -1770,37 +1901,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M6">
-        <v>3.589676654169766</v>
+        <v>3.515258254169766</v>
       </c>
       <c r="N6">
-        <v>166.8436566791636</v>
+        <v>166.9180750791636</v>
       </c>
       <c r="O6">
-        <v>41.71091416979089</v>
+        <v>41.72951876979089</v>
       </c>
       <c r="P6">
-        <v>125.1327425093727</v>
+        <v>125.1885563093727</v>
       </c>
       <c r="Q6">
-        <v>201.5327425093727</v>
+        <v>201.5885563093727</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1111330493842631</v>
+        <v>0.1111153727849001</v>
       </c>
       <c r="T6">
         <v>1.010408044204659</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1808,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.47874244755668</v>
+        <v>48.4838725948988</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,13 +1950,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1086037559251235</v>
+        <v>0.1085343292420971</v>
       </c>
       <c r="C7">
-        <v>1447.315262473663</v>
+        <v>1448.17860547436</v>
       </c>
       <c r="D7">
-        <v>1373.360262473663</v>
+        <v>1374.223605474359</v>
       </c>
       <c r="E7">
         <v>-924.8549999999999</v>
@@ -1852,37 +1983,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M7">
-        <v>4.487095817712208</v>
+        <v>4.394072817712208</v>
       </c>
       <c r="N7">
-        <v>165.9462375156211</v>
+        <v>166.0392605156211</v>
       </c>
       <c r="O7">
-        <v>41.48655937890528</v>
+        <v>41.50981512890528</v>
       </c>
       <c r="P7">
-        <v>124.4596781367159</v>
+        <v>124.5294453867158</v>
       </c>
       <c r="Q7">
-        <v>200.8596781367158</v>
+        <v>200.9294453867159</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1116540465882843</v>
+        <v>0.1116362290272039</v>
       </c>
       <c r="T7">
         <v>1.018465524620964</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1890,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.98299395804535</v>
+        <v>38.78709807591904</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,13 +2032,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1084938551083517</v>
+        <v>0.1084139712776874</v>
       </c>
       <c r="C8">
-        <v>1435.732158039083</v>
+        <v>1436.760413891088</v>
       </c>
       <c r="D8">
-        <v>1375.066158039083</v>
+        <v>1376.094413891088</v>
       </c>
       <c r="E8">
         <v>-911.5659999999999</v>
@@ -1934,37 +2065,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M8">
-        <v>5.384514981254649</v>
+        <v>5.27288738125465</v>
       </c>
       <c r="N8">
-        <v>165.0488183520787</v>
+        <v>165.1604459520787</v>
       </c>
       <c r="O8">
-        <v>41.26220458801967</v>
+        <v>41.29011148801967</v>
       </c>
       <c r="P8">
-        <v>123.786613764059</v>
+        <v>123.870334464059</v>
       </c>
       <c r="Q8">
-        <v>200.186613764059</v>
+        <v>200.270334464059</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1121861288391996</v>
+        <v>0.1121681673172163</v>
       </c>
       <c r="T8">
         <v>1.026694440790807</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1972,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.65249496503779</v>
+        <v>32.32258172993253</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,13 +2114,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1083839542915799</v>
+        <v>0.1082936133132777</v>
       </c>
       <c r="C9">
-        <v>1424.153296772098</v>
+        <v>1425.347322926461</v>
       </c>
       <c r="D9">
-        <v>1376.776296772098</v>
+        <v>1377.970322926461</v>
       </c>
       <c r="E9">
         <v>-898.2769999999999</v>
@@ -2016,37 +2147,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M9">
-        <v>6.281934144797091</v>
+        <v>6.151701944797091</v>
       </c>
       <c r="N9">
-        <v>164.1513991885362</v>
+        <v>164.2816313885363</v>
       </c>
       <c r="O9">
-        <v>41.03784979713406</v>
+        <v>41.07040784713406</v>
       </c>
       <c r="P9">
-        <v>123.1135493914022</v>
+        <v>123.2112235414022</v>
       </c>
       <c r="Q9">
-        <v>199.5135493914022</v>
+        <v>199.6112235414022</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1127296537191669</v>
+        <v>0.1127115451403473</v>
       </c>
       <c r="T9">
         <v>1.035100322899787</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2054,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.13070997003239</v>
+        <v>27.70507005422789</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,13 +2196,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1082740534748082</v>
+        <v>0.108173255348868</v>
       </c>
       <c r="C10">
-        <v>1412.578694523815</v>
+        <v>1413.939353468635</v>
       </c>
       <c r="D10">
-        <v>1378.490694523815</v>
+        <v>1379.851353468635</v>
       </c>
       <c r="E10">
         <v>-884.9879999999999</v>
@@ -2098,37 +2229,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M10">
-        <v>7.179353308339532</v>
+        <v>7.030516508339533</v>
       </c>
       <c r="N10">
-        <v>163.2539800249938</v>
+        <v>163.4028168249938</v>
       </c>
       <c r="O10">
-        <v>40.81349500624845</v>
+        <v>40.85070420624845</v>
       </c>
       <c r="P10">
-        <v>122.4404850187454</v>
+        <v>122.5521126187454</v>
       </c>
       <c r="Q10">
-        <v>198.8404850187454</v>
+        <v>198.9521126187454</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1132849943573943</v>
+        <v>0.1132667355248506</v>
       </c>
       <c r="T10">
         <v>1.043688941576354</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2136,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.73937122377834</v>
+        <v>24.2419362974494</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,13 +2278,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1081641526580364</v>
+        <v>0.1080528973844583</v>
       </c>
       <c r="C11">
-        <v>1401.008367224396</v>
+        <v>1402.536526519976</v>
       </c>
       <c r="D11">
-        <v>1380.209367224396</v>
+        <v>1381.737526519976</v>
       </c>
       <c r="E11">
         <v>-871.699</v>
@@ -2180,37 +2311,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M11">
-        <v>8.076772471881974</v>
+        <v>7.909331071881973</v>
       </c>
       <c r="N11">
-        <v>162.3565608614514</v>
+        <v>162.5240022614514</v>
       </c>
       <c r="O11">
-        <v>40.58914021536284</v>
+        <v>40.63100056536284</v>
       </c>
       <c r="P11">
-        <v>121.7674206460885</v>
+        <v>121.8930016960885</v>
       </c>
       <c r="Q11">
-        <v>198.1674206460885</v>
+        <v>198.2930016960885</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1138525402843739</v>
+        <v>0.1138341278958266</v>
       </c>
       <c r="T11">
         <v>1.052466321102955</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2218,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.1016633100252</v>
+        <v>21.54838781995502</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,13 +2360,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1080542518412646</v>
+        <v>0.1079325394200487</v>
       </c>
       <c r="C12">
-        <v>1389.442330883545</v>
+        <v>1391.138863197844</v>
       </c>
       <c r="D12">
-        <v>1381.932330883545</v>
+        <v>1383.628863197844</v>
       </c>
       <c r="E12">
         <v>-858.41</v>
@@ -2262,37 +2393,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M12">
-        <v>8.974191635424416</v>
+        <v>8.788145635424415</v>
       </c>
       <c r="N12">
-        <v>161.4591416979089</v>
+        <v>161.6451876979089</v>
       </c>
       <c r="O12">
-        <v>40.36478542447723</v>
+        <v>40.41129692447723</v>
       </c>
       <c r="P12">
-        <v>121.0943562734317</v>
+        <v>121.2338907734317</v>
       </c>
       <c r="Q12">
-        <v>197.4943562734317</v>
+        <v>197.6338907734317</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1144326983430642</v>
+        <v>0.1144141289861576</v>
       </c>
       <c r="T12">
         <v>1.061438753507924</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2300,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.99149697902267</v>
+        <v>19.39354903795952</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,13 +2442,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1079443510244929</v>
+        <v>0.107812181455639</v>
       </c>
       <c r="C13">
-        <v>1377.880601591009</v>
+        <v>1379.746384735381</v>
       </c>
       <c r="D13">
-        <v>1383.659601591009</v>
+        <v>1385.525384735381</v>
       </c>
       <c r="E13">
         <v>-845.121</v>
@@ -2344,37 +2475,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M13">
-        <v>9.871610798966856</v>
+        <v>9.666960198966857</v>
       </c>
       <c r="N13">
-        <v>160.5617225343665</v>
+        <v>160.7663731343665</v>
       </c>
       <c r="O13">
-        <v>40.14043063359162</v>
+        <v>40.19159328359162</v>
       </c>
       <c r="P13">
-        <v>120.4212919007749</v>
+        <v>120.5747798507749</v>
       </c>
       <c r="Q13">
-        <v>196.8212919007749</v>
+        <v>196.9747798507749</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1150258936615004</v>
+        <v>0.1150071638088556</v>
       </c>
       <c r="T13">
         <v>1.070612813607388</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2382,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.26499725365698</v>
+        <v>17.63049912541775</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,13 +2524,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1078344502077211</v>
+        <v>0.1076918234912293</v>
       </c>
       <c r="C14">
-        <v>1366.323195517077</v>
+        <v>1368.359112482302</v>
       </c>
       <c r="D14">
-        <v>1385.391195517077</v>
+        <v>1387.427112482302</v>
       </c>
       <c r="E14">
         <v>-831.8319999999999</v>
@@ -2426,37 +2557,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M14">
-        <v>10.7690299625093</v>
+        <v>10.5457747625093</v>
       </c>
       <c r="N14">
-        <v>159.664303370824</v>
+        <v>159.887558570824</v>
       </c>
       <c r="O14">
-        <v>39.91607584270601</v>
+        <v>39.97188964270601</v>
       </c>
       <c r="P14">
-        <v>119.748227528118</v>
+        <v>119.915668928118</v>
       </c>
       <c r="Q14">
-        <v>196.148227528118</v>
+        <v>196.315668928118</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1156325706917192</v>
+        <v>0.1156136766957058</v>
       </c>
       <c r="T14">
         <v>1.079995375072748</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2464,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.82624748251889</v>
+        <v>16.16129086496627</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,13 +2606,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1077245493909493</v>
+        <v>0.1075714655268196</v>
       </c>
       <c r="C15">
-        <v>1354.770128913086</v>
+        <v>1356.977067905702</v>
       </c>
       <c r="D15">
-        <v>1387.127128913086</v>
+        <v>1389.334067905702</v>
       </c>
       <c r="E15">
         <v>-818.5429999999999</v>
@@ -2508,37 +2639,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M15">
-        <v>11.66644912605174</v>
+        <v>11.42458932605174</v>
       </c>
       <c r="N15">
-        <v>158.7668842072816</v>
+        <v>159.0087440072816</v>
       </c>
       <c r="O15">
-        <v>39.6917210518204</v>
+        <v>39.7521860018204</v>
       </c>
       <c r="P15">
-        <v>119.0751631554612</v>
+        <v>119.2565580054612</v>
       </c>
       <c r="Q15">
-        <v>195.4751631554612</v>
+        <v>195.6565580054612</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1162531943203338</v>
+        <v>0.1162341324075411</v>
       </c>
       <c r="T15">
         <v>1.089593627606278</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2546,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.60884383001744</v>
+        <v>14.91811464458425</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,13 +2688,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1076146485741775</v>
+        <v>0.10745110756241</v>
       </c>
       <c r="C16">
-        <v>1343.221418111928</v>
+        <v>1345.600272590859</v>
       </c>
       <c r="D16">
-        <v>1388.867418111928</v>
+        <v>1391.246272590859</v>
       </c>
       <c r="E16">
         <v>-805.2539999999999</v>
@@ -2590,37 +2721,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M16">
-        <v>12.56386828959418</v>
+        <v>12.30340388959418</v>
       </c>
       <c r="N16">
-        <v>157.8694650437392</v>
+        <v>158.1299294437391</v>
       </c>
       <c r="O16">
-        <v>39.46736626093479</v>
+        <v>39.53248236093479</v>
       </c>
       <c r="P16">
-        <v>118.4020987828044</v>
+        <v>118.5974470828044</v>
       </c>
       <c r="Q16">
-        <v>194.8020987828044</v>
+        <v>194.9974470828044</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1168882510565907</v>
+        <v>0.1168690173219772</v>
       </c>
       <c r="T16">
         <v>1.099415095315006</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2628,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.56535498501619</v>
+        <v>13.85253502711394</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,13 +2770,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1076284977574058</v>
+        <v>0.1073307495980003</v>
       </c>
       <c r="C17">
-        <v>1329.712874636959</v>
+        <v>1334.22874824205</v>
       </c>
       <c r="D17">
-        <v>1388.647874636958</v>
+        <v>1393.16374824205</v>
       </c>
       <c r="E17">
         <v>-791.9649999999999</v>
@@ -2672,45 +2803,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M17">
-        <v>13.68055595313662</v>
+        <v>13.18221845313662</v>
       </c>
       <c r="N17">
-        <v>156.7527773801967</v>
+        <v>157.2511148801967</v>
       </c>
       <c r="O17">
-        <v>39.18819434504918</v>
+        <v>39.31277872004918</v>
       </c>
       <c r="P17">
-        <v>117.5645830351475</v>
+        <v>117.9383361601475</v>
       </c>
       <c r="Q17">
-        <v>193.9645830351475</v>
+        <v>194.3383361601475</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1175382503042889</v>
+        <v>0.1175188407049883</v>
       </c>
       <c r="T17">
         <v>1.109467656381586</v>
       </c>
       <c r="U17">
-        <v>0.06863097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.05147323332506819</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>12.45807070393634</v>
+        <v>12.92903269197302</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,13 +2852,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.107526846940634</v>
+        <v>0.1073903916335906</v>
       </c>
       <c r="C18">
-        <v>1318.036905831178</v>
+        <v>1319.988904565624</v>
       </c>
       <c r="D18">
-        <v>1390.260905831178</v>
+        <v>1392.212904565624</v>
       </c>
       <c r="E18">
         <v>-778.6759999999999</v>
@@ -2754,37 +2885,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M18">
-        <v>14.59259301667907</v>
+        <v>14.37996901667907</v>
       </c>
       <c r="N18">
-        <v>155.8407403166543</v>
+        <v>156.0533643166543</v>
       </c>
       <c r="O18">
-        <v>38.96018507916357</v>
+        <v>39.01334107916357</v>
       </c>
       <c r="P18">
-        <v>116.8805552374907</v>
+        <v>117.0400232374907</v>
       </c>
       <c r="Q18">
-        <v>193.2805552374907</v>
+        <v>193.4400232374907</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1182037257245513</v>
+        <v>0.1181841360733091</v>
       </c>
       <c r="T18">
         <v>1.119759564140228</v>
       </c>
       <c r="U18">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2792,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.67944128494032</v>
+        <v>11.85213494797178</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,13 +2934,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1074251961238622</v>
+        <v>0.1072812836691809</v>
       </c>
       <c r="C19">
-        <v>1306.364688725861</v>
+        <v>1308.440345109423</v>
       </c>
       <c r="D19">
-        <v>1391.877688725861</v>
+        <v>1393.953345109423</v>
       </c>
       <c r="E19">
         <v>-765.3869999999999</v>
@@ -2836,37 +2967,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M19">
-        <v>15.50463008022151</v>
+        <v>15.27871708022151</v>
       </c>
       <c r="N19">
-        <v>154.9287032531118</v>
+        <v>155.1546162531118</v>
       </c>
       <c r="O19">
-        <v>38.73217581327796</v>
+        <v>38.78865406327796</v>
       </c>
       <c r="P19">
-        <v>116.1965274398339</v>
+        <v>116.3659621898339</v>
       </c>
       <c r="Q19">
-        <v>192.5965274398339</v>
+        <v>192.7659621898339</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1188852366971092</v>
+        <v>0.1188654626553245</v>
       </c>
       <c r="T19">
         <v>1.130299469676187</v>
       </c>
       <c r="U19">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2874,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.99241532700266</v>
+        <v>11.15495053926756</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,13 +3016,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1073235453070904</v>
+        <v>0.1071721757047712</v>
       </c>
       <c r="C20">
-        <v>1294.696236425199</v>
+        <v>1296.896142637434</v>
       </c>
       <c r="D20">
-        <v>1393.498236425199</v>
+        <v>1395.698142637434</v>
       </c>
       <c r="E20">
         <v>-752.098</v>
@@ -2918,37 +3049,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M20">
-        <v>16.41666714376395</v>
+        <v>16.17746514376395</v>
       </c>
       <c r="N20">
-        <v>154.0166661895694</v>
+        <v>154.2558681895694</v>
       </c>
       <c r="O20">
-        <v>38.50416654739234</v>
+        <v>38.56396704739235</v>
       </c>
       <c r="P20">
-        <v>115.512499642177</v>
+        <v>115.691901142177</v>
       </c>
       <c r="Q20">
-        <v>191.912499642177</v>
+        <v>192.0919011421771</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.11958336988851</v>
+        <v>0.1195634069588524</v>
       </c>
       <c r="T20">
         <v>1.141096446078876</v>
       </c>
       <c r="U20">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2956,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.38172558661362</v>
+        <v>10.5352310648638</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,13 +3098,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1072218944903187</v>
+        <v>0.1070630677403615</v>
       </c>
       <c r="C21">
-        <v>1283.03156209448</v>
+        <v>1285.356313530943</v>
       </c>
       <c r="D21">
-        <v>1395.12256209448</v>
+        <v>1397.447313530943</v>
       </c>
       <c r="E21">
         <v>-738.809</v>
@@ -3000,37 +3131,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M21">
-        <v>17.32870420730639</v>
+        <v>17.07621320730639</v>
       </c>
       <c r="N21">
-        <v>153.1046291260269</v>
+        <v>153.357120126027</v>
       </c>
       <c r="O21">
-        <v>38.27615728150673</v>
+        <v>38.33928003150674</v>
       </c>
       <c r="P21">
-        <v>114.8284718445202</v>
+        <v>115.0178400945202</v>
       </c>
       <c r="Q21">
-        <v>191.2284718445202</v>
+        <v>191.4178400945202</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1202987409364885</v>
+        <v>0.12027858445506</v>
       </c>
       <c r="T21">
         <v>1.152160014491508</v>
       </c>
       <c r="U21">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3038,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.83531897679185</v>
+        <v>9.980745219344659</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,13 +3180,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1074502436735469</v>
+        <v>0.1072089597759519</v>
       </c>
       <c r="C22">
-        <v>1266.098951841788</v>
+        <v>1269.729423149773</v>
       </c>
       <c r="D22">
-        <v>1391.478951841788</v>
+        <v>1395.109423149773</v>
       </c>
       <c r="E22">
         <v>-725.52</v>
@@ -3082,37 +3213,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M22">
-        <v>18.82545727084883</v>
+        <v>18.42678727084883</v>
       </c>
       <c r="N22">
-        <v>151.6078760624845</v>
+        <v>152.0065460624845</v>
       </c>
       <c r="O22">
-        <v>37.90196901562113</v>
+        <v>38.00163651562113</v>
       </c>
       <c r="P22">
-        <v>113.7059070468634</v>
+        <v>114.0049095468634</v>
       </c>
       <c r="Q22">
-        <v>190.1059070468634</v>
+        <v>190.4049095468634</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1210319962606665</v>
+        <v>0.1210116413886728</v>
       </c>
       <c r="T22">
         <v>1.163500172114456</v>
       </c>
       <c r="U22">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3120,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.053343612388577</v>
+        <v>9.249215874053032</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,13 +3262,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1073650928567751</v>
+        <v>0.1071126018115422</v>
       </c>
       <c r="C23">
-        <v>1254.166417210075</v>
+        <v>1257.983661998125</v>
       </c>
       <c r="D23">
-        <v>1392.835417210075</v>
+        <v>1396.652661998125</v>
       </c>
       <c r="E23">
         <v>-712.231</v>
@@ -3164,37 +3295,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M23">
-        <v>19.76673013439127</v>
+        <v>19.34812663439127</v>
       </c>
       <c r="N23">
-        <v>150.6666031989421</v>
+        <v>151.0852066989421</v>
       </c>
       <c r="O23">
-        <v>37.66665079973551</v>
+        <v>37.77130167473552</v>
       </c>
       <c r="P23">
-        <v>112.9999523992065</v>
+        <v>113.3139050242065</v>
       </c>
       <c r="Q23">
-        <v>189.3999523992065</v>
+        <v>189.7139050242066</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1217838150107731</v>
+        <v>0.1217632567256682</v>
       </c>
       <c r="T23">
         <v>1.175127422335453</v>
       </c>
       <c r="U23">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3202,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.622232011798644</v>
+        <v>8.80877702290765</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,13 +3344,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1072799420400033</v>
+        <v>0.1070162438471325</v>
       </c>
       <c r="C24">
-        <v>1242.236529824649</v>
+        <v>1246.241318819976</v>
       </c>
       <c r="D24">
-        <v>1394.194529824649</v>
+        <v>1398.199318819976</v>
       </c>
       <c r="E24">
         <v>-698.942</v>
@@ -3246,37 +3377,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M24">
-        <v>20.70800299793371</v>
+        <v>20.26946599793371</v>
       </c>
       <c r="N24">
-        <v>149.7253303353996</v>
+        <v>150.1638673353996</v>
       </c>
       <c r="O24">
-        <v>37.43133258384991</v>
+        <v>37.54096683384991</v>
       </c>
       <c r="P24">
-        <v>112.2939977515497</v>
+        <v>112.6229005015497</v>
       </c>
       <c r="Q24">
-        <v>188.6939977515497</v>
+        <v>189.0229005015497</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1225549111647286</v>
+        <v>0.1225341442507916</v>
       </c>
       <c r="T24">
         <v>1.187052807177501</v>
       </c>
       <c r="U24">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3284,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.230312374898707</v>
+        <v>8.408378067320939</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,13 +3426,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1071947912232316</v>
+        <v>0.1069198858827228</v>
       </c>
       <c r="C25">
-        <v>1230.309297442536</v>
+        <v>1234.502404983132</v>
       </c>
       <c r="D25">
-        <v>1395.556297442536</v>
+        <v>1399.749404983132</v>
       </c>
       <c r="E25">
         <v>-685.6529999999999</v>
@@ -3328,37 +3459,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M25">
-        <v>21.64927586147616</v>
+        <v>21.19080536147615</v>
       </c>
       <c r="N25">
-        <v>148.7840574718572</v>
+        <v>149.2425279718572</v>
       </c>
       <c r="O25">
-        <v>37.1960143679643</v>
+        <v>37.3106319929643</v>
       </c>
       <c r="P25">
-        <v>111.5880431038929</v>
+        <v>111.9318959788929</v>
       </c>
       <c r="Q25">
-        <v>187.9880431038929</v>
+        <v>188.3318959788929</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1233460357902154</v>
+        <v>0.1233250548285157</v>
       </c>
       <c r="T25">
         <v>1.199287942275187</v>
       </c>
       <c r="U25">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3366,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.872472706424849</v>
+        <v>8.042796412220028</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,13 +3508,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1073796404064598</v>
+        <v>0.1068235279183131</v>
       </c>
       <c r="C26">
-        <v>1214.067485260965</v>
+        <v>1222.766931905867</v>
       </c>
       <c r="D26">
-        <v>1392.603485260965</v>
+        <v>1401.302931905867</v>
       </c>
       <c r="E26">
         <v>-672.3639999999999</v>
@@ -3410,45 +3541,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M26">
-        <v>23.0689527250186</v>
+        <v>22.1121447250186</v>
       </c>
       <c r="N26">
-        <v>147.3643806083147</v>
+        <v>148.3211886083147</v>
       </c>
       <c r="O26">
-        <v>36.84109515207869</v>
+        <v>37.08029715207869</v>
       </c>
       <c r="P26">
-        <v>110.5232854562361</v>
+        <v>111.2408914562361</v>
       </c>
       <c r="Q26">
-        <v>186.9232854562361</v>
+        <v>187.6408914562361</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.124157979484794</v>
+        <v>0.1241367788424957</v>
       </c>
       <c r="T26">
         <v>1.211845054612286</v>
       </c>
       <c r="U26">
-        <v>0.07233097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.05424823332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.387996124700366</v>
+        <v>7.707679895044193</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,13 +3590,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.107305739589688</v>
+        <v>0.1068771699539035</v>
       </c>
       <c r="C27">
-        <v>1201.957488964433</v>
+        <v>1208.612665368707</v>
       </c>
       <c r="D27">
-        <v>1393.782488964433</v>
+        <v>1400.437665368707</v>
       </c>
       <c r="E27">
         <v>-659.0749999999999</v>
@@ -3492,37 +3623,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M27">
-        <v>24.03015908856104</v>
+        <v>23.29926408856104</v>
       </c>
       <c r="N27">
-        <v>146.4031742447723</v>
+        <v>147.1340692447723</v>
       </c>
       <c r="O27">
-        <v>36.60079356119307</v>
+        <v>36.78351731119307</v>
       </c>
       <c r="P27">
-        <v>109.8023806835792</v>
+        <v>110.3505519335792</v>
       </c>
       <c r="Q27">
-        <v>186.2023806835792</v>
+        <v>186.7505519335792</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.124991575011228</v>
+        <v>0.1249701488301819</v>
       </c>
       <c r="T27">
         <v>1.224737023278374</v>
       </c>
       <c r="U27">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3530,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.092476279712351</v>
+        <v>7.31496637342331</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,13 +3672,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1072318387729162</v>
+        <v>0.1067868119894938</v>
       </c>
       <c r="C28">
-        <v>1189.849490691871</v>
+        <v>1196.781790509176</v>
       </c>
       <c r="D28">
-        <v>1394.963490691871</v>
+        <v>1401.895790509176</v>
       </c>
       <c r="E28">
         <v>-645.7859999999999</v>
@@ -3574,37 +3705,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M28">
-        <v>24.99136545210348</v>
+        <v>24.23123465210348</v>
       </c>
       <c r="N28">
-        <v>145.4419678812299</v>
+        <v>146.2020986812299</v>
       </c>
       <c r="O28">
-        <v>36.36049197030746</v>
+        <v>36.55052467030747</v>
       </c>
       <c r="P28">
-        <v>109.0814759109224</v>
+        <v>109.6515740109224</v>
       </c>
       <c r="Q28">
-        <v>185.4814759109224</v>
+        <v>186.0515740109224</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1258477001464845</v>
+        <v>0.1258260423310487</v>
       </c>
       <c r="T28">
         <v>1.237977423530032</v>
       </c>
       <c r="U28">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3612,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.819688730492645</v>
+        <v>7.033621512907031</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,13 +3754,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1071579379561445</v>
+        <v>0.1066964540250841</v>
       </c>
       <c r="C29">
-        <v>1177.743495526576</v>
+        <v>1184.953955192203</v>
       </c>
       <c r="D29">
-        <v>1396.146495526576</v>
+        <v>1403.356955192203</v>
       </c>
       <c r="E29">
         <v>-632.4969999999998</v>
@@ -3656,37 +3787,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M29">
-        <v>25.95257181564592</v>
+        <v>25.16320521564592</v>
       </c>
       <c r="N29">
-        <v>144.4807615176874</v>
+        <v>145.2701281176874</v>
       </c>
       <c r="O29">
-        <v>36.12019037942186</v>
+        <v>36.31753202942186</v>
       </c>
       <c r="P29">
-        <v>108.3605711382656</v>
+        <v>108.9525960882656</v>
       </c>
       <c r="Q29">
-        <v>184.7605711382656</v>
+        <v>185.3525960882656</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1267272807648987</v>
+        <v>0.1267053849689256</v>
       </c>
       <c r="T29">
         <v>1.251580574473517</v>
       </c>
       <c r="U29">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3694,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.567107666400325</v>
+        <v>6.773117012428992</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,13 +3836,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1070840371393727</v>
+        <v>0.1066060960606744</v>
       </c>
       <c r="C30">
-        <v>1165.639508569107</v>
+        <v>1173.129168931848</v>
       </c>
       <c r="D30">
-        <v>1397.331508569107</v>
+        <v>1404.821168931848</v>
       </c>
       <c r="E30">
         <v>-619.2079999999999</v>
@@ -3738,37 +3869,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M30">
-        <v>26.91377817918836</v>
+        <v>26.09517577918837</v>
       </c>
       <c r="N30">
-        <v>143.519555154145</v>
+        <v>144.338157554145</v>
       </c>
       <c r="O30">
-        <v>35.87988878853624</v>
+        <v>36.08453938853624</v>
       </c>
       <c r="P30">
-        <v>107.6396663656087</v>
+        <v>108.2536181656087</v>
       </c>
       <c r="Q30">
-        <v>184.0396663656087</v>
+        <v>184.6536181656087</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1276312941782689</v>
+        <v>0.1276091537911879</v>
       </c>
       <c r="T30">
         <v>1.265561590720987</v>
       </c>
       <c r="U30">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3776,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.332568106886027</v>
+        <v>6.531219976270813</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,13 +3918,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1073146363226009</v>
+        <v>0.1065157380962647</v>
       </c>
       <c r="C31">
-        <v>1148.659445993293</v>
+        <v>1161.307441281914</v>
       </c>
       <c r="D31">
-        <v>1393.640445993293</v>
+        <v>1406.288441281914</v>
       </c>
       <c r="E31">
         <v>-605.919</v>
@@ -3820,45 +3951,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M31">
-        <v>28.4145179427308</v>
+        <v>27.0271463427308</v>
       </c>
       <c r="N31">
-        <v>142.0188153906025</v>
+        <v>143.4061869906025</v>
       </c>
       <c r="O31">
-        <v>35.50470384765063</v>
+        <v>35.85154674765063</v>
       </c>
       <c r="P31">
-        <v>106.5141115429519</v>
+        <v>107.5546402429519</v>
       </c>
       <c r="Q31">
-        <v>182.9141115429519</v>
+        <v>183.9546402429519</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1285607727582129</v>
+        <v>0.1285383808901337</v>
       </c>
       <c r="T31">
         <v>1.279936438412048</v>
       </c>
       <c r="U31">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.05529823332506818</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>5.998107505354838</v>
+        <v>6.306005494330441</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,13 +4000,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1072512355058291</v>
+        <v>0.106425380131855</v>
       </c>
       <c r="C32">
-        <v>1136.383319726834</v>
+        <v>1149.488781836166</v>
       </c>
       <c r="D32">
-        <v>1394.653319726834</v>
+        <v>1407.758781836166</v>
       </c>
       <c r="E32">
         <v>-592.6299999999999</v>
@@ -3902,45 +4033,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M32">
-        <v>29.39432890627324</v>
+        <v>27.95911690627325</v>
       </c>
       <c r="N32">
-        <v>141.0390044270601</v>
+        <v>142.4742164270601</v>
       </c>
       <c r="O32">
-        <v>35.25975110676502</v>
+        <v>35.61855410676502</v>
       </c>
       <c r="P32">
-        <v>105.7792533202951</v>
+        <v>106.8556623202951</v>
       </c>
       <c r="Q32">
-        <v>182.1792533202951</v>
+        <v>183.2556623202951</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1295168078690124</v>
+        <v>0.1294941573347637</v>
       </c>
       <c r="T32">
         <v>1.294721996037139</v>
       </c>
       <c r="U32">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.05529823332506818</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>5.798170588509676</v>
+        <v>6.095805311186093</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,13 +4082,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1071878346890574</v>
+        <v>0.1065675221674454</v>
       </c>
       <c r="C33">
-        <v>1124.108666809346</v>
+        <v>1133.888174056536</v>
       </c>
       <c r="D33">
-        <v>1395.667666809346</v>
+        <v>1405.447174056536</v>
       </c>
       <c r="E33">
         <v>-579.3409999999999</v>
@@ -3984,37 +4115,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M33">
-        <v>30.37413986981569</v>
+        <v>29.30304646981569</v>
       </c>
       <c r="N33">
-        <v>140.0591934635177</v>
+        <v>141.1302868635177</v>
       </c>
       <c r="O33">
-        <v>35.01479836587941</v>
+        <v>35.28257171587941</v>
       </c>
       <c r="P33">
-        <v>105.0443950976382</v>
+        <v>105.8477151476382</v>
       </c>
       <c r="Q33">
-        <v>181.4443950976382</v>
+        <v>182.2477151476382</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1305005541424438</v>
+        <v>0.1304776374444554</v>
       </c>
       <c r="T33">
         <v>1.309936120549913</v>
       </c>
       <c r="U33">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4022,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.61113282759001</v>
+        <v>5.81623257188949</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,13 +4164,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1071244338722856</v>
+        <v>0.1064846642030357</v>
       </c>
       <c r="C34">
-        <v>1111.835490457918</v>
+        <v>1121.945741340763</v>
       </c>
       <c r="D34">
-        <v>1396.683490457918</v>
+        <v>1406.793741340763</v>
       </c>
       <c r="E34">
         <v>-566.0519999999999</v>
@@ -4066,37 +4197,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M34">
-        <v>31.35395083335813</v>
+        <v>30.24830603335813</v>
       </c>
       <c r="N34">
-        <v>139.0793824999752</v>
+        <v>140.1850272999752</v>
       </c>
       <c r="O34">
-        <v>34.7698456249938</v>
+        <v>35.0462568249938</v>
       </c>
       <c r="P34">
-        <v>104.3095368749814</v>
+        <v>105.1387704749814</v>
       </c>
       <c r="Q34">
-        <v>180.7095368749814</v>
+        <v>181.5387704749814</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1315132341297997</v>
+        <v>0.1314900434397263</v>
       </c>
       <c r="T34">
         <v>1.325597719313064</v>
       </c>
       <c r="U34">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4104,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.435784926727821</v>
+        <v>5.634475304017943</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,13 +4246,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1070610330555138</v>
+        <v>0.106401806238626</v>
       </c>
       <c r="C35">
-        <v>1099.563793899013</v>
+        <v>1110.005891407794</v>
       </c>
       <c r="D35">
-        <v>1397.700793899013</v>
+        <v>1408.142891407794</v>
       </c>
       <c r="E35">
         <v>-552.7629999999999</v>
@@ -4148,37 +4279,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M35">
-        <v>32.33376179690057</v>
+        <v>31.19356559690057</v>
       </c>
       <c r="N35">
-        <v>138.0995715364328</v>
+        <v>139.2397677364328</v>
       </c>
       <c r="O35">
-        <v>34.52489288410819</v>
+        <v>34.80994193410819</v>
       </c>
       <c r="P35">
-        <v>103.5746786523246</v>
+        <v>104.4298258023246</v>
       </c>
       <c r="Q35">
-        <v>179.9746786523246</v>
+        <v>180.8298258023246</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1325561433705094</v>
+        <v>0.1325326705094828</v>
       </c>
       <c r="T35">
         <v>1.341726828487055</v>
       </c>
       <c r="U35">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4186,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.271064171372434</v>
+        <v>5.463733628138611</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,13 +4328,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.106997632238742</v>
+        <v>0.1063189482742163</v>
       </c>
       <c r="C36">
-        <v>1087.293580368502</v>
+        <v>1098.06863169562</v>
       </c>
       <c r="D36">
-        <v>1398.719580368502</v>
+        <v>1409.49463169562</v>
       </c>
       <c r="E36">
         <v>-539.4739999999999</v>
@@ -4230,37 +4361,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M36">
-        <v>33.31357276044302</v>
+        <v>32.13882516044302</v>
       </c>
       <c r="N36">
-        <v>137.1197605728903</v>
+        <v>138.2945081728903</v>
       </c>
       <c r="O36">
-        <v>34.27994014322258</v>
+        <v>34.57362704322258</v>
       </c>
       <c r="P36">
-        <v>102.8398204296678</v>
+        <v>103.7208811296677</v>
       </c>
       <c r="Q36">
-        <v>179.2398204296678</v>
+        <v>180.1208811296677</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1336306559215437</v>
+        <v>0.133606892338929</v>
       </c>
       <c r="T36">
         <v>1.358344698545106</v>
       </c>
       <c r="U36">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4268,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.116032872214419</v>
+        <v>5.303035580252181</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,13 +4410,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1069342314219703</v>
+        <v>0.1062360903098066</v>
       </c>
       <c r="C37">
-        <v>1075.024853111695</v>
+        <v>1086.133969670821</v>
       </c>
       <c r="D37">
-        <v>1399.739853111695</v>
+        <v>1410.84896967082</v>
       </c>
       <c r="E37">
         <v>-526.1849999999999</v>
@@ -4312,37 +4443,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M37">
-        <v>34.29338372398546</v>
+        <v>33.08408472398546</v>
       </c>
       <c r="N37">
-        <v>136.1399496093479</v>
+        <v>137.3492486093479</v>
       </c>
       <c r="O37">
-        <v>34.03498740233697</v>
+        <v>34.33731215233697</v>
       </c>
       <c r="P37">
-        <v>102.1049622070109</v>
+        <v>103.0119364570109</v>
       </c>
       <c r="Q37">
-        <v>178.5049622070109</v>
+        <v>179.4119364570109</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1347382303972253</v>
+        <v>0.1347141671477427</v>
       </c>
       <c r="T37">
         <v>1.375473887681867</v>
       </c>
       <c r="U37">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4350,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.969860504436864</v>
+        <v>5.151520277959261</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,13 +4492,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1068708306051985</v>
+        <v>0.1061532323453969</v>
       </c>
       <c r="C38">
-        <v>1062.757615383379</v>
+        <v>1074.2019128287</v>
       </c>
       <c r="D38">
-        <v>1400.761615383379</v>
+        <v>1412.205912828699</v>
       </c>
       <c r="E38">
         <v>-512.896</v>
@@ -4394,37 +4525,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M38">
-        <v>35.27319468752789</v>
+        <v>34.0293442875279</v>
       </c>
       <c r="N38">
-        <v>135.1601386458054</v>
+        <v>136.4039890458054</v>
       </c>
       <c r="O38">
-        <v>33.79003466145136</v>
+        <v>34.10099726145136</v>
       </c>
       <c r="P38">
-        <v>101.3701039843541</v>
+        <v>102.3029917843541</v>
       </c>
       <c r="Q38">
-        <v>177.7701039843541</v>
+        <v>178.7029917843541</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1358804165752718</v>
+        <v>0.1358560442943319</v>
       </c>
       <c r="T38">
         <v>1.393138363979151</v>
       </c>
       <c r="U38">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4432,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.831808823758063</v>
+        <v>5.008422492460394</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,13 +4574,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1068074297884267</v>
+        <v>0.1060703743809873</v>
       </c>
       <c r="C39">
-        <v>1050.491870447852</v>
+        <v>1062.272468693425</v>
       </c>
       <c r="D39">
-        <v>1401.784870447852</v>
+        <v>1413.565468693424</v>
       </c>
       <c r="E39">
         <v>-499.6069999999999</v>
@@ -4476,37 +4607,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M39">
-        <v>36.25300565107034</v>
+        <v>34.97460385107034</v>
       </c>
       <c r="N39">
-        <v>134.180327682263</v>
+        <v>135.458729482263</v>
       </c>
       <c r="O39">
-        <v>33.54508192056575</v>
+        <v>33.86468237056575</v>
       </c>
       <c r="P39">
-        <v>100.6352457616972</v>
+        <v>101.5940471116972</v>
       </c>
       <c r="Q39">
-        <v>177.0352457616972</v>
+        <v>177.9940471116972</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1370588626319865</v>
+        <v>0.1370341715090667</v>
       </c>
       <c r="T39">
         <v>1.411363617301746</v>
       </c>
       <c r="U39">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4514,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.701219396088927</v>
+        <v>4.873059722393895</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,13 +4656,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.106744028971655</v>
+        <v>0.1059875164165776</v>
       </c>
       <c r="C40">
-        <v>1038.227621578957</v>
+        <v>1050.345644818166</v>
       </c>
       <c r="D40">
-        <v>1402.809621578957</v>
+        <v>1414.927644818166</v>
       </c>
       <c r="E40">
         <v>-486.3179999999999</v>
@@ -4558,37 +4689,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M40">
-        <v>37.23281661461278</v>
+        <v>35.91986341461278</v>
       </c>
       <c r="N40">
-        <v>133.2005167187206</v>
+        <v>134.5134699187205</v>
       </c>
       <c r="O40">
-        <v>33.30012917968014</v>
+        <v>33.62836747968014</v>
       </c>
       <c r="P40">
-        <v>99.90038753904042</v>
+        <v>100.8851024390404</v>
       </c>
       <c r="Q40">
-        <v>176.3003875390404</v>
+        <v>177.2851024390404</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1382753230776275</v>
+        <v>0.1382503028275027</v>
       </c>
       <c r="T40">
         <v>1.430176782021844</v>
       </c>
       <c r="U40">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4596,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.577503096191849</v>
+        <v>4.744821308646689</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,13 +4738,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1074411281548832</v>
+        <v>0.1059046584521679</v>
       </c>
       <c r="C41">
-        <v>1013.753037136711</v>
+        <v>1038.421448785237</v>
       </c>
       <c r="D41">
-        <v>1391.624037136711</v>
+        <v>1416.292448785237</v>
       </c>
       <c r="E41">
         <v>-473.0289999999999</v>
@@ -4640,45 +4771,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M41">
-        <v>39.56013217815521</v>
+        <v>36.86512297815523</v>
       </c>
       <c r="N41">
-        <v>130.8732011551781</v>
+        <v>133.5682103551781</v>
       </c>
       <c r="O41">
-        <v>32.71830028879453</v>
+        <v>33.39205258879453</v>
       </c>
       <c r="P41">
-        <v>98.1549008663836</v>
+        <v>100.1761577663836</v>
       </c>
       <c r="Q41">
-        <v>174.5549008663836</v>
+        <v>176.5761577663836</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1395316674723059</v>
+        <v>0.1395063073039202</v>
       </c>
       <c r="T41">
         <v>1.449606771814732</v>
       </c>
       <c r="U41">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05724823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.308209400459113</v>
+        <v>4.623159223809594</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,13 +4820,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1073972273381114</v>
+        <v>0.1058218004877582</v>
       </c>
       <c r="C42">
-        <v>1001.163199482524</v>
+        <v>1026.499888206233</v>
       </c>
       <c r="D42">
-        <v>1392.323199482524</v>
+        <v>1417.659888206233</v>
       </c>
       <c r="E42">
         <v>-459.7399999999999</v>
@@ -4722,45 +4853,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M42">
-        <v>40.57449454169766</v>
+        <v>37.81038254169766</v>
       </c>
       <c r="N42">
-        <v>129.8588387916357</v>
+        <v>132.6229507916357</v>
       </c>
       <c r="O42">
-        <v>32.46470969790892</v>
+        <v>33.15573769790892</v>
       </c>
       <c r="P42">
-        <v>97.39412909372675</v>
+        <v>99.46721309372676</v>
       </c>
       <c r="Q42">
-        <v>173.7941290937268</v>
+        <v>175.8672130937268</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1408298900134735</v>
+        <v>0.1408041785962182</v>
       </c>
       <c r="T42">
         <v>1.469684427934049</v>
       </c>
       <c r="U42">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.05724823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.200504165447635</v>
+        <v>4.507580243214354</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,13 +4902,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1073533265213396</v>
+        <v>0.1065076925233485</v>
       </c>
       <c r="C43">
-        <v>988.5740647102751</v>
+        <v>1001.970237451435</v>
       </c>
       <c r="D43">
-        <v>1393.023064710275</v>
+        <v>1406.419237451435</v>
       </c>
       <c r="E43">
         <v>-446.4509999999999</v>
@@ -4804,37 +4935,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M43">
-        <v>41.5888569052401</v>
+        <v>40.1177646052401</v>
       </c>
       <c r="N43">
-        <v>128.8444764280932</v>
+        <v>130.3155687280932</v>
       </c>
       <c r="O43">
-        <v>32.21111910702331</v>
+        <v>32.57889218202331</v>
       </c>
       <c r="P43">
-        <v>96.63335732106992</v>
+        <v>97.73667654606993</v>
       </c>
       <c r="Q43">
-        <v>173.0333573210699</v>
+        <v>174.1366765460699</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1421721200984096</v>
+        <v>0.1421460455255434</v>
       </c>
       <c r="T43">
         <v>1.490442682565886</v>
       </c>
       <c r="U43">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4842,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.098052844339156</v>
+        <v>4.248325773143194</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,13 +4984,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1073094257045679</v>
+        <v>0.1064435845589389</v>
       </c>
       <c r="C44">
-        <v>975.9856338804294</v>
+        <v>989.7243049244286</v>
       </c>
       <c r="D44">
-        <v>1393.723633880429</v>
+        <v>1407.462304924429</v>
       </c>
       <c r="E44">
         <v>-433.1619999999999</v>
@@ -4886,37 +5017,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M44">
-        <v>42.60321926878254</v>
+        <v>41.09624666878254</v>
       </c>
       <c r="N44">
-        <v>127.8301140645508</v>
+        <v>129.3370866645508</v>
       </c>
       <c r="O44">
-        <v>31.9575285161377</v>
+        <v>32.3342716661377</v>
       </c>
       <c r="P44">
-        <v>95.8725855484131</v>
+        <v>97.00281499841309</v>
       </c>
       <c r="Q44">
-        <v>172.2725855484131</v>
+        <v>173.4028149984131</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.143560633979378</v>
+        <v>0.1435341837282935</v>
       </c>
       <c r="T44">
         <v>1.511916739081579</v>
       </c>
       <c r="U44">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4924,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.000480157569177</v>
+        <v>4.147175159496928</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,13 +5066,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1081362748877961</v>
+        <v>0.1063794765945292</v>
       </c>
       <c r="C45">
-        <v>949.6190125318723</v>
+        <v>977.4799207227408</v>
       </c>
       <c r="D45">
-        <v>1380.646012531872</v>
+        <v>1408.506920722741</v>
       </c>
       <c r="E45">
         <v>-419.8729999999999</v>
@@ -4968,45 +5099,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M45">
-        <v>45.16043453232498</v>
+        <v>42.07472873232499</v>
       </c>
       <c r="N45">
-        <v>125.2728988010084</v>
+        <v>128.3586046010084</v>
       </c>
       <c r="O45">
-        <v>31.31822470025209</v>
+        <v>32.08965115025209</v>
       </c>
       <c r="P45">
-        <v>93.95467410075626</v>
+        <v>96.26895345075627</v>
       </c>
       <c r="Q45">
-        <v>170.3546741007563</v>
+        <v>172.6689534507563</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1449978676456434</v>
+        <v>0.1449710285346489</v>
       </c>
       <c r="T45">
         <v>1.53414427126449</v>
       </c>
       <c r="U45">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05927323332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.773952467426778</v>
+        <v>4.050729225555139</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,13 +5148,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1081126240710243</v>
+        <v>0.1074703686301195</v>
       </c>
       <c r="C46">
-        <v>936.7006683795292</v>
+        <v>946.6239058730747</v>
       </c>
       <c r="D46">
-        <v>1381.016668379529</v>
+        <v>1390.939905873075</v>
       </c>
       <c r="E46">
         <v>-406.5839999999999</v>
@@ -5050,37 +5181,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M46">
-        <v>46.21067719586743</v>
+        <v>45.09971679586742</v>
       </c>
       <c r="N46">
-        <v>124.2226561374659</v>
+        <v>125.3336165374659</v>
       </c>
       <c r="O46">
-        <v>31.05566403436648</v>
+        <v>31.33340413436648</v>
       </c>
       <c r="P46">
-        <v>93.16699210309943</v>
+        <v>94.00021240309944</v>
       </c>
       <c r="Q46">
-        <v>169.5669921030994</v>
+        <v>170.4002124030994</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1464864310857041</v>
+        <v>0.1464591892269455</v>
       </c>
       <c r="T46">
         <v>1.557165643882505</v>
       </c>
       <c r="U46">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05927323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5088,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.688180820439806</v>
+        <v>3.779033338607361</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,13 +5230,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1080889732542525</v>
+        <v>0.1074325106657098</v>
       </c>
       <c r="C47">
-        <v>923.7825232972584</v>
+        <v>933.937203085286</v>
       </c>
       <c r="D47">
-        <v>1381.387523297258</v>
+        <v>1391.542203085286</v>
       </c>
       <c r="E47">
         <v>-393.2949999999998</v>
@@ -5132,37 +5263,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M47">
-        <v>47.26091985940987</v>
+        <v>46.12471035940987</v>
       </c>
       <c r="N47">
-        <v>123.1724134739235</v>
+        <v>124.3086229739235</v>
       </c>
       <c r="O47">
-        <v>30.79310336848086</v>
+        <v>31.07715574348087</v>
       </c>
       <c r="P47">
-        <v>92.37931010544258</v>
+        <v>93.2314672304426</v>
       </c>
       <c r="Q47">
-        <v>168.7793101054426</v>
+        <v>169.6314672304426</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1480291241054034</v>
+        <v>0.1480014648535075</v>
       </c>
       <c r="T47">
         <v>1.581024157322992</v>
       </c>
       <c r="U47">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05927323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5170,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.606221246652254</v>
+        <v>3.695054819971641</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,13 +5312,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1080653224374808</v>
+        <v>0.1073946527013002</v>
       </c>
       <c r="C48">
-        <v>910.8645774454767</v>
+        <v>921.2510221303671</v>
       </c>
       <c r="D48">
-        <v>1381.758577445477</v>
+        <v>1392.145022130367</v>
       </c>
       <c r="E48">
         <v>-380.0059999999999</v>
@@ -5214,37 +5345,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M48">
-        <v>48.31116252295232</v>
+        <v>47.14970392295231</v>
       </c>
       <c r="N48">
-        <v>122.122170810381</v>
+        <v>123.283629410381</v>
       </c>
       <c r="O48">
-        <v>30.53054270259526</v>
+        <v>30.82090735259526</v>
       </c>
       <c r="P48">
-        <v>91.59162810778577</v>
+        <v>92.46272205778577</v>
       </c>
       <c r="Q48">
-        <v>167.9916281077858</v>
+        <v>168.8627220577858</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.14962895390361</v>
+        <v>0.1496008617995718</v>
       </c>
       <c r="T48">
         <v>1.605766319409424</v>
       </c>
       <c r="U48">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05927323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5252,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.527825132594596</v>
+        <v>3.614727541276606</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,13 +5394,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.109698421620709</v>
+        <v>0.1073567947368905</v>
       </c>
       <c r="C49">
-        <v>872.4139335767295</v>
+        <v>908.5653636867887</v>
       </c>
       <c r="D49">
-        <v>1356.596933576729</v>
+        <v>1392.748363686789</v>
       </c>
       <c r="E49">
         <v>-366.7169999999999</v>
@@ -5296,45 +5427,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M49">
-        <v>52.29694528649476</v>
+        <v>48.17469748649476</v>
       </c>
       <c r="N49">
-        <v>118.1363880468386</v>
+        <v>122.2586358468386</v>
       </c>
       <c r="O49">
-        <v>29.53409701170964</v>
+        <v>30.56465896170965</v>
       </c>
       <c r="P49">
-        <v>88.60229103512893</v>
+        <v>91.69397688512893</v>
       </c>
       <c r="Q49">
-        <v>165.0022910351289</v>
+        <v>168.0939768851289</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.151289154637598</v>
+        <v>0.1512606133473743</v>
       </c>
       <c r="T49">
         <v>1.631442147989683</v>
       </c>
       <c r="U49">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.06279823332506819</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.258953891085992</v>
+        <v>3.537818444653699</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,13 +5476,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1097100208039372</v>
+        <v>0.1083269367724808</v>
       </c>
       <c r="C50">
-        <v>858.9494985312683</v>
+        <v>879.9784289738579</v>
       </c>
       <c r="D50">
-        <v>1356.421498531268</v>
+        <v>1377.450428973858</v>
       </c>
       <c r="E50">
         <v>-353.4279999999999</v>
@@ -5378,37 +5509,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M50">
-        <v>53.4096462500372</v>
+        <v>50.9857326500372</v>
       </c>
       <c r="N50">
-        <v>117.0236870832961</v>
+        <v>119.4476006832961</v>
       </c>
       <c r="O50">
-        <v>29.25592177082403</v>
+        <v>29.86190017082404</v>
       </c>
       <c r="P50">
-        <v>87.76776531247211</v>
+        <v>89.5857005124721</v>
       </c>
       <c r="Q50">
-        <v>164.1677653124721</v>
+        <v>165.9857005124721</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1530132092459702</v>
+        <v>0.1529842014931693</v>
       </c>
       <c r="T50">
         <v>1.658105508438414</v>
       </c>
       <c r="U50">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5416,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.191059018355034</v>
+        <v>3.342765210479112</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,13 +5558,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1097216199871654</v>
+        <v>0.1083100788080711</v>
       </c>
       <c r="C51">
-        <v>845.4851088544422</v>
+        <v>866.9523884555531</v>
       </c>
       <c r="D51">
-        <v>1356.246108854442</v>
+        <v>1377.713388455553</v>
       </c>
       <c r="E51">
         <v>-340.1389999999999</v>
@@ -5460,37 +5591,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M51">
-        <v>54.52234721357964</v>
+        <v>52.04793541357964</v>
       </c>
       <c r="N51">
-        <v>115.9109861197537</v>
+        <v>118.3853979197537</v>
       </c>
       <c r="O51">
-        <v>28.97774652993842</v>
+        <v>29.59634947993843</v>
       </c>
       <c r="P51">
-        <v>86.93323958981526</v>
+        <v>88.78904843981528</v>
       </c>
       <c r="Q51">
-        <v>163.3332395898153</v>
+        <v>165.1890484398153</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1548048738389844</v>
+        <v>0.1547753813309562</v>
       </c>
       <c r="T51">
         <v>1.685814490865527</v>
       </c>
       <c r="U51">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5498,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.125935364919217</v>
+        <v>3.274545512306069</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,13 +5640,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1097332191703937</v>
+        <v>0.1082932208436614</v>
       </c>
       <c r="C52">
-        <v>832.0207645286546</v>
+        <v>853.9264483559502</v>
       </c>
       <c r="D52">
-        <v>1356.070764528655</v>
+        <v>1377.97644835595</v>
       </c>
       <c r="E52">
         <v>-326.8499999999999</v>
@@ -5542,37 +5673,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M52">
-        <v>55.63504817712208</v>
+        <v>53.11013817712208</v>
       </c>
       <c r="N52">
-        <v>114.7982851562113</v>
+        <v>117.3231951562113</v>
       </c>
       <c r="O52">
-        <v>28.69957128905281</v>
+        <v>29.33079878905281</v>
       </c>
       <c r="P52">
-        <v>86.09871386715844</v>
+        <v>87.99239636715845</v>
       </c>
       <c r="Q52">
-        <v>162.4987138671584</v>
+        <v>164.3923963671585</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1566682050157192</v>
+        <v>0.1566382083622546</v>
       </c>
       <c r="T52">
         <v>1.714631832589724</v>
       </c>
       <c r="U52">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5580,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.063416657620833</v>
+        <v>3.209054602059948</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,13 +5722,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1097448183536219</v>
+        <v>0.1082763628792517</v>
       </c>
       <c r="C53">
-        <v>818.5564655363173</v>
+        <v>840.9006087325818</v>
       </c>
       <c r="D53">
-        <v>1355.895465536317</v>
+        <v>1378.239608732582</v>
       </c>
       <c r="E53">
         <v>-313.5609999999999</v>
@@ -5624,37 +5755,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M53">
-        <v>56.74774914066452</v>
+        <v>54.17234094066453</v>
       </c>
       <c r="N53">
-        <v>113.6855841926688</v>
+        <v>116.2609923926688</v>
       </c>
       <c r="O53">
-        <v>28.4213960481672</v>
+        <v>29.0652480981672</v>
       </c>
       <c r="P53">
-        <v>85.26418814450162</v>
+        <v>87.19574429450161</v>
       </c>
       <c r="Q53">
-        <v>161.6641881445016</v>
+        <v>163.5957442945016</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1586075905261982</v>
+        <v>0.1585770691499326</v>
       </c>
       <c r="T53">
         <v>1.74462539234348</v>
       </c>
       <c r="U53">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5662,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.00334966433415</v>
+        <v>3.14613196280387</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,13 +5804,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1133834175368501</v>
+        <v>0.108259504914842</v>
       </c>
       <c r="C54">
-        <v>752.4270015003187</v>
+        <v>827.874869643025</v>
       </c>
       <c r="D54">
-        <v>1303.055001500319</v>
+        <v>1378.502869643025</v>
       </c>
       <c r="E54">
         <v>-300.2719999999999</v>
@@ -5706,45 +5837,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M54">
-        <v>64.28701050420696</v>
+        <v>55.23454370420696</v>
       </c>
       <c r="N54">
-        <v>106.1463228291264</v>
+        <v>115.1987896291264</v>
       </c>
       <c r="O54">
-        <v>26.53658070728159</v>
+        <v>28.79969740728159</v>
       </c>
       <c r="P54">
-        <v>79.60974212184479</v>
+        <v>86.39909222184477</v>
       </c>
       <c r="Q54">
-        <v>156.0097421218448</v>
+        <v>162.7990922218448</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1606277837662805</v>
+        <v>0.1605967158037637</v>
       </c>
       <c r="T54">
         <v>1.775868683753643</v>
       </c>
       <c r="U54">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.651131729358921</v>
+        <v>3.085629425057642</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,13 +5886,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1134647667200783</v>
+        <v>0.1082426469504324</v>
       </c>
       <c r="C55">
-        <v>738.0036597618022</v>
+        <v>814.8492311448998</v>
       </c>
       <c r="D55">
-        <v>1301.920659761802</v>
+        <v>1378.7662311449</v>
       </c>
       <c r="E55">
         <v>-286.9829999999998</v>
@@ -5788,45 +5919,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M55">
-        <v>65.5232991677494</v>
+        <v>56.29674646774941</v>
       </c>
       <c r="N55">
-        <v>104.9100341655839</v>
+        <v>114.1365868655839</v>
       </c>
       <c r="O55">
-        <v>26.22750854139598</v>
+        <v>28.53414671639598</v>
       </c>
       <c r="P55">
-        <v>78.68252562418795</v>
+        <v>85.60244014918794</v>
       </c>
       <c r="Q55">
-        <v>155.082525624188</v>
+        <v>162.0024401491879</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1627339426761536</v>
+        <v>0.1627023048683962</v>
       </c>
       <c r="T55">
         <v>1.80844147692594</v>
       </c>
       <c r="U55">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.601110375974791</v>
+        <v>3.027410001943347</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,13 +5968,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1135461159033066</v>
+        <v>0.1113847889860227</v>
       </c>
       <c r="C56">
-        <v>723.5822912508485</v>
+        <v>754.1513257573268</v>
       </c>
       <c r="D56">
-        <v>1300.788291250848</v>
+        <v>1331.357325757327</v>
       </c>
       <c r="E56">
         <v>-273.6939999999998</v>
@@ -5870,37 +6001,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M56">
-        <v>66.75958783129185</v>
+        <v>62.95627603129186</v>
       </c>
       <c r="N56">
-        <v>103.6737455020415</v>
+        <v>107.4770573020415</v>
       </c>
       <c r="O56">
-        <v>25.91843637551037</v>
+        <v>26.86926432551037</v>
       </c>
       <c r="P56">
-        <v>77.75530912653112</v>
+        <v>80.60779297653112</v>
       </c>
       <c r="Q56">
-        <v>154.1553091265311</v>
+        <v>157.0077929765311</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1649316737125429</v>
+        <v>0.1648994412836649</v>
       </c>
       <c r="T56">
         <v>1.842430478497033</v>
       </c>
       <c r="U56">
-        <v>0.09303097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.06977323332506818</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5908,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.552941665308591</v>
+        <v>2.707169865775113</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,13 +6050,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1136274650865348</v>
+        <v>0.111426431021613</v>
       </c>
       <c r="C57">
-        <v>709.1628908231836</v>
+        <v>740.2559075959601</v>
       </c>
       <c r="D57">
-        <v>1299.657890823184</v>
+        <v>1330.75090759596</v>
       </c>
       <c r="E57">
         <v>-260.4049999999999</v>
@@ -5952,37 +6083,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M57">
-        <v>67.99587649483429</v>
+        <v>64.1221329948343</v>
       </c>
       <c r="N57">
-        <v>102.437456838499</v>
+        <v>106.311200338499</v>
       </c>
       <c r="O57">
-        <v>25.60936420962476</v>
+        <v>26.57780008462476</v>
       </c>
       <c r="P57">
-        <v>76.82809262887429</v>
+        <v>79.73340025387428</v>
       </c>
       <c r="Q57">
-        <v>153.2280926288743</v>
+        <v>156.1334002538743</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1672270816838829</v>
+        <v>0.1671942282062789</v>
       </c>
       <c r="T57">
         <v>1.877930102360174</v>
       </c>
       <c r="U57">
-        <v>0.09303097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.06977323332506818</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5990,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.506524544121162</v>
+        <v>2.657948595488293</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,13 +6132,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.115682814269763</v>
+        <v>0.1114680730572033</v>
       </c>
       <c r="C58">
-        <v>667.9513549801039</v>
+        <v>726.3610416162697</v>
       </c>
       <c r="D58">
-        <v>1271.735354980104</v>
+        <v>1330.14504161627</v>
       </c>
       <c r="E58">
         <v>-247.1159999999999</v>
@@ -6034,45 +6165,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M58">
-        <v>72.72982995837673</v>
+        <v>65.28798995837674</v>
       </c>
       <c r="N58">
-        <v>97.70350337495661</v>
+        <v>105.1453433749566</v>
       </c>
       <c r="O58">
-        <v>24.42587584373915</v>
+        <v>26.28633584373915</v>
       </c>
       <c r="P58">
-        <v>73.27762753121746</v>
+        <v>78.85900753121744</v>
       </c>
       <c r="Q58">
-        <v>149.6776275312175</v>
+        <v>155.2590075312174</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1696268263811928</v>
+        <v>0.1695933236253753</v>
       </c>
       <c r="T58">
         <v>1.915043345489822</v>
       </c>
       <c r="U58">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.07329823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.343375935718155</v>
+        <v>2.610485227711716</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,13 +6214,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1157994134529912</v>
+        <v>0.1115097150927936</v>
       </c>
       <c r="C59">
-        <v>653.1142391626786</v>
+        <v>712.4667270644049</v>
       </c>
       <c r="D59">
-        <v>1270.187239162679</v>
+        <v>1329.539727064405</v>
       </c>
       <c r="E59">
         <v>-233.8269999999998</v>
@@ -6116,45 +6247,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M59">
-        <v>74.02857692191918</v>
+        <v>66.45384692191919</v>
       </c>
       <c r="N59">
-        <v>96.40475641141416</v>
+        <v>103.9794864114141</v>
       </c>
       <c r="O59">
-        <v>24.10118910285354</v>
+        <v>25.99487160285354</v>
       </c>
       <c r="P59">
-        <v>72.30356730856062</v>
+        <v>77.98461480856061</v>
       </c>
       <c r="Q59">
-        <v>148.7035673085606</v>
+        <v>154.3846148085606</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1721381871109358</v>
+        <v>0.1721040048779181</v>
       </c>
       <c r="T59">
         <v>1.953882785974337</v>
       </c>
       <c r="U59">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.07329823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.302264077196783</v>
+        <v>2.564687241260633</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,13 +6296,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1159160126362195</v>
+        <v>0.111551357128384</v>
       </c>
       <c r="C60">
-        <v>638.2808878841624</v>
+        <v>698.5729631878871</v>
       </c>
       <c r="D60">
-        <v>1268.642887884162</v>
+        <v>1328.934963187887</v>
       </c>
       <c r="E60">
         <v>-220.538</v>
@@ -6198,45 +6329,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M60">
-        <v>75.3273238854616</v>
+        <v>67.6197038854616</v>
       </c>
       <c r="N60">
-        <v>95.10600944787174</v>
+        <v>102.8136294478717</v>
       </c>
       <c r="O60">
-        <v>23.77650236196794</v>
+        <v>25.70340736196793</v>
       </c>
       <c r="P60">
-        <v>71.3295070859038</v>
+        <v>77.1102220859038</v>
       </c>
       <c r="Q60">
-        <v>147.7295070859038</v>
+        <v>153.5102220859038</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.174769136446857</v>
+        <v>0.1747342423805819</v>
       </c>
       <c r="T60">
         <v>1.994571723624781</v>
       </c>
       <c r="U60">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.07329823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.262569868969253</v>
+        <v>2.520468495721658</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,13 +6378,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1160326118194477</v>
+        <v>0.1133187491639743</v>
       </c>
       <c r="C61">
-        <v>623.451287429939</v>
+        <v>660.1138746969417</v>
       </c>
       <c r="D61">
-        <v>1267.102287429939</v>
+        <v>1303.764874696942</v>
       </c>
       <c r="E61">
         <v>-207.2489999999999</v>
@@ -6280,37 +6411,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M61">
-        <v>76.62607084900405</v>
+        <v>71.84335974900405</v>
       </c>
       <c r="N61">
-        <v>93.80726248432929</v>
+        <v>98.58997358432929</v>
       </c>
       <c r="O61">
-        <v>23.45181562108232</v>
+        <v>24.64749339608232</v>
       </c>
       <c r="P61">
-        <v>70.35544686324697</v>
+        <v>73.94248018824696</v>
       </c>
       <c r="Q61">
-        <v>146.755446863247</v>
+        <v>150.342480188247</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1775284247747743</v>
+        <v>0.1774927841516684</v>
       </c>
       <c r="T61">
         <v>2.037245487502076</v>
       </c>
       <c r="U61">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6318,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.224221227122317</v>
+        <v>2.372290688085422</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,13 +6460,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1161492110026759</v>
+        <v>0.1133896411995646</v>
       </c>
       <c r="C62">
-        <v>608.6254241519283</v>
+        <v>645.8351485731163</v>
       </c>
       <c r="D62">
-        <v>1265.565424151928</v>
+        <v>1302.775148573116</v>
       </c>
       <c r="E62">
         <v>-193.9599999999999</v>
@@ -6362,37 +6493,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M62">
-        <v>77.92481781254648</v>
+        <v>73.06104381254649</v>
       </c>
       <c r="N62">
-        <v>92.50851552078686</v>
+        <v>97.37228952078685</v>
       </c>
       <c r="O62">
-        <v>23.12712888019671</v>
+        <v>24.34307238019671</v>
       </c>
       <c r="P62">
-        <v>69.38138664059014</v>
+        <v>73.02921714059013</v>
       </c>
       <c r="Q62">
-        <v>145.7813866405901</v>
+        <v>149.4292171405901</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1804256775190875</v>
+        <v>0.1803892530113092</v>
       </c>
       <c r="T62">
         <v>2.082052939573236</v>
       </c>
       <c r="U62">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6400,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.187150873336945</v>
+        <v>2.332752509950665</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,13 +6542,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1162658101859042</v>
+        <v>0.1134605332351549</v>
       </c>
       <c r="C63">
-        <v>593.8032844681862</v>
+        <v>631.557923969653</v>
       </c>
       <c r="D63">
-        <v>1264.032284468186</v>
+        <v>1301.786923969653</v>
       </c>
       <c r="E63">
         <v>-180.6709999999999</v>
@@ -6444,37 +6575,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M63">
-        <v>79.22356477608892</v>
+        <v>74.27872787608892</v>
       </c>
       <c r="N63">
-        <v>91.20976855724442</v>
+        <v>96.15460545724441</v>
       </c>
       <c r="O63">
-        <v>22.8024421393111</v>
+        <v>24.0386513643111</v>
       </c>
       <c r="P63">
-        <v>68.40732641793332</v>
+        <v>72.11595409293331</v>
       </c>
       <c r="Q63">
-        <v>144.8073264179333</v>
+        <v>148.5159540929333</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1834715073272117</v>
+        <v>0.183434258735547</v>
       </c>
       <c r="T63">
         <v>2.129158209699328</v>
       </c>
       <c r="U63">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6482,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.151295940987159</v>
+        <v>2.294510665525245</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,13 +6624,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1163824093691324</v>
+        <v>0.1135314252707452</v>
       </c>
       <c r="C64">
-        <v>578.9848548625031</v>
+        <v>617.2821974721909</v>
       </c>
       <c r="D64">
-        <v>1262.502854862503</v>
+        <v>1300.800197472191</v>
       </c>
       <c r="E64">
         <v>-167.3819999999999</v>
@@ -6526,37 +6657,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M64">
-        <v>80.52231173963136</v>
+        <v>75.49641193963137</v>
       </c>
       <c r="N64">
-        <v>89.91102159370197</v>
+        <v>94.93692139370197</v>
       </c>
       <c r="O64">
-        <v>22.47775539842549</v>
+        <v>23.73423034842549</v>
       </c>
       <c r="P64">
-        <v>67.43326619527647</v>
+        <v>71.20269104527648</v>
       </c>
       <c r="Q64">
-        <v>143.8332661952765</v>
+        <v>147.6026910452765</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1866776439673424</v>
+        <v>0.1866395279189551</v>
       </c>
       <c r="T64">
         <v>2.178742704568898</v>
       </c>
       <c r="U64">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6564,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.116597619358334</v>
+        <v>2.257502428984515</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,13 +6706,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1164990085523606</v>
+        <v>0.1136023173063355</v>
       </c>
       <c r="C65">
-        <v>564.1701218840058</v>
+        <v>603.0079656767136</v>
       </c>
       <c r="D65">
-        <v>1260.977121884006</v>
+        <v>1299.814965676714</v>
       </c>
       <c r="E65">
         <v>-154.0929999999998</v>
@@ -6608,37 +6739,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M65">
-        <v>81.82105870317382</v>
+        <v>76.71409600317382</v>
       </c>
       <c r="N65">
-        <v>88.61227463015952</v>
+        <v>93.71923733015952</v>
       </c>
       <c r="O65">
-        <v>22.15306865753988</v>
+        <v>23.42980933253988</v>
       </c>
       <c r="P65">
-        <v>66.45920597261964</v>
+        <v>70.28942799761964</v>
       </c>
       <c r="Q65">
-        <v>142.8592059726196</v>
+        <v>146.6894279976196</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1900570852907234</v>
+        <v>0.1900180548960611</v>
       </c>
       <c r="T65">
         <v>2.23100744240439</v>
       </c>
       <c r="U65">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6646,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.083000831749471</v>
+        <v>2.221669057095871</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,13 +6788,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1166156077355888</v>
+        <v>0.1136732093419259</v>
       </c>
       <c r="C66">
-        <v>549.3590721467642</v>
+        <v>588.7352251895104</v>
       </c>
       <c r="D66">
-        <v>1259.455072146764</v>
+        <v>1298.83122518951</v>
       </c>
       <c r="E66">
         <v>-140.8039999999999</v>
@@ -6690,37 +6821,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M66">
-        <v>83.11980566671626</v>
+        <v>77.93178006671626</v>
       </c>
       <c r="N66">
-        <v>87.31352766661708</v>
+        <v>92.50155326661708</v>
       </c>
       <c r="O66">
-        <v>21.82838191665427</v>
+        <v>23.12538831665427</v>
       </c>
       <c r="P66">
-        <v>65.48514574996281</v>
+        <v>69.37616494996281</v>
       </c>
       <c r="Q66">
-        <v>141.8851457499628</v>
+        <v>145.7761649499628</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1936242733542922</v>
+        <v>0.1935842778163395</v>
       </c>
       <c r="T66">
         <v>2.286175776786299</v>
       </c>
       <c r="U66">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6728,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.050453943753385</v>
+        <v>2.186955478078748</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,13 +6870,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1167322069188171</v>
+        <v>0.1137441013775162</v>
       </c>
       <c r="C67">
-        <v>534.5516923294001</v>
+        <v>574.4639726271366</v>
       </c>
       <c r="D67">
-        <v>1257.9366923294</v>
+        <v>1297.848972627137</v>
       </c>
       <c r="E67">
         <v>-127.5149999999999</v>
@@ -6772,37 +6903,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M67">
-        <v>84.4185526302587</v>
+        <v>79.14946413025871</v>
       </c>
       <c r="N67">
-        <v>86.01478070307463</v>
+        <v>91.28386920307463</v>
       </c>
       <c r="O67">
-        <v>21.50369517576866</v>
+        <v>22.82096730076866</v>
       </c>
       <c r="P67">
-        <v>64.51108552730598</v>
+        <v>68.46290190230597</v>
       </c>
       <c r="Q67">
-        <v>140.911085527306</v>
+        <v>144.862901902306</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1973953007357793</v>
+        <v>0.1973542849034911</v>
       </c>
       <c r="T67">
         <v>2.344496587418603</v>
       </c>
       <c r="U67">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.07329823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6810,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.018908498464872</v>
+        <v>2.153310009185229</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,13 +6952,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1249173061020453</v>
+        <v>0.1138149934131065</v>
       </c>
       <c r="C68">
-        <v>423.1097755787382</v>
+        <v>560.1942046163738</v>
       </c>
       <c r="D68">
-        <v>1159.783775578738</v>
+        <v>1296.868204616374</v>
       </c>
       <c r="E68">
         <v>-114.2259999999999</v>
@@ -6854,45 +6985,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M68">
-        <v>100.0136057938011</v>
+        <v>80.36714819380114</v>
       </c>
       <c r="N68">
-        <v>70.41972753953219</v>
+        <v>90.06618513953219</v>
       </c>
       <c r="O68">
-        <v>17.60493188488305</v>
+        <v>22.51654628488305</v>
       </c>
       <c r="P68">
-        <v>52.81479565464915</v>
+        <v>67.54963885464915</v>
       </c>
       <c r="Q68">
-        <v>129.2147956546492</v>
+        <v>143.9496388546492</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2013881532573538</v>
+        <v>0.2013460571134162</v>
       </c>
       <c r="T68">
         <v>2.406248033970453</v>
       </c>
       <c r="U68">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.08552323332506818</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.704101476800238</v>
+        <v>2.12068409995515</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,13 +7034,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1251561552852735</v>
+        <v>0.1138858854486968</v>
       </c>
       <c r="C69">
-        <v>407.1860611721096</v>
+        <v>545.9259177941927</v>
       </c>
       <c r="D69">
-        <v>1157.14906117211</v>
+        <v>1295.888917794193</v>
       </c>
       <c r="E69">
         <v>-100.9369999999998</v>
@@ -6936,45 +7067,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M69">
-        <v>101.5289634573436</v>
+        <v>81.58483225734359</v>
       </c>
       <c r="N69">
-        <v>68.90436987598974</v>
+        <v>88.84850107598974</v>
       </c>
       <c r="O69">
-        <v>17.22609246899744</v>
+        <v>22.21212526899744</v>
       </c>
       <c r="P69">
-        <v>51.67827740699231</v>
+        <v>66.63637580699231</v>
       </c>
       <c r="Q69">
-        <v>128.0782774069923</v>
+        <v>143.0363758069923</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2056229968408419</v>
+        <v>0.2055797549118216</v>
       </c>
       <c r="T69">
         <v>2.471741992434537</v>
       </c>
       <c r="U69">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.08552323332506818</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.678667126400234</v>
+        <v>2.089032098463282</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,13 +7116,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1253950044685017</v>
+        <v>0.1139567774842871</v>
       </c>
       <c r="C70">
-        <v>391.2742903470129</v>
+        <v>531.6591088077149</v>
       </c>
       <c r="D70">
-        <v>1154.526290347013</v>
+        <v>1294.911108807715</v>
       </c>
       <c r="E70">
         <v>-87.6479999999998</v>
@@ -7018,45 +7149,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M70">
-        <v>103.044321120886</v>
+        <v>82.80251632088603</v>
       </c>
       <c r="N70">
-        <v>67.3890122124473</v>
+        <v>87.63081701244731</v>
       </c>
       <c r="O70">
-        <v>16.84725305311182</v>
+        <v>21.90770425311183</v>
       </c>
       <c r="P70">
-        <v>50.54175915933547</v>
+        <v>65.72311275933548</v>
       </c>
       <c r="Q70">
-        <v>126.9417591593355</v>
+        <v>142.1231127593355</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.210122518148298</v>
+        <v>0.2100780588226274</v>
       </c>
       <c r="T70">
         <v>2.541329323302627</v>
       </c>
       <c r="U70">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.08552323332506818</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.653980845129642</v>
+        <v>2.058311038191763</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,13 +7198,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.12563385365173</v>
+        <v>0.1140276695198774</v>
       </c>
       <c r="C71">
-        <v>375.3743820738617</v>
+        <v>517.3937743141738</v>
       </c>
       <c r="D71">
-        <v>1151.915382073862</v>
+        <v>1293.934774314174</v>
       </c>
       <c r="E71">
         <v>-74.35899999999981</v>
@@ -7100,45 +7231,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M71">
-        <v>104.5596787844285</v>
+        <v>84.02020038442848</v>
       </c>
       <c r="N71">
-        <v>65.87365454890485</v>
+        <v>86.41313294890486</v>
       </c>
       <c r="O71">
-        <v>16.46841363722621</v>
+        <v>21.60328323722621</v>
       </c>
       <c r="P71">
-        <v>49.40524091167864</v>
+        <v>64.80984971167865</v>
       </c>
       <c r="Q71">
-        <v>125.8052409116787</v>
+        <v>141.2098497116787</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2149123311530094</v>
+        <v>0.2148665758889691</v>
       </c>
       <c r="T71">
         <v>2.615406159388013</v>
       </c>
       <c r="U71">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.08552323332506818</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.630010108243706</v>
+        <v>2.02848044343536</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,13 +7280,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1258727028349582</v>
+        <v>0.1215535615554678</v>
       </c>
       <c r="C72">
-        <v>359.4862560543946</v>
+        <v>408.2109014988674</v>
       </c>
       <c r="D72">
-        <v>1149.316256054395</v>
+        <v>1198.040901498867</v>
       </c>
       <c r="E72">
         <v>-61.06999999999982</v>
@@ -7182,37 +7313,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M72">
-        <v>106.0750364479709</v>
+        <v>98.44715044797091</v>
       </c>
       <c r="N72">
-        <v>64.35829688536242</v>
+        <v>71.98618288536242</v>
       </c>
       <c r="O72">
-        <v>16.08957422134061</v>
+        <v>17.99654572134061</v>
       </c>
       <c r="P72">
-        <v>48.26872266402182</v>
+        <v>53.98963716402181</v>
       </c>
       <c r="Q72">
-        <v>124.6687226640218</v>
+        <v>130.3896371640218</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2200214650247015</v>
+        <v>0.2199743274264002</v>
       </c>
       <c r="T72">
         <v>2.694421451212424</v>
       </c>
       <c r="U72">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.08552323332506818</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7220,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.60672424955451</v>
+        <v>1.731216521329451</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,13 +7362,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1261115520181864</v>
+        <v>0.1217309535910581</v>
       </c>
       <c r="C73">
-        <v>343.6098327134439</v>
+        <v>392.8327580129396</v>
       </c>
       <c r="D73">
-        <v>1146.728832713444</v>
+        <v>1195.95175801294</v>
       </c>
       <c r="E73">
         <v>-47.78099999999995</v>
@@ -7264,37 +7395,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M73">
-        <v>107.5903941115133</v>
+        <v>99.85353831151335</v>
       </c>
       <c r="N73">
-        <v>62.84293922181999</v>
+        <v>70.57979502181999</v>
       </c>
       <c r="O73">
-        <v>15.710734805455</v>
+        <v>17.644948755455</v>
       </c>
       <c r="P73">
-        <v>47.13220441636499</v>
+        <v>52.93484626636499</v>
       </c>
       <c r="Q73">
-        <v>123.532204416365</v>
+        <v>129.334846266365</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2254829529565103</v>
+        <v>0.2254343376905506</v>
       </c>
       <c r="T73">
         <v>2.778886073507484</v>
       </c>
       <c r="U73">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.08552323332506818</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7302,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.5840943305467</v>
+        <v>1.706833190043121</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,13 +7444,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1263504012014146</v>
+        <v>0.1219083456266484</v>
       </c>
       <c r="C74">
-        <v>327.7450331908119</v>
+        <v>377.461887939628</v>
       </c>
       <c r="D74">
-        <v>1144.153033190812</v>
+        <v>1193.869887939628</v>
       </c>
       <c r="E74">
         <v>-34.49199999999996</v>
@@ -7346,37 +7477,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M74">
-        <v>109.1057517750558</v>
+        <v>101.2599261750558</v>
       </c>
       <c r="N74">
-        <v>61.32758155827756</v>
+        <v>69.17340715827756</v>
       </c>
       <c r="O74">
-        <v>15.33189538956939</v>
+        <v>17.29335178956939</v>
       </c>
       <c r="P74">
-        <v>45.99568616870817</v>
+        <v>51.88005536870817</v>
       </c>
       <c r="Q74">
-        <v>122.3956861687082</v>
+        <v>128.2800553687082</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2313345471691626</v>
+        <v>0.2312843486878547</v>
       </c>
       <c r="T74">
         <v>2.869383883109334</v>
       </c>
       <c r="U74">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.08552323332506818</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7384,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.562093020400218</v>
+        <v>1.683127173514745</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,13 +7526,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1265892503846429</v>
+        <v>0.1220857376622387</v>
       </c>
       <c r="C75">
-        <v>311.8917793332627</v>
+        <v>362.0982533610473</v>
       </c>
       <c r="D75">
-        <v>1141.588779333263</v>
+        <v>1191.795253361047</v>
       </c>
       <c r="E75">
         <v>-21.20299999999986</v>
@@ -7428,37 +7559,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M75">
-        <v>110.6211094385982</v>
+        <v>102.6663140385982</v>
       </c>
       <c r="N75">
-        <v>59.8122238947351</v>
+        <v>67.76701929473509</v>
       </c>
       <c r="O75">
-        <v>14.95305597368377</v>
+        <v>16.94175482368377</v>
       </c>
       <c r="P75">
-        <v>44.85916792105132</v>
+        <v>50.82526447105132</v>
       </c>
       <c r="Q75">
-        <v>121.2591679210513</v>
+        <v>127.2252644710513</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2376195928049744</v>
+        <v>0.2375676938331072</v>
       </c>
       <c r="T75">
         <v>2.966585234163173</v>
       </c>
       <c r="U75">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.08552323332506818</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7466,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.540694485874187</v>
+        <v>1.660070636891255</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,13 +7608,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1268280995678711</v>
+        <v>0.122263129697829</v>
       </c>
       <c r="C76">
-        <v>296.0499936866144</v>
+        <v>346.741816622423</v>
       </c>
       <c r="D76">
-        <v>1139.035993686614</v>
+        <v>1189.727816622423</v>
       </c>
       <c r="E76">
         <v>-7.913999999999874</v>
@@ -7510,37 +7641,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M76">
-        <v>112.1364671021407</v>
+        <v>104.0727019021407</v>
       </c>
       <c r="N76">
-        <v>58.29686623119265</v>
+        <v>66.36063143119266</v>
       </c>
       <c r="O76">
-        <v>14.57421655779816</v>
+        <v>16.59015785779816</v>
       </c>
       <c r="P76">
-        <v>43.72264967339449</v>
+        <v>49.7704735733945</v>
       </c>
       <c r="Q76">
-        <v>120.1226496733945</v>
+        <v>126.1704735733945</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2443881034896947</v>
+        <v>0.2443343732203022</v>
       </c>
       <c r="T76">
         <v>3.071263612221153</v>
       </c>
       <c r="U76">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.08552323332506818</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7548,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.519874290119131</v>
+        <v>1.637637249906238</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,13 +7690,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1659929211013388</v>
+        <v>0.1224405217334193</v>
       </c>
       <c r="C77">
-        <v>-22.83692198854396</v>
+        <v>331.3925403298091</v>
       </c>
       <c r="D77">
-        <v>833.4380780114561</v>
+        <v>1187.667540329809</v>
       </c>
       <c r="E77">
         <v>5.375000000000114</v>
@@ -7592,45 +7723,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M77">
-        <v>178.8343697656831</v>
+        <v>105.4790897656831</v>
       </c>
       <c r="N77">
-        <v>-8.401036432349798</v>
+        <v>64.95424356765022</v>
       </c>
       <c r="O77">
-        <v>-2.10025910808745</v>
+        <v>16.23856089191256</v>
       </c>
       <c r="P77">
-        <v>-6.300777324262349</v>
+        <v>48.71568267573767</v>
       </c>
       <c r="Q77">
-        <v>70.09922267573765</v>
+        <v>125.1156826757377</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.253930187129865</v>
+        <v>0.2516423869584729</v>
       </c>
       <c r="T77">
-        <v>3.218836673013018</v>
+        <v>3.184316260523773</v>
       </c>
       <c r="U77">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V77">
-        <v>0.2382558419232315</v>
+        <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.1366804990918301</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.9530233676929261</v>
+        <v>1.615802086574155</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,13 +7772,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1673292308790064</v>
+        <v>0.1226179137690097</v>
       </c>
       <c r="C78">
-        <v>-43.68623381499924</v>
+        <v>316.0503873478361</v>
       </c>
       <c r="D78">
-        <v>825.8777661850008</v>
+        <v>1185.614387347836</v>
       </c>
       <c r="E78">
         <v>18.6640000000001</v>
@@ -7674,45 +7805,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M78">
-        <v>181.2188280292256</v>
+        <v>106.8854776292256</v>
       </c>
       <c r="N78">
-        <v>-10.78549469589223</v>
+        <v>63.54785570410777</v>
       </c>
       <c r="O78">
-        <v>-2.696373673973056</v>
+        <v>15.88696392602694</v>
       </c>
       <c r="P78">
-        <v>-8.089121021919169</v>
+        <v>47.66089177808083</v>
       </c>
       <c r="Q78">
-        <v>68.31087897808084</v>
+        <v>124.0608917780808</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.262602278260276</v>
+        <v>0.2595594018414911</v>
       </c>
       <c r="T78">
-        <v>3.352954867721894</v>
+        <v>3.306789962851611</v>
       </c>
       <c r="U78">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V78">
-        <v>0.235120896634768</v>
+        <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.1372430053901844</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.9404835865390718</v>
+        <v>1.594541532803442</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,13 +7854,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.168665540656674</v>
+        <v>0.1227953058046</v>
       </c>
       <c r="C79">
-        <v>-64.39961597594288</v>
+        <v>300.7153207974785</v>
       </c>
       <c r="D79">
-        <v>818.4533840240572</v>
+        <v>1183.568320797478</v>
       </c>
       <c r="E79">
         <v>31.95300000000009</v>
@@ -7756,45 +7887,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M79">
-        <v>183.603286292768</v>
+        <v>108.291865492768</v>
       </c>
       <c r="N79">
-        <v>-13.16995295943468</v>
+        <v>62.14146784056534</v>
       </c>
       <c r="O79">
-        <v>-3.29248823985867</v>
+        <v>15.53536696014134</v>
       </c>
       <c r="P79">
-        <v>-9.877464719576011</v>
+        <v>46.60610088042401</v>
       </c>
       <c r="Q79">
-        <v>66.52253528042399</v>
+        <v>123.006100880424</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2720284642715924</v>
+        <v>0.2681648528012934</v>
       </c>
       <c r="T79">
-        <v>3.498735514144586</v>
+        <v>3.439913552338391</v>
       </c>
       <c r="U79">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V79">
-        <v>0.2320673784966541</v>
+        <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.1377909011353347</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.9282695139866163</v>
+        <v>1.573833201208592</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,13 +7936,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1700018504343416</v>
+        <v>0.1229726978401903</v>
       </c>
       <c r="C80">
-        <v>-84.98070170495953</v>
+        <v>285.3873040538479</v>
       </c>
       <c r="D80">
-        <v>811.1612982950406</v>
+        <v>1181.529304053848</v>
       </c>
       <c r="E80">
         <v>45.24200000000019</v>
@@ -7838,45 +7969,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M80">
-        <v>185.9877445563105</v>
+        <v>109.6982533563104</v>
       </c>
       <c r="N80">
-        <v>-15.55441122297714</v>
+        <v>60.73507997702289</v>
       </c>
       <c r="O80">
-        <v>-3.888602805744284</v>
+        <v>15.18376999425572</v>
       </c>
       <c r="P80">
-        <v>-11.66580841723285</v>
+        <v>45.55130998276717</v>
       </c>
       <c r="Q80">
-        <v>64.73419158276715</v>
+        <v>121.9513099827672</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2823115762839375</v>
+        <v>0.2775526174847142</v>
       </c>
       <c r="T80">
-        <v>3.657768946605703</v>
+        <v>3.585139286323968</v>
       </c>
       <c r="U80">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V80">
-        <v>0.2290921556954149</v>
+        <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.138324748271635</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9163686227816596</v>
+        <v>1.553655852475149</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,13 +8018,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1713381602120091</v>
+        <v>0.1231500898757806</v>
       </c>
       <c r="C81">
-        <v>-105.432995896566</v>
+        <v>270.066300744006</v>
       </c>
       <c r="D81">
-        <v>803.9980041034341</v>
+        <v>1179.497300744006</v>
       </c>
       <c r="E81">
         <v>58.53100000000018</v>
@@ -7920,45 +8051,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M81">
-        <v>188.3722028198529</v>
+        <v>111.1046412198529</v>
       </c>
       <c r="N81">
-        <v>-17.93886948651956</v>
+        <v>59.32869211348044</v>
       </c>
       <c r="O81">
-        <v>-4.484717371629891</v>
+        <v>14.83217302837011</v>
       </c>
       <c r="P81">
-        <v>-13.45415211488967</v>
+        <v>44.49651908511034</v>
       </c>
       <c r="Q81">
-        <v>62.94584788511033</v>
+        <v>120.8965190851103</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2935740322974584</v>
+        <v>0.2878344549951274</v>
       </c>
       <c r="T81">
-        <v>3.831948420253594</v>
+        <v>3.744196042593888</v>
       </c>
       <c r="U81">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V81">
-        <v>0.2261922549904097</v>
+        <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.1388450802905606</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.9047690199616387</v>
+        <v>1.533989322696982</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,13 +8100,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1726744699896767</v>
+        <v>0.123327481911371</v>
       </c>
       <c r="C82">
-        <v>-125.7598807233641</v>
+        <v>254.7522747448036</v>
       </c>
       <c r="D82">
-        <v>796.9601192766361</v>
+        <v>1177.472274744804</v>
       </c>
       <c r="E82">
         <v>71.82000000000016</v>
@@ -8002,45 +8133,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M82">
-        <v>190.7566610833954</v>
+        <v>112.5110290833953</v>
       </c>
       <c r="N82">
-        <v>-20.32332775006202</v>
+        <v>57.92230424993801</v>
       </c>
       <c r="O82">
-        <v>-5.080831937515505</v>
+        <v>14.4805760624845</v>
       </c>
       <c r="P82">
-        <v>-15.24249581254652</v>
+        <v>43.44172818745351</v>
       </c>
       <c r="Q82">
-        <v>61.15750418745349</v>
+        <v>119.8417281874535</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3059627339123314</v>
+        <v>0.2991444762565821</v>
       </c>
       <c r="T82">
-        <v>4.023545841266274</v>
+        <v>3.919158474490799</v>
       </c>
       <c r="U82">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V82">
-        <v>0.2233648518030295</v>
+        <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.1393524040090131</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8934594072121181</v>
+        <v>1.51481445616327</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,13 +8182,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1740107797673443</v>
+        <v>0.1592195731865994</v>
       </c>
       <c r="C83">
-        <v>-145.9646209607268</v>
+        <v>-62.10792753547059</v>
       </c>
       <c r="D83">
-        <v>790.0443790392733</v>
+        <v>873.9010724645295</v>
       </c>
       <c r="E83">
         <v>85.10900000000015</v>
@@ -8084,37 +8215,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M83">
-        <v>193.1411193469378</v>
+        <v>175.0574481469378</v>
       </c>
       <c r="N83">
-        <v>-22.70778601360445</v>
+        <v>-4.62411481360445</v>
       </c>
       <c r="O83">
-        <v>-5.676946503401112</v>
+        <v>-1.156028703401113</v>
       </c>
       <c r="P83">
-        <v>-17.03083951020334</v>
+        <v>-3.468086110203338</v>
       </c>
       <c r="Q83">
-        <v>59.36916048979667</v>
+        <v>72.93191388979668</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3196555093814014</v>
+        <v>0.3134281063248494</v>
       </c>
       <c r="T83">
-        <v>4.235311411859236</v>
+        <v>4.140121688908177</v>
       </c>
       <c r="U83">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V83">
-        <v>0.2206072610400292</v>
+        <v>0.2433962895287336</v>
       </c>
       <c r="W83">
-        <v>0.1398472012158988</v>
+        <v>0.1230472012158988</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8122,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8824290441601167</v>
+        <v>0.9735851581149343</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,13 +8264,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1753470895450119</v>
+        <v>0.160387882964267</v>
       </c>
       <c r="C84">
-        <v>-166.0503690366394</v>
+        <v>-82.66973313233234</v>
       </c>
       <c r="D84">
-        <v>783.2476309633607</v>
+        <v>866.6282668676678</v>
       </c>
       <c r="E84">
         <v>98.39800000000014</v>
@@ -8166,37 +8297,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M84">
-        <v>195.5255776104802</v>
+        <v>177.2186512104802</v>
       </c>
       <c r="N84">
-        <v>-25.0922442771469</v>
+        <v>-6.785317877146895</v>
       </c>
       <c r="O84">
-        <v>-6.273061069286726</v>
+        <v>-1.696329469286724</v>
       </c>
       <c r="P84">
-        <v>-18.81918320786018</v>
+        <v>-5.088988407860171</v>
       </c>
       <c r="Q84">
-        <v>57.58081679213983</v>
+        <v>71.31101159213983</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3348697043470348</v>
+        <v>0.3282963344540078</v>
       </c>
       <c r="T84">
-        <v>4.47060649029586</v>
+        <v>4.370128449403077</v>
       </c>
       <c r="U84">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V84">
-        <v>0.2179169285883215</v>
+        <v>0.2404280420954563</v>
       </c>
       <c r="W84">
-        <v>0.1403299301982264</v>
+        <v>0.1235299301982264</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8204,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8716677143532859</v>
+        <v>0.9617121683818253</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,13 +8346,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1766833993226795</v>
+        <v>0.1615561927419346</v>
       </c>
       <c r="C85">
-        <v>-186.0201698230976</v>
+        <v>-103.1114859165384</v>
       </c>
       <c r="D85">
-        <v>776.5668301769025</v>
+        <v>859.4755140834617</v>
       </c>
       <c r="E85">
         <v>111.6870000000001</v>
@@ -8248,37 +8379,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M85">
-        <v>197.9100358740227</v>
+        <v>179.3798542740226</v>
       </c>
       <c r="N85">
-        <v>-27.47670254068933</v>
+        <v>-8.946520940689311</v>
       </c>
       <c r="O85">
-        <v>-6.869175635172333</v>
+        <v>-2.236630235172328</v>
       </c>
       <c r="P85">
-        <v>-20.607526905517</v>
+        <v>-6.709890705516983</v>
       </c>
       <c r="Q85">
-        <v>55.79247309448301</v>
+        <v>69.69010929448302</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3518738046027428</v>
+        <v>0.3449137658924789</v>
       </c>
       <c r="T85">
-        <v>4.733583342666205</v>
+        <v>4.627194828779729</v>
       </c>
       <c r="U85">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V85">
-        <v>0.2152914234246068</v>
+        <v>0.2375313186967159</v>
       </c>
       <c r="W85">
-        <v>0.1408010271568834</v>
+        <v>0.1240010271568834</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8286,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8611656936984271</v>
+        <v>0.9501252747868637</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,13 +8428,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.178019709100347</v>
+        <v>0.1627245025196022</v>
       </c>
       <c r="C86">
-        <v>-205.8769651843692</v>
+        <v>-123.4361341373785</v>
       </c>
       <c r="D86">
-        <v>769.9990348156309</v>
+        <v>852.4398658626216</v>
       </c>
       <c r="E86">
         <v>124.9760000000001</v>
@@ -8330,37 +8461,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M86">
-        <v>200.2944941375651</v>
+        <v>181.5410573375651</v>
       </c>
       <c r="N86">
-        <v>-29.86116080423179</v>
+        <v>-11.10772400423176</v>
       </c>
       <c r="O86">
-        <v>-7.465290201057947</v>
+        <v>-2.776931001057939</v>
       </c>
       <c r="P86">
-        <v>-22.39587060317384</v>
+        <v>-8.330793003173817</v>
       </c>
       <c r="Q86">
-        <v>54.00412939682617</v>
+        <v>68.06920699682618</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.371003417390414</v>
+        <v>0.3636083762607586</v>
       </c>
       <c r="T86">
-        <v>5.02943230158284</v>
+        <v>4.916394505578459</v>
       </c>
       <c r="U86">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V86">
-        <v>0.2127284302885996</v>
+        <v>0.2347035649027074</v>
       </c>
       <c r="W86">
-        <v>0.1412609075212866</v>
+        <v>0.1244609075212866</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8368,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8509137211543982</v>
+        <v>0.9388142596108296</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,13 +8510,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1793560188780146</v>
+        <v>0.1638928122972697</v>
       </c>
       <c r="C87">
-        <v>-225.6235982963906</v>
+        <v>-143.6465302907535</v>
       </c>
       <c r="D87">
-        <v>763.5414017036095</v>
+        <v>845.5184697092466</v>
       </c>
       <c r="E87">
         <v>138.2650000000001</v>
@@ -8412,37 +8543,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M87">
-        <v>202.6789524011076</v>
+        <v>183.7022604011075</v>
       </c>
       <c r="N87">
-        <v>-32.24561906777421</v>
+        <v>-13.2689270677742</v>
       </c>
       <c r="O87">
-        <v>-8.061404766943554</v>
+        <v>-3.31723176694355</v>
       </c>
       <c r="P87">
-        <v>-24.18421430083066</v>
+        <v>-9.95169530083065</v>
       </c>
       <c r="Q87">
-        <v>52.21578569916934</v>
+        <v>66.44830469916936</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3926836452164417</v>
+        <v>0.3847956013448092</v>
       </c>
       <c r="T87">
-        <v>5.36472778835503</v>
+        <v>5.24415413928369</v>
       </c>
       <c r="U87">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V87">
-        <v>0.2102257428734396</v>
+        <v>0.2319423464920873</v>
       </c>
       <c r="W87">
-        <v>0.1417099671712334</v>
+        <v>0.1249099671712333</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8450,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8409029714937583</v>
+        <v>0.9277693859683492</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,13 +8592,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1806923286556822</v>
+        <v>0.1650611220749373</v>
       </c>
       <c r="C88">
-        <v>-245.2628177506202</v>
+        <v>-163.7454349752217</v>
       </c>
       <c r="D88">
-        <v>757.1911822493798</v>
+        <v>838.7085650247784</v>
       </c>
       <c r="E88">
         <v>151.5540000000001</v>
@@ -8494,37 +8625,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M88">
-        <v>205.06341066465</v>
+        <v>185.86346346465</v>
       </c>
       <c r="N88">
-        <v>-34.63007733131664</v>
+        <v>-15.43013013131664</v>
       </c>
       <c r="O88">
-        <v>-8.65751933282916</v>
+        <v>-3.857532532829161</v>
       </c>
       <c r="P88">
-        <v>-25.97255799848748</v>
+        <v>-11.57259759848748</v>
       </c>
       <c r="Q88">
-        <v>50.42744200151252</v>
+        <v>64.82740240151253</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4174610484461875</v>
+        <v>0.4090095728694385</v>
       </c>
       <c r="T88">
-        <v>5.74792263038039</v>
+        <v>5.618736577803954</v>
       </c>
       <c r="U88">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V88">
-        <v>0.2077812574911903</v>
+        <v>0.2292453424631095</v>
       </c>
       <c r="W88">
-        <v>0.1421485835735069</v>
+        <v>0.1253485835735069</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8532,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8311250299647612</v>
+        <v>0.9169813698524382</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,13 +8674,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1820286384333497</v>
+        <v>0.1662294318526049</v>
       </c>
       <c r="C89">
-        <v>-264.7972814547969</v>
+        <v>-183.7355205631895</v>
       </c>
       <c r="D89">
-        <v>750.9457185452031</v>
+        <v>832.0074794368105</v>
       </c>
       <c r="E89">
         <v>164.8430000000001</v>
@@ -8576,37 +8707,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M89">
-        <v>207.4478689281924</v>
+        <v>188.0246665281924</v>
       </c>
       <c r="N89">
-        <v>-37.0145355948591</v>
+        <v>-17.59133319485909</v>
       </c>
       <c r="O89">
-        <v>-9.253633898714774</v>
+        <v>-4.397833298714772</v>
       </c>
       <c r="P89">
-        <v>-27.76090169614432</v>
+        <v>-13.19349989614432</v>
       </c>
       <c r="Q89">
-        <v>48.63909830385568</v>
+        <v>63.20650010385569</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4460503598651249</v>
+        <v>0.4369487707824722</v>
       </c>
       <c r="T89">
-        <v>6.190070525025034</v>
+        <v>6.050947083788873</v>
       </c>
       <c r="U89">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V89">
-        <v>0.2053929671751996</v>
+        <v>0.226610338526752</v>
       </c>
       <c r="W89">
-        <v>0.142577116840096</v>
+        <v>0.125777116840096</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8614,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8215718687007983</v>
+        <v>0.9064413541070079</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,13 +8756,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1833649482110173</v>
+        <v>0.1673977416302725</v>
       </c>
       <c r="C90">
-        <v>-284.2295603422324</v>
+        <v>-203.6193746975069</v>
       </c>
       <c r="D90">
-        <v>744.8024396577676</v>
+        <v>825.4126253024931</v>
       </c>
       <c r="E90">
         <v>178.1320000000001</v>
@@ -8658,37 +8789,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M90">
-        <v>209.8323271917349</v>
+        <v>190.1858695917349</v>
       </c>
       <c r="N90">
-        <v>-39.39899385840152</v>
+        <v>-19.75253625840153</v>
       </c>
       <c r="O90">
-        <v>-9.849748464600381</v>
+        <v>-4.938134064600384</v>
       </c>
       <c r="P90">
-        <v>-29.54924539380114</v>
+        <v>-14.81440219380115</v>
       </c>
       <c r="Q90">
-        <v>46.85075460619886</v>
+        <v>61.58559780619886</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4794045565205521</v>
+        <v>0.4695445016810116</v>
       </c>
       <c r="T90">
-        <v>6.705909735443788</v>
+        <v>6.555192674104614</v>
       </c>
       <c r="U90">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V90">
-        <v>0.2030589561845723</v>
+        <v>0.2240352210434934</v>
       </c>
       <c r="W90">
-        <v>0.1429959107142626</v>
+        <v>0.1261959107142626</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8696,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8122358247382893</v>
+        <v>0.8961408841739736</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,13 +8838,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1847012579886849</v>
+        <v>0.16856605140794</v>
       </c>
       <c r="C91">
-        <v>-303.5621419005116</v>
+        <v>-223.399503623077</v>
       </c>
       <c r="D91">
-        <v>738.7588580994884</v>
+        <v>818.9214963769231</v>
       </c>
       <c r="E91">
         <v>191.421</v>
@@ -8740,37 +8871,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M91">
-        <v>212.2167854552773</v>
+        <v>192.3470726552773</v>
       </c>
       <c r="N91">
-        <v>-41.78345212194398</v>
+        <v>-21.91373932194395</v>
       </c>
       <c r="O91">
-        <v>-10.445863030486</v>
+        <v>-5.478434830485988</v>
       </c>
       <c r="P91">
-        <v>-31.33758909145799</v>
+        <v>-16.43530449145796</v>
       </c>
       <c r="Q91">
-        <v>45.06241090854202</v>
+        <v>59.96469550854204</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.518823152567875</v>
+        <v>0.508066729106558</v>
       </c>
       <c r="T91">
-        <v>7.315537893211405</v>
+        <v>7.151119280841397</v>
       </c>
       <c r="U91">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V91">
-        <v>0.2007773948791277</v>
+        <v>0.2215179713688475</v>
       </c>
       <c r="W91">
-        <v>0.1434052934901333</v>
+        <v>0.1266052934901333</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8778,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8031095795165107</v>
+        <v>0.8860718854753898</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,13 +8920,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2355687862437843</v>
+        <v>0.1697343611856076</v>
       </c>
       <c r="C92">
-        <v>-491.1884612948303</v>
+        <v>-243.0783353624903</v>
       </c>
       <c r="D92">
-        <v>564.42153870517</v>
+        <v>812.5316646375099</v>
       </c>
       <c r="E92">
         <v>204.7100000000003</v>
@@ -8822,45 +8953,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M92">
-        <v>277.0329657188198</v>
+        <v>194.5082757188198</v>
       </c>
       <c r="N92">
-        <v>-106.5996323854865</v>
+        <v>-24.07494238548642</v>
       </c>
       <c r="O92">
-        <v>-26.64990809637162</v>
+        <v>-6.018735596371606</v>
       </c>
       <c r="P92">
-        <v>-79.94972428911485</v>
+        <v>-18.05620678911482</v>
       </c>
       <c r="Q92">
-        <v>-3.549724289114849</v>
+        <v>58.34379321088519</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5916376525989805</v>
+        <v>0.5542934020172139</v>
       </c>
       <c r="T92">
-        <v>8.44165028593696</v>
+        <v>7.866231208925538</v>
       </c>
       <c r="U92">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1538023939597843</v>
+        <v>0.2190566605758602</v>
       </c>
       <c r="W92">
-        <v>0.1960055788709847</v>
+        <v>0.1270055788709847</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.6152095758391372</v>
+        <v>0.8762266423034408</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,13 +9002,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2374270960214518</v>
+        <v>0.1709026709632752</v>
       </c>
       <c r="C93">
-        <v>-509.3018317352435</v>
+        <v>-262.6582227441392</v>
       </c>
       <c r="D93">
-        <v>559.5971682647568</v>
+        <v>806.2407772558611</v>
       </c>
       <c r="E93">
         <v>217.9990000000003</v>
@@ -8904,45 +9035,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M93">
-        <v>280.1111097823622</v>
+        <v>196.6694787823622</v>
       </c>
       <c r="N93">
-        <v>-109.6777764490289</v>
+        <v>-26.23614544902887</v>
       </c>
       <c r="O93">
-        <v>-27.41944411225722</v>
+        <v>-6.559036362257217</v>
       </c>
       <c r="P93">
-        <v>-82.25833233677167</v>
+        <v>-19.67710908677165</v>
       </c>
       <c r="Q93">
-        <v>-5.858332336771667</v>
+        <v>56.72289091322835</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6522862806655338</v>
+        <v>0.6107926689080155</v>
       </c>
       <c r="T93">
-        <v>9.379611428818846</v>
+        <v>8.740256898806154</v>
       </c>
       <c r="U93">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.152112257762424</v>
+        <v>0.2166494445255761</v>
       </c>
       <c r="W93">
-        <v>0.1963970667709383</v>
+        <v>0.1273970667709383</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.6084490310496961</v>
+        <v>0.8665977781023042</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,13 +9084,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2392854057991194</v>
+        <v>0.1720709807409428</v>
       </c>
       <c r="C94">
-        <v>-527.3334289041325</v>
+        <v>-282.1414462907459</v>
       </c>
       <c r="D94">
-        <v>554.8545710958678</v>
+        <v>800.0465537092543</v>
       </c>
       <c r="E94">
         <v>231.2880000000002</v>
@@ -8986,45 +9117,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M94">
-        <v>283.1892538459047</v>
+        <v>198.8306818459046</v>
       </c>
       <c r="N94">
-        <v>-112.7559205125713</v>
+        <v>-28.39734851257131</v>
       </c>
       <c r="O94">
-        <v>-28.18898012814283</v>
+        <v>-7.099337128142828</v>
       </c>
       <c r="P94">
-        <v>-84.56694038442849</v>
+        <v>-21.29801138442848</v>
       </c>
       <c r="Q94">
-        <v>-8.166940384428486</v>
+        <v>55.10198861557152</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7280970657487258</v>
+        <v>0.6814167525215177</v>
       </c>
       <c r="T94">
-        <v>10.5520628574212</v>
+        <v>9.832789011156926</v>
       </c>
       <c r="U94">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.1504588636563107</v>
+        <v>0.2142945592589937</v>
       </c>
       <c r="W94">
-        <v>0.1967800440643711</v>
+        <v>0.1277800440643711</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.6018354546252429</v>
+        <v>0.8571782370359747</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,13 +9166,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.241143715576787</v>
+        <v>0.1732392905186104</v>
       </c>
       <c r="C95">
-        <v>-545.285314419567</v>
+        <v>-301.5302169757514</v>
       </c>
       <c r="D95">
-        <v>550.1916855804332</v>
+        <v>793.9467830242488</v>
       </c>
       <c r="E95">
         <v>244.5770000000002</v>
@@ -9068,45 +9199,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M95">
-        <v>286.2673979094471</v>
+        <v>200.9918849094471</v>
       </c>
       <c r="N95">
-        <v>-115.8340645761137</v>
+        <v>-30.55855157611376</v>
       </c>
       <c r="O95">
-        <v>-28.95851614402844</v>
+        <v>-7.639637894028439</v>
       </c>
       <c r="P95">
-        <v>-86.87554843208531</v>
+        <v>-22.91891368208532</v>
       </c>
       <c r="Q95">
-        <v>-10.4755484320853</v>
+        <v>53.48108631791469</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8255680751414008</v>
+        <v>0.7722191457388774</v>
       </c>
       <c r="T95">
-        <v>12.05950040848137</v>
+        <v>11.23747315560792</v>
       </c>
       <c r="U95">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1488410264126945</v>
+        <v>0.2119903166863163</v>
       </c>
       <c r="W95">
-        <v>0.1971547852869774</v>
+        <v>0.1281547852869774</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5953641056507779</v>
+        <v>0.8479612667452654</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,13 +9248,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2430020253544546</v>
+        <v>0.1744076002962779</v>
       </c>
       <c r="C96">
-        <v>-563.1594811754773</v>
+        <v>-320.826678854567</v>
       </c>
       <c r="D96">
-        <v>545.6065188245229</v>
+        <v>787.9393211454332</v>
       </c>
       <c r="E96">
         <v>257.8660000000002</v>
@@ -9150,45 +9281,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M96">
-        <v>289.3455419729896</v>
+        <v>203.1530879729895</v>
       </c>
       <c r="N96">
-        <v>-118.9122086396562</v>
+        <v>-32.7197546396562</v>
       </c>
       <c r="O96">
-        <v>-29.72805215991406</v>
+        <v>-8.17993865991405</v>
       </c>
       <c r="P96">
-        <v>-89.18415647974217</v>
+        <v>-24.53981597974215</v>
       </c>
       <c r="Q96">
-        <v>-12.78415647974217</v>
+        <v>51.86018402025785</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9555294209983013</v>
+        <v>0.8932890033620239</v>
       </c>
       <c r="T96">
-        <v>14.06941714322828</v>
+        <v>13.11038534820924</v>
       </c>
       <c r="U96">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.1472576112380913</v>
+        <v>0.2097351005513555</v>
       </c>
       <c r="W96">
-        <v>0.1975215532920814</v>
+        <v>0.1285215532920814</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5890304449523653</v>
+        <v>0.8389404022054221</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,13 +9330,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2448603351321222</v>
+        <v>0.1755759100739455</v>
       </c>
       <c r="C97">
-        <v>-580.9578561816381</v>
+        <v>-340.032911577264</v>
       </c>
       <c r="D97">
-        <v>541.097143818362</v>
+        <v>782.0220884227361</v>
       </c>
       <c r="E97">
         <v>271.1550000000002</v>
@@ -9232,45 +9363,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M97">
-        <v>292.423686036532</v>
+        <v>205.314291036532</v>
       </c>
       <c r="N97">
-        <v>-121.9903527031987</v>
+        <v>-34.88095770319865</v>
       </c>
       <c r="O97">
-        <v>-30.49758817579966</v>
+        <v>-8.720239425799662</v>
       </c>
       <c r="P97">
-        <v>-91.49276452739899</v>
+        <v>-26.16071827739898</v>
       </c>
       <c r="Q97">
-        <v>-15.09276452739898</v>
+        <v>50.23928172260102</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.137475305197962</v>
+        <v>1.062786804034429</v>
       </c>
       <c r="T97">
-        <v>16.88330057187394</v>
+        <v>15.73246241785109</v>
       </c>
       <c r="U97">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.1457075311197956</v>
+        <v>0.2075273626508149</v>
       </c>
       <c r="W97">
-        <v>0.1978805998654991</v>
+        <v>0.128880599865499</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5828301244791825</v>
+        <v>0.8301094506032597</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,13 +9412,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2467186449097897</v>
+        <v>0.1767442198516131</v>
       </c>
       <c r="C98">
-        <v>-598.6823032639768</v>
+        <v>-359.1509327888919</v>
       </c>
       <c r="D98">
-        <v>536.6616967360234</v>
+        <v>776.1930672111083</v>
       </c>
       <c r="E98">
         <v>284.4440000000002</v>
@@ -9314,45 +9445,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M98">
-        <v>295.5018301000744</v>
+        <v>207.4754941000744</v>
       </c>
       <c r="N98">
-        <v>-125.0684967667411</v>
+        <v>-37.04216076674106</v>
       </c>
       <c r="O98">
-        <v>-31.26712419168527</v>
+        <v>-9.260540191685266</v>
       </c>
       <c r="P98">
-        <v>-93.80137257505581</v>
+        <v>-27.7816205750558</v>
       </c>
       <c r="Q98">
-        <v>-17.4013725750558</v>
+        <v>48.61837942494421</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.41039413149745</v>
+        <v>1.317033505043034</v>
       </c>
       <c r="T98">
-        <v>21.10412571484238</v>
+        <v>19.66557802231382</v>
       </c>
       <c r="U98">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.1441897443372978</v>
+        <v>0.205365619289869</v>
       </c>
       <c r="W98">
-        <v>0.1982321663019705</v>
+        <v>0.1292321663019705</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5767589773491911</v>
+        <v>0.8214624771594758</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,13 +9494,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2485769546874573</v>
+        <v>0.1779125296292806</v>
       </c>
       <c r="C99">
-        <v>-616.3346256331515</v>
+        <v>-378.1827004232379</v>
       </c>
       <c r="D99">
-        <v>532.2983743668486</v>
+        <v>770.4502995767623</v>
       </c>
       <c r="E99">
         <v>297.7330000000002</v>
@@ -9396,45 +9527,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M99">
-        <v>298.5799741636168</v>
+        <v>209.6366971636168</v>
       </c>
       <c r="N99">
-        <v>-128.1466408302835</v>
+        <v>-39.20336383028351</v>
       </c>
       <c r="O99">
-        <v>-32.03666020757088</v>
+        <v>-9.800840957570877</v>
       </c>
       <c r="P99">
-        <v>-96.10998062271263</v>
+        <v>-29.40252287271263</v>
       </c>
       <c r="Q99">
-        <v>-19.70998062271262</v>
+        <v>46.99747712728738</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.865258841996599</v>
+        <v>1.740778006724045</v>
       </c>
       <c r="T99">
-        <v>28.1388342864565</v>
+        <v>26.22077069641844</v>
       </c>
       <c r="U99">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.1427032521276349</v>
+        <v>0.2032484479569837</v>
       </c>
       <c r="W99">
-        <v>0.1985764839459374</v>
+        <v>0.1295764839459374</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5708130085105396</v>
+        <v>0.8129937918279349</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,13 +9576,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2504352644651249</v>
+        <v>0.1790808394069482</v>
       </c>
       <c r="C100">
-        <v>-633.9165683288358</v>
+        <v>-397.1301148955151</v>
       </c>
       <c r="D100">
-        <v>528.0054316711644</v>
+        <v>764.791885104485</v>
       </c>
       <c r="E100">
         <v>311.0220000000002</v>
@@ -9478,45 +9609,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M100">
-        <v>301.6581182271593</v>
+        <v>211.7979002271593</v>
       </c>
       <c r="N100">
-        <v>-131.224784893826</v>
+        <v>-41.36456689382595</v>
       </c>
       <c r="O100">
-        <v>-32.8061962234565</v>
+        <v>-10.34114172345649</v>
       </c>
       <c r="P100">
-        <v>-98.41858867036949</v>
+        <v>-31.02342517036946</v>
       </c>
       <c r="Q100">
-        <v>-22.01858867036948</v>
+        <v>45.37657482963054</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.774988262994899</v>
+        <v>2.588267010086066</v>
       </c>
       <c r="T100">
-        <v>42.20825142968475</v>
+        <v>39.33115604462764</v>
       </c>
       <c r="U100">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V100">
-        <v>0.1412470964936794</v>
+        <v>0.2011744842023206</v>
       </c>
       <c r="W100">
-        <v>0.1989137746992111</v>
+        <v>0.1299137746992111</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5649883859747178</v>
+        <v>0.8046979368092825</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9527,13 +9658,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2522935742427925</v>
+        <v>0.2368217513873206</v>
       </c>
       <c r="C101">
-        <v>-651.4298205466746</v>
+        <v>-614.0911447212956</v>
       </c>
       <c r="D101">
-        <v>523.7811794533255</v>
+        <v>561.1198552787046</v>
       </c>
       <c r="E101">
         <v>324.3110000000001</v>
@@ -9560,37 +9691,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M101">
-        <v>304.7362622907017</v>
+        <v>285.0020972907017</v>
       </c>
       <c r="N101">
-        <v>-134.3029289573684</v>
+        <v>-114.5687639573684</v>
       </c>
       <c r="O101">
-        <v>-33.5757322393421</v>
+        <v>-28.6421909893421</v>
       </c>
       <c r="P101">
-        <v>-100.7271967180263</v>
+        <v>-85.92657296802629</v>
       </c>
       <c r="Q101">
-        <v>-24.3271967180263</v>
+        <v>-9.526572968026287</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.504176525989798</v>
+        <v>5.441994240442613</v>
       </c>
       <c r="T101">
-        <v>84.4165028593695</v>
+        <v>83.47740870422729</v>
       </c>
       <c r="U101">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V101">
-        <v>0.1398203581452584</v>
+        <v>0.1495018238054329</v>
       </c>
       <c r="W101">
-        <v>0.1992442514978732</v>
+        <v>0.1842442514978731</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9598,7 +9729,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.5592814325810338</v>
+        <v>0.5980072952217316</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/spain/spain_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_publishing_newspapers.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1091361190641455</v>
+        <v>0.1090157610997358</v>
       </c>
       <c r="C2">
-        <v>1505.345349482586</v>
+        <v>1493.901964184944</v>
       </c>
       <c r="D2">
-        <v>1364.945349482586</v>
+        <v>1366.790964184944</v>
       </c>
       <c r="E2">
-        <v>-991.3</v>
+        <v>-978.011</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.289</v>
       </c>
       <c r="G2">
         <v>140.4</v>
@@ -1573,28 +1573,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8788145635424416</v>
       </c>
       <c r="N2">
-        <v>170.4333333333333</v>
+        <v>169.5545187697909</v>
       </c>
       <c r="O2">
-        <v>42.60833333333333</v>
+        <v>42.38862969244772</v>
       </c>
       <c r="P2">
-        <v>127.825</v>
+        <v>127.1658890773432</v>
       </c>
       <c r="Q2">
-        <v>204.225</v>
+        <v>203.5658890773432</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1091361190641455</v>
+        <v>0.1096159381479648</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226994</v>
+        <v>0.987212267248629</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>193.9354903795952</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1090157610997358</v>
+        <v>0.1088954031353261</v>
       </c>
       <c r="C3">
-        <v>1493.901964184944</v>
+        <v>1482.463576751423</v>
       </c>
       <c r="D3">
-        <v>1366.790964184944</v>
+        <v>1368.641576751423</v>
       </c>
       <c r="E3">
-        <v>-978.011</v>
+        <v>-964.722</v>
       </c>
       <c r="F3">
-        <v>13.289</v>
+        <v>26.578</v>
       </c>
       <c r="G3">
         <v>140.4</v>
@@ -1655,28 +1655,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M3">
-        <v>0.8788145635424416</v>
+        <v>1.757629127084883</v>
       </c>
       <c r="N3">
-        <v>169.5545187697909</v>
+        <v>168.6757042062484</v>
       </c>
       <c r="O3">
-        <v>42.38862969244772</v>
+        <v>42.16892605156211</v>
       </c>
       <c r="P3">
-        <v>127.1658890773432</v>
+        <v>126.5067781546863</v>
       </c>
       <c r="Q3">
-        <v>203.5658890773432</v>
+        <v>202.9067781546863</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1096159381479648</v>
+        <v>0.1101055494579845</v>
       </c>
       <c r="T3">
-        <v>0.987212267248629</v>
+        <v>0.9947863984995775</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>193.9354903795952</v>
+        <v>96.9677451897976</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1088954031353261</v>
+        <v>0.1087750451709165</v>
       </c>
       <c r="C4">
-        <v>1482.463576751423</v>
+        <v>1471.030207510627</v>
       </c>
       <c r="D4">
-        <v>1368.641576751423</v>
+        <v>1370.497207510627</v>
       </c>
       <c r="E4">
-        <v>-964.722</v>
+        <v>-951.433</v>
       </c>
       <c r="F4">
-        <v>26.578</v>
+        <v>39.867</v>
       </c>
       <c r="G4">
         <v>140.4</v>
@@ -1737,28 +1737,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M4">
-        <v>1.757629127084883</v>
+        <v>2.636443690627325</v>
       </c>
       <c r="N4">
-        <v>168.6757042062484</v>
+        <v>167.796889642706</v>
       </c>
       <c r="O4">
-        <v>42.16892605156211</v>
+        <v>41.94922241067651</v>
       </c>
       <c r="P4">
-        <v>126.5067781546863</v>
+        <v>125.8476672320295</v>
       </c>
       <c r="Q4">
-        <v>202.9067781546863</v>
+        <v>202.2476672320295</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1101055494579845</v>
+        <v>0.1106052558465613</v>
       </c>
       <c r="T4">
-        <v>0.9947863984995775</v>
+        <v>1.002516697405185</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.9677451897976</v>
+        <v>64.64516345986507</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1087750451709165</v>
+        <v>0.1086546872065068</v>
       </c>
       <c r="C5">
-        <v>1471.030207510627</v>
+        <v>1459.601876901557</v>
       </c>
       <c r="D5">
-        <v>1370.497207510627</v>
+        <v>1372.357876901557</v>
       </c>
       <c r="E5">
-        <v>-951.433</v>
+        <v>-938.144</v>
       </c>
       <c r="F5">
-        <v>39.867</v>
+        <v>53.15600000000001</v>
       </c>
       <c r="G5">
         <v>140.4</v>
@@ -1819,28 +1819,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M5">
-        <v>2.636443690627325</v>
+        <v>3.515258254169766</v>
       </c>
       <c r="N5">
-        <v>167.796889642706</v>
+        <v>166.9180750791636</v>
       </c>
       <c r="O5">
-        <v>41.94922241067651</v>
+        <v>41.72951876979089</v>
       </c>
       <c r="P5">
-        <v>125.8476672320295</v>
+        <v>125.1885563093727</v>
       </c>
       <c r="Q5">
-        <v>202.2476672320295</v>
+        <v>201.5885563093727</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1106052558465613</v>
+        <v>0.1111153727849001</v>
       </c>
       <c r="T5">
-        <v>1.002516697405185</v>
+        <v>1.010408044204659</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.64516345986507</v>
+        <v>48.4838725948988</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1086546872065068</v>
+        <v>0.1085343292420971</v>
       </c>
       <c r="C6">
-        <v>1459.601876901557</v>
+        <v>1448.17860547436</v>
       </c>
       <c r="D6">
-        <v>1372.357876901557</v>
+        <v>1374.223605474359</v>
       </c>
       <c r="E6">
-        <v>-938.144</v>
+        <v>-924.8549999999999</v>
       </c>
       <c r="F6">
-        <v>53.15600000000001</v>
+        <v>66.44500000000001</v>
       </c>
       <c r="G6">
         <v>140.4</v>
@@ -1901,28 +1901,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M6">
-        <v>3.515258254169766</v>
+        <v>4.394072817712208</v>
       </c>
       <c r="N6">
-        <v>166.9180750791636</v>
+        <v>166.0392605156211</v>
       </c>
       <c r="O6">
-        <v>41.72951876979089</v>
+        <v>41.50981512890528</v>
       </c>
       <c r="P6">
-        <v>125.1885563093727</v>
+        <v>124.5294453867158</v>
       </c>
       <c r="Q6">
-        <v>201.5885563093727</v>
+        <v>200.9294453867159</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1111153727849001</v>
+        <v>0.1116362290272039</v>
       </c>
       <c r="T6">
-        <v>1.010408044204659</v>
+        <v>1.018465524620964</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.4838725948988</v>
+        <v>38.78709807591904</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1085343292420971</v>
+        <v>0.1084139712776874</v>
       </c>
       <c r="C7">
-        <v>1448.17860547436</v>
+        <v>1436.760413891088</v>
       </c>
       <c r="D7">
-        <v>1374.223605474359</v>
+        <v>1376.094413891087</v>
       </c>
       <c r="E7">
-        <v>-924.8549999999999</v>
+        <v>-911.5659999999999</v>
       </c>
       <c r="F7">
-        <v>66.44500000000001</v>
+        <v>79.73400000000001</v>
       </c>
       <c r="G7">
         <v>140.4</v>
@@ -1983,28 +1983,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M7">
-        <v>4.394072817712208</v>
+        <v>5.27288738125465</v>
       </c>
       <c r="N7">
-        <v>166.0392605156211</v>
+        <v>165.1604459520787</v>
       </c>
       <c r="O7">
-        <v>41.50981512890528</v>
+        <v>41.29011148801967</v>
       </c>
       <c r="P7">
-        <v>124.5294453867158</v>
+        <v>123.870334464059</v>
       </c>
       <c r="Q7">
-        <v>200.9294453867159</v>
+        <v>200.270334464059</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1116362290272039</v>
+        <v>0.1121681673172163</v>
       </c>
       <c r="T7">
-        <v>1.018465524620964</v>
+        <v>1.026694440790807</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.78709807591904</v>
+        <v>32.32258172993253</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1084139712776874</v>
+        <v>0.1082936133132777</v>
       </c>
       <c r="C8">
-        <v>1436.760413891088</v>
+        <v>1425.347322926461</v>
       </c>
       <c r="D8">
-        <v>1376.094413891088</v>
+        <v>1377.970322926461</v>
       </c>
       <c r="E8">
-        <v>-911.5659999999999</v>
+        <v>-898.2769999999999</v>
       </c>
       <c r="F8">
-        <v>79.73400000000001</v>
+        <v>93.023</v>
       </c>
       <c r="G8">
         <v>140.4</v>
@@ -2065,28 +2065,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M8">
-        <v>5.27288738125465</v>
+        <v>6.15170194479709</v>
       </c>
       <c r="N8">
-        <v>165.1604459520787</v>
+        <v>164.2816313885363</v>
       </c>
       <c r="O8">
-        <v>41.29011148801967</v>
+        <v>41.07040784713406</v>
       </c>
       <c r="P8">
-        <v>123.870334464059</v>
+        <v>123.2112235414022</v>
       </c>
       <c r="Q8">
-        <v>200.270334464059</v>
+        <v>199.6112235414022</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1121681673172163</v>
+        <v>0.1127115451403473</v>
       </c>
       <c r="T8">
-        <v>1.026694440790807</v>
+        <v>1.035100322899787</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.32258172993253</v>
+        <v>27.70507005422789</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1082936133132777</v>
+        <v>0.108173255348868</v>
       </c>
       <c r="C9">
-        <v>1425.347322926461</v>
+        <v>1413.939353468635</v>
       </c>
       <c r="D9">
-        <v>1377.970322926461</v>
+        <v>1379.851353468635</v>
       </c>
       <c r="E9">
-        <v>-898.2769999999999</v>
+        <v>-884.9879999999999</v>
       </c>
       <c r="F9">
-        <v>93.02300000000001</v>
+        <v>106.312</v>
       </c>
       <c r="G9">
         <v>140.4</v>
@@ -2147,28 +2147,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M9">
-        <v>6.151701944797091</v>
+        <v>7.030516508339533</v>
       </c>
       <c r="N9">
-        <v>164.2816313885363</v>
+        <v>163.4028168249938</v>
       </c>
       <c r="O9">
-        <v>41.07040784713406</v>
+        <v>40.85070420624845</v>
       </c>
       <c r="P9">
-        <v>123.2112235414022</v>
+        <v>122.5521126187454</v>
       </c>
       <c r="Q9">
-        <v>199.6112235414022</v>
+        <v>198.9521126187454</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1127115451403473</v>
+        <v>0.1132667355248506</v>
       </c>
       <c r="T9">
-        <v>1.035100322899787</v>
+        <v>1.043688941576354</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.70507005422789</v>
+        <v>24.2419362974494</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.108173255348868</v>
+        <v>0.1080528973844583</v>
       </c>
       <c r="C10">
-        <v>1413.939353468635</v>
+        <v>1402.536526519976</v>
       </c>
       <c r="D10">
-        <v>1379.851353468635</v>
+        <v>1381.737526519976</v>
       </c>
       <c r="E10">
-        <v>-884.9879999999999</v>
+        <v>-871.699</v>
       </c>
       <c r="F10">
-        <v>106.312</v>
+        <v>119.601</v>
       </c>
       <c r="G10">
         <v>140.4</v>
@@ -2229,28 +2229,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M10">
-        <v>7.030516508339533</v>
+        <v>7.909331071881973</v>
       </c>
       <c r="N10">
-        <v>163.4028168249938</v>
+        <v>162.5240022614514</v>
       </c>
       <c r="O10">
-        <v>40.85070420624845</v>
+        <v>40.63100056536284</v>
       </c>
       <c r="P10">
-        <v>122.5521126187454</v>
+        <v>121.8930016960885</v>
       </c>
       <c r="Q10">
-        <v>198.9521126187454</v>
+        <v>198.2930016960885</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1132667355248506</v>
+        <v>0.1138341278958266</v>
       </c>
       <c r="T10">
-        <v>1.043688941576354</v>
+        <v>1.052466321102955</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.2419362974494</v>
+        <v>21.54838781995502</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1080528973844583</v>
+        <v>0.1079325394200487</v>
       </c>
       <c r="C11">
-        <v>1402.536526519976</v>
+        <v>1391.138863197844</v>
       </c>
       <c r="D11">
-        <v>1381.737526519976</v>
+        <v>1383.628863197844</v>
       </c>
       <c r="E11">
-        <v>-871.699</v>
+        <v>-858.41</v>
       </c>
       <c r="F11">
-        <v>119.601</v>
+        <v>132.89</v>
       </c>
       <c r="G11">
         <v>140.4</v>
@@ -2311,28 +2311,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M11">
-        <v>7.909331071881973</v>
+        <v>8.788145635424414</v>
       </c>
       <c r="N11">
-        <v>162.5240022614514</v>
+        <v>161.6451876979089</v>
       </c>
       <c r="O11">
-        <v>40.63100056536284</v>
+        <v>40.41129692447723</v>
       </c>
       <c r="P11">
-        <v>121.8930016960885</v>
+        <v>121.2338907734317</v>
       </c>
       <c r="Q11">
-        <v>198.2930016960885</v>
+        <v>197.6338907734317</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1138341278958266</v>
+        <v>0.1144141289861576</v>
       </c>
       <c r="T11">
-        <v>1.052466321102955</v>
+        <v>1.061438753507924</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.54838781995502</v>
+        <v>19.39354903795952</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1079325394200487</v>
+        <v>0.107812181455639</v>
       </c>
       <c r="C12">
-        <v>1391.138863197844</v>
+        <v>1379.746384735381</v>
       </c>
       <c r="D12">
-        <v>1383.628863197844</v>
+        <v>1385.525384735381</v>
       </c>
       <c r="E12">
-        <v>-858.41</v>
+        <v>-845.121</v>
       </c>
       <c r="F12">
-        <v>132.89</v>
+        <v>146.179</v>
       </c>
       <c r="G12">
         <v>140.4</v>
@@ -2393,28 +2393,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M12">
-        <v>8.788145635424415</v>
+        <v>9.666960198966857</v>
       </c>
       <c r="N12">
-        <v>161.6451876979089</v>
+        <v>160.7663731343665</v>
       </c>
       <c r="O12">
-        <v>40.41129692447723</v>
+        <v>40.19159328359162</v>
       </c>
       <c r="P12">
-        <v>121.2338907734317</v>
+        <v>120.5747798507749</v>
       </c>
       <c r="Q12">
-        <v>197.6338907734317</v>
+        <v>196.9747798507749</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1144141289861576</v>
+        <v>0.1150071638088556</v>
       </c>
       <c r="T12">
-        <v>1.061438753507924</v>
+        <v>1.070612813607388</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.39354903795952</v>
+        <v>17.63049912541775</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.107812181455639</v>
+        <v>0.1076918234912293</v>
       </c>
       <c r="C13">
-        <v>1379.746384735381</v>
+        <v>1368.359112482302</v>
       </c>
       <c r="D13">
-        <v>1385.525384735381</v>
+        <v>1387.427112482302</v>
       </c>
       <c r="E13">
-        <v>-845.121</v>
+        <v>-831.8319999999999</v>
       </c>
       <c r="F13">
-        <v>146.179</v>
+        <v>159.468</v>
       </c>
       <c r="G13">
         <v>140.4</v>
@@ -2475,28 +2475,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M13">
-        <v>9.666960198966857</v>
+        <v>10.5457747625093</v>
       </c>
       <c r="N13">
-        <v>160.7663731343665</v>
+        <v>159.887558570824</v>
       </c>
       <c r="O13">
-        <v>40.19159328359162</v>
+        <v>39.97188964270601</v>
       </c>
       <c r="P13">
-        <v>120.5747798507749</v>
+        <v>119.915668928118</v>
       </c>
       <c r="Q13">
-        <v>196.9747798507749</v>
+        <v>196.315668928118</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1150071638088556</v>
+        <v>0.1156136766957058</v>
       </c>
       <c r="T13">
-        <v>1.070612813607388</v>
+        <v>1.079995375072748</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.63049912541775</v>
+        <v>16.16129086496627</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1076918234912293</v>
+        <v>0.1075714655268196</v>
       </c>
       <c r="C14">
-        <v>1368.359112482302</v>
+        <v>1356.977067905702</v>
       </c>
       <c r="D14">
-        <v>1387.427112482302</v>
+        <v>1389.334067905702</v>
       </c>
       <c r="E14">
-        <v>-831.8319999999999</v>
+        <v>-818.5429999999999</v>
       </c>
       <c r="F14">
-        <v>159.468</v>
+        <v>172.757</v>
       </c>
       <c r="G14">
         <v>140.4</v>
@@ -2557,28 +2557,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M14">
-        <v>10.5457747625093</v>
+        <v>11.42458932605174</v>
       </c>
       <c r="N14">
-        <v>159.887558570824</v>
+        <v>159.0087440072816</v>
       </c>
       <c r="O14">
-        <v>39.97188964270601</v>
+        <v>39.7521860018204</v>
       </c>
       <c r="P14">
-        <v>119.915668928118</v>
+        <v>119.2565580054612</v>
       </c>
       <c r="Q14">
-        <v>196.315668928118</v>
+        <v>195.6565580054612</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1156136766957058</v>
+        <v>0.1162341324075411</v>
       </c>
       <c r="T14">
-        <v>1.079995375072748</v>
+        <v>1.089593627606278</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.16129086496627</v>
+        <v>14.91811464458425</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1075714655268196</v>
+        <v>0.10745110756241</v>
       </c>
       <c r="C15">
-        <v>1356.977067905702</v>
+        <v>1345.600272590859</v>
       </c>
       <c r="D15">
-        <v>1389.334067905702</v>
+        <v>1391.246272590859</v>
       </c>
       <c r="E15">
-        <v>-818.5429999999999</v>
+        <v>-805.2539999999999</v>
       </c>
       <c r="F15">
-        <v>172.757</v>
+        <v>186.046</v>
       </c>
       <c r="G15">
         <v>140.4</v>
@@ -2639,28 +2639,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M15">
-        <v>11.42458932605174</v>
+        <v>12.30340388959418</v>
       </c>
       <c r="N15">
-        <v>159.0087440072816</v>
+        <v>158.1299294437391</v>
       </c>
       <c r="O15">
-        <v>39.7521860018204</v>
+        <v>39.53248236093479</v>
       </c>
       <c r="P15">
-        <v>119.2565580054612</v>
+        <v>118.5974470828044</v>
       </c>
       <c r="Q15">
-        <v>195.6565580054612</v>
+        <v>194.9974470828044</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1162341324075411</v>
+        <v>0.1168690173219772</v>
       </c>
       <c r="T15">
-        <v>1.089593627606278</v>
+        <v>1.099415095315006</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.91811464458425</v>
+        <v>13.85253502711394</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.10745110756241</v>
+        <v>0.1073307495980003</v>
       </c>
       <c r="C16">
-        <v>1345.600272590859</v>
+        <v>1334.22874824205</v>
       </c>
       <c r="D16">
-        <v>1391.246272590859</v>
+        <v>1393.16374824205</v>
       </c>
       <c r="E16">
-        <v>-805.2539999999999</v>
+        <v>-791.9649999999999</v>
       </c>
       <c r="F16">
-        <v>186.046</v>
+        <v>199.335</v>
       </c>
       <c r="G16">
         <v>140.4</v>
@@ -2721,28 +2721,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M16">
-        <v>12.30340388959418</v>
+        <v>13.18221845313663</v>
       </c>
       <c r="N16">
-        <v>158.1299294437391</v>
+        <v>157.2511148801967</v>
       </c>
       <c r="O16">
-        <v>39.53248236093479</v>
+        <v>39.31277872004918</v>
       </c>
       <c r="P16">
-        <v>118.5974470828044</v>
+        <v>117.9383361601475</v>
       </c>
       <c r="Q16">
-        <v>194.9974470828044</v>
+        <v>194.3383361601475</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1168690173219772</v>
+        <v>0.1175188407049883</v>
       </c>
       <c r="T16">
-        <v>1.099415095315006</v>
+        <v>1.109467656381586</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.85253502711394</v>
+        <v>12.92903269197301</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1073307495980003</v>
+        <v>0.1073903916335906</v>
       </c>
       <c r="C17">
-        <v>1334.22874824205</v>
+        <v>1319.988904565624</v>
       </c>
       <c r="D17">
-        <v>1393.16374824205</v>
+        <v>1392.212904565624</v>
       </c>
       <c r="E17">
-        <v>-791.9649999999999</v>
+        <v>-778.6759999999999</v>
       </c>
       <c r="F17">
-        <v>199.335</v>
+        <v>212.624</v>
       </c>
       <c r="G17">
         <v>140.4</v>
@@ -2803,45 +2803,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M17">
-        <v>13.18221845313662</v>
+        <v>14.37996901667907</v>
       </c>
       <c r="N17">
-        <v>157.2511148801967</v>
+        <v>156.0533643166543</v>
       </c>
       <c r="O17">
-        <v>39.31277872004918</v>
+        <v>39.01334107916357</v>
       </c>
       <c r="P17">
-        <v>117.9383361601475</v>
+        <v>117.0400232374907</v>
       </c>
       <c r="Q17">
-        <v>194.3383361601475</v>
+        <v>193.4400232374907</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1175188407049883</v>
+        <v>0.1181841360733091</v>
       </c>
       <c r="T17">
-        <v>1.109467656381586</v>
+        <v>1.119759564140228</v>
       </c>
       <c r="U17">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04959823332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>12.92903269197302</v>
+        <v>11.85213494797178</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1073903916335906</v>
+        <v>0.1072812836691809</v>
       </c>
       <c r="C18">
-        <v>1319.988904565624</v>
+        <v>1308.440345109423</v>
       </c>
       <c r="D18">
-        <v>1392.212904565624</v>
+        <v>1393.953345109423</v>
       </c>
       <c r="E18">
-        <v>-778.6759999999999</v>
+        <v>-765.3869999999999</v>
       </c>
       <c r="F18">
-        <v>212.624</v>
+        <v>225.913</v>
       </c>
       <c r="G18">
         <v>140.4</v>
@@ -2885,28 +2885,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M18">
-        <v>14.37996901667907</v>
+        <v>15.27871708022151</v>
       </c>
       <c r="N18">
-        <v>156.0533643166543</v>
+        <v>155.1546162531118</v>
       </c>
       <c r="O18">
-        <v>39.01334107916357</v>
+        <v>38.78865406327796</v>
       </c>
       <c r="P18">
-        <v>117.0400232374907</v>
+        <v>116.3659621898339</v>
       </c>
       <c r="Q18">
-        <v>193.4400232374907</v>
+        <v>192.7659621898339</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1181841360733091</v>
+        <v>0.1188654626553245</v>
       </c>
       <c r="T18">
-        <v>1.119759564140228</v>
+        <v>1.130299469676187</v>
       </c>
       <c r="U18">
         <v>0.06763097776675758</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.85213494797178</v>
+        <v>11.15495053926756</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1072812836691809</v>
+        <v>0.1071721757047712</v>
       </c>
       <c r="C19">
-        <v>1308.440345109423</v>
+        <v>1296.896142637434</v>
       </c>
       <c r="D19">
-        <v>1393.953345109423</v>
+        <v>1395.698142637434</v>
       </c>
       <c r="E19">
-        <v>-765.3869999999999</v>
+        <v>-752.098</v>
       </c>
       <c r="F19">
-        <v>225.913</v>
+        <v>239.2020000000001</v>
       </c>
       <c r="G19">
         <v>140.4</v>
@@ -2967,28 +2967,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M19">
-        <v>15.27871708022151</v>
+        <v>16.17746514376395</v>
       </c>
       <c r="N19">
-        <v>155.1546162531118</v>
+        <v>154.2558681895694</v>
       </c>
       <c r="O19">
-        <v>38.78865406327796</v>
+        <v>38.56396704739235</v>
       </c>
       <c r="P19">
-        <v>116.3659621898339</v>
+        <v>115.691901142177</v>
       </c>
       <c r="Q19">
-        <v>192.7659621898339</v>
+        <v>192.0919011421771</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1188654626553245</v>
+        <v>0.1195634069588524</v>
       </c>
       <c r="T19">
-        <v>1.130299469676187</v>
+        <v>1.141096446078876</v>
       </c>
       <c r="U19">
         <v>0.06763097776675758</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.15495053926756</v>
+        <v>10.5352310648638</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1071721757047712</v>
+        <v>0.1070630677403615</v>
       </c>
       <c r="C20">
-        <v>1296.896142637434</v>
+        <v>1285.356313530943</v>
       </c>
       <c r="D20">
-        <v>1395.698142637434</v>
+        <v>1397.447313530943</v>
       </c>
       <c r="E20">
-        <v>-752.098</v>
+        <v>-738.809</v>
       </c>
       <c r="F20">
-        <v>239.202</v>
+        <v>252.491</v>
       </c>
       <c r="G20">
         <v>140.4</v>
@@ -3049,28 +3049,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M20">
-        <v>16.17746514376395</v>
+        <v>17.07621320730639</v>
       </c>
       <c r="N20">
-        <v>154.2558681895694</v>
+        <v>153.357120126027</v>
       </c>
       <c r="O20">
-        <v>38.56396704739235</v>
+        <v>38.33928003150674</v>
       </c>
       <c r="P20">
-        <v>115.691901142177</v>
+        <v>115.0178400945202</v>
       </c>
       <c r="Q20">
-        <v>192.0919011421771</v>
+        <v>191.4178400945202</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1195634069588524</v>
+        <v>0.12027858445506</v>
       </c>
       <c r="T20">
-        <v>1.141096446078876</v>
+        <v>1.152160014491508</v>
       </c>
       <c r="U20">
         <v>0.06763097776675758</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.5352310648638</v>
+        <v>9.980745219344659</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1070630677403615</v>
+        <v>0.1072089597759519</v>
       </c>
       <c r="C21">
-        <v>1285.356313530943</v>
+        <v>1269.729423149773</v>
       </c>
       <c r="D21">
-        <v>1397.447313530943</v>
+        <v>1395.109423149773</v>
       </c>
       <c r="E21">
-        <v>-738.809</v>
+        <v>-725.52</v>
       </c>
       <c r="F21">
-        <v>252.491</v>
+        <v>265.78</v>
       </c>
       <c r="G21">
         <v>140.4</v>
@@ -3131,45 +3131,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M21">
-        <v>17.07621320730639</v>
+        <v>18.42678727084883</v>
       </c>
       <c r="N21">
-        <v>153.357120126027</v>
+        <v>152.0065460624845</v>
       </c>
       <c r="O21">
-        <v>38.33928003150674</v>
+        <v>38.00163651562113</v>
       </c>
       <c r="P21">
-        <v>115.0178400945202</v>
+        <v>114.0049095468634</v>
       </c>
       <c r="Q21">
-        <v>191.4178400945202</v>
+        <v>190.4049095468634</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.12027858445506</v>
+        <v>0.1210116413886728</v>
       </c>
       <c r="T21">
-        <v>1.152160014491508</v>
+        <v>1.163500172114456</v>
       </c>
       <c r="U21">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.05072323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.980745219344659</v>
+        <v>9.249215874053032</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1072089597759519</v>
+        <v>0.1071126018115422</v>
       </c>
       <c r="C22">
-        <v>1269.729423149773</v>
+        <v>1257.983661998125</v>
       </c>
       <c r="D22">
-        <v>1395.109423149773</v>
+        <v>1396.652661998125</v>
       </c>
       <c r="E22">
-        <v>-725.52</v>
+        <v>-712.2309999999999</v>
       </c>
       <c r="F22">
-        <v>265.78</v>
+        <v>279.0690000000001</v>
       </c>
       <c r="G22">
         <v>140.4</v>
@@ -3213,28 +3213,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M22">
-        <v>18.42678727084883</v>
+        <v>19.34812663439127</v>
       </c>
       <c r="N22">
-        <v>152.0065460624845</v>
+        <v>151.0852066989421</v>
       </c>
       <c r="O22">
-        <v>38.00163651562113</v>
+        <v>37.77130167473552</v>
       </c>
       <c r="P22">
-        <v>114.0049095468634</v>
+        <v>113.3139050242065</v>
       </c>
       <c r="Q22">
-        <v>190.4049095468634</v>
+        <v>189.7139050242066</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1210116413886728</v>
+        <v>0.1217632567256682</v>
       </c>
       <c r="T22">
-        <v>1.163500172114456</v>
+        <v>1.175127422335453</v>
       </c>
       <c r="U22">
         <v>0.06933097776675758</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.249215874053032</v>
+        <v>8.808777022907648</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1071126018115422</v>
+        <v>0.1070162438471325</v>
       </c>
       <c r="C23">
-        <v>1257.983661998125</v>
+        <v>1246.241318819976</v>
       </c>
       <c r="D23">
-        <v>1396.652661998125</v>
+        <v>1398.199318819976</v>
       </c>
       <c r="E23">
-        <v>-712.231</v>
+        <v>-698.942</v>
       </c>
       <c r="F23">
-        <v>279.069</v>
+        <v>292.358</v>
       </c>
       <c r="G23">
         <v>140.4</v>
@@ -3295,28 +3295,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M23">
-        <v>19.34812663439127</v>
+        <v>20.26946599793371</v>
       </c>
       <c r="N23">
-        <v>151.0852066989421</v>
+        <v>150.1638673353996</v>
       </c>
       <c r="O23">
-        <v>37.77130167473552</v>
+        <v>37.54096683384991</v>
       </c>
       <c r="P23">
-        <v>113.3139050242065</v>
+        <v>112.6229005015497</v>
       </c>
       <c r="Q23">
-        <v>189.7139050242066</v>
+        <v>189.0229005015497</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1217632567256682</v>
+        <v>0.1225341442507916</v>
       </c>
       <c r="T23">
-        <v>1.175127422335453</v>
+        <v>1.187052807177501</v>
       </c>
       <c r="U23">
         <v>0.06933097776675758</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.80877702290765</v>
+        <v>8.408378067320939</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1070162438471325</v>
+        <v>0.1069198858827228</v>
       </c>
       <c r="C24">
-        <v>1246.241318819976</v>
+        <v>1234.502404983132</v>
       </c>
       <c r="D24">
-        <v>1398.199318819976</v>
+        <v>1399.749404983132</v>
       </c>
       <c r="E24">
-        <v>-698.942</v>
+        <v>-685.6529999999999</v>
       </c>
       <c r="F24">
-        <v>292.358</v>
+        <v>305.647</v>
       </c>
       <c r="G24">
         <v>140.4</v>
@@ -3377,28 +3377,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M24">
-        <v>20.26946599793371</v>
+        <v>21.19080536147615</v>
       </c>
       <c r="N24">
-        <v>150.1638673353996</v>
+        <v>149.2425279718572</v>
       </c>
       <c r="O24">
-        <v>37.54096683384991</v>
+        <v>37.3106319929643</v>
       </c>
       <c r="P24">
-        <v>112.6229005015497</v>
+        <v>111.9318959788929</v>
       </c>
       <c r="Q24">
-        <v>189.0229005015497</v>
+        <v>188.3318959788929</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1225341442507916</v>
+        <v>0.1233250548285157</v>
       </c>
       <c r="T24">
-        <v>1.187052807177501</v>
+        <v>1.199287942275187</v>
       </c>
       <c r="U24">
         <v>0.06933097776675758</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.408378067320939</v>
+        <v>8.042796412220028</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1069198858827228</v>
+        <v>0.1068235279183131</v>
       </c>
       <c r="C25">
-        <v>1234.502404983132</v>
+        <v>1222.766931905867</v>
       </c>
       <c r="D25">
-        <v>1399.749404983132</v>
+        <v>1401.302931905867</v>
       </c>
       <c r="E25">
-        <v>-685.6529999999999</v>
+        <v>-672.3639999999999</v>
       </c>
       <c r="F25">
-        <v>305.647</v>
+        <v>318.936</v>
       </c>
       <c r="G25">
         <v>140.4</v>
@@ -3459,28 +3459,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M25">
-        <v>21.19080536147615</v>
+        <v>22.1121447250186</v>
       </c>
       <c r="N25">
-        <v>149.2425279718572</v>
+        <v>148.3211886083147</v>
       </c>
       <c r="O25">
-        <v>37.3106319929643</v>
+        <v>37.08029715207869</v>
       </c>
       <c r="P25">
-        <v>111.9318959788929</v>
+        <v>111.2408914562361</v>
       </c>
       <c r="Q25">
-        <v>188.3318959788929</v>
+        <v>187.6408914562361</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1233250548285157</v>
+        <v>0.1241367788424957</v>
       </c>
       <c r="T25">
-        <v>1.199287942275187</v>
+        <v>1.211845054612286</v>
       </c>
       <c r="U25">
         <v>0.06933097776675758</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.042796412220028</v>
+        <v>7.707679895044193</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1068235279183131</v>
+        <v>0.1068771699539035</v>
       </c>
       <c r="C26">
-        <v>1222.766931905867</v>
+        <v>1208.612665368707</v>
       </c>
       <c r="D26">
-        <v>1401.302931905867</v>
+        <v>1400.437665368707</v>
       </c>
       <c r="E26">
-        <v>-672.3639999999999</v>
+        <v>-659.0749999999999</v>
       </c>
       <c r="F26">
-        <v>318.936</v>
+        <v>332.225</v>
       </c>
       <c r="G26">
         <v>140.4</v>
@@ -3541,45 +3541,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M26">
-        <v>22.1121447250186</v>
+        <v>23.29926408856104</v>
       </c>
       <c r="N26">
-        <v>148.3211886083147</v>
+        <v>147.1340692447723</v>
       </c>
       <c r="O26">
-        <v>37.08029715207869</v>
+        <v>36.78351731119307</v>
       </c>
       <c r="P26">
-        <v>111.2408914562361</v>
+        <v>110.3505519335792</v>
       </c>
       <c r="Q26">
-        <v>187.6408914562361</v>
+        <v>186.7505519335792</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1241367788424957</v>
+        <v>0.1249701488301819</v>
       </c>
       <c r="T26">
-        <v>1.211845054612286</v>
+        <v>1.224737023278374</v>
       </c>
       <c r="U26">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.05199823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.707679895044193</v>
+        <v>7.31496637342331</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1068771699539035</v>
+        <v>0.1067868119894938</v>
       </c>
       <c r="C27">
-        <v>1208.612665368707</v>
+        <v>1196.781790509176</v>
       </c>
       <c r="D27">
-        <v>1400.437665368707</v>
+        <v>1401.895790509176</v>
       </c>
       <c r="E27">
-        <v>-659.0749999999999</v>
+        <v>-645.7859999999999</v>
       </c>
       <c r="F27">
-        <v>332.225</v>
+        <v>345.514</v>
       </c>
       <c r="G27">
         <v>140.4</v>
@@ -3623,28 +3623,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M27">
-        <v>23.29926408856104</v>
+        <v>24.23123465210348</v>
       </c>
       <c r="N27">
-        <v>147.1340692447723</v>
+        <v>146.2020986812299</v>
       </c>
       <c r="O27">
-        <v>36.78351731119307</v>
+        <v>36.55052467030747</v>
       </c>
       <c r="P27">
-        <v>110.3505519335792</v>
+        <v>109.6515740109224</v>
       </c>
       <c r="Q27">
-        <v>186.7505519335792</v>
+        <v>186.0515740109224</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1249701488301819</v>
+        <v>0.1258260423310487</v>
       </c>
       <c r="T27">
-        <v>1.224737023278374</v>
+        <v>1.237977423530032</v>
       </c>
       <c r="U27">
         <v>0.07013097776675759</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.31496637342331</v>
+        <v>7.033621512907031</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1067868119894938</v>
+        <v>0.1066964540250841</v>
       </c>
       <c r="C28">
-        <v>1196.781790509176</v>
+        <v>1184.953955192203</v>
       </c>
       <c r="D28">
-        <v>1401.895790509176</v>
+        <v>1403.356955192203</v>
       </c>
       <c r="E28">
-        <v>-645.7859999999999</v>
+        <v>-632.4969999999998</v>
       </c>
       <c r="F28">
-        <v>345.514</v>
+        <v>358.8030000000001</v>
       </c>
       <c r="G28">
         <v>140.4</v>
@@ -3705,28 +3705,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M28">
-        <v>24.23123465210348</v>
+        <v>25.16320521564592</v>
       </c>
       <c r="N28">
-        <v>146.2020986812299</v>
+        <v>145.2701281176874</v>
       </c>
       <c r="O28">
-        <v>36.55052467030747</v>
+        <v>36.31753202942186</v>
       </c>
       <c r="P28">
-        <v>109.6515740109224</v>
+        <v>108.9525960882656</v>
       </c>
       <c r="Q28">
-        <v>186.0515740109224</v>
+        <v>185.3525960882656</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1258260423310487</v>
+        <v>0.1267053849689256</v>
       </c>
       <c r="T28">
-        <v>1.237977423530032</v>
+        <v>1.251580574473517</v>
       </c>
       <c r="U28">
         <v>0.07013097776675759</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.033621512907031</v>
+        <v>6.773117012428992</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1066964540250841</v>
+        <v>0.1066060960606744</v>
       </c>
       <c r="C29">
-        <v>1184.953955192203</v>
+        <v>1173.129168931848</v>
       </c>
       <c r="D29">
-        <v>1403.356955192203</v>
+        <v>1404.821168931848</v>
       </c>
       <c r="E29">
-        <v>-632.4969999999998</v>
+        <v>-619.2079999999999</v>
       </c>
       <c r="F29">
-        <v>358.8030000000001</v>
+        <v>372.092</v>
       </c>
       <c r="G29">
         <v>140.4</v>
@@ -3787,28 +3787,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M29">
-        <v>25.16320521564592</v>
+        <v>26.09517577918837</v>
       </c>
       <c r="N29">
-        <v>145.2701281176874</v>
+        <v>144.338157554145</v>
       </c>
       <c r="O29">
-        <v>36.31753202942186</v>
+        <v>36.08453938853624</v>
       </c>
       <c r="P29">
-        <v>108.9525960882656</v>
+        <v>108.2536181656087</v>
       </c>
       <c r="Q29">
-        <v>185.3525960882656</v>
+        <v>184.6536181656087</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1267053849689256</v>
+        <v>0.1276091537911879</v>
       </c>
       <c r="T29">
-        <v>1.251580574473517</v>
+        <v>1.265561590720987</v>
       </c>
       <c r="U29">
         <v>0.07013097776675759</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.773117012428992</v>
+        <v>6.531219976270813</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1066060960606744</v>
+        <v>0.1065157380962647</v>
       </c>
       <c r="C30">
-        <v>1173.129168931848</v>
+        <v>1161.307441281914</v>
       </c>
       <c r="D30">
-        <v>1404.821168931848</v>
+        <v>1406.288441281914</v>
       </c>
       <c r="E30">
-        <v>-619.2079999999999</v>
+        <v>-605.9189999999999</v>
       </c>
       <c r="F30">
-        <v>372.092</v>
+        <v>385.3810000000001</v>
       </c>
       <c r="G30">
         <v>140.4</v>
@@ -3869,28 +3869,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M30">
-        <v>26.09517577918837</v>
+        <v>27.02714634273081</v>
       </c>
       <c r="N30">
-        <v>144.338157554145</v>
+        <v>143.4061869906025</v>
       </c>
       <c r="O30">
-        <v>36.08453938853624</v>
+        <v>35.85154674765063</v>
       </c>
       <c r="P30">
-        <v>108.2536181656087</v>
+        <v>107.5546402429519</v>
       </c>
       <c r="Q30">
-        <v>184.6536181656087</v>
+        <v>183.9546402429519</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1276091537911879</v>
+        <v>0.1285383808901337</v>
       </c>
       <c r="T30">
-        <v>1.265561590720987</v>
+        <v>1.279936438412048</v>
       </c>
       <c r="U30">
         <v>0.07013097776675759</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.531219976270813</v>
+        <v>6.30600549433044</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1065157380962647</v>
+        <v>0.106425380131855</v>
       </c>
       <c r="C31">
-        <v>1161.307441281914</v>
+        <v>1149.488781836166</v>
       </c>
       <c r="D31">
-        <v>1406.288441281914</v>
+        <v>1407.758781836166</v>
       </c>
       <c r="E31">
-        <v>-605.919</v>
+        <v>-592.6299999999999</v>
       </c>
       <c r="F31">
-        <v>385.381</v>
+        <v>398.67</v>
       </c>
       <c r="G31">
         <v>140.4</v>
@@ -3951,28 +3951,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M31">
-        <v>27.0271463427308</v>
+        <v>27.95911690627325</v>
       </c>
       <c r="N31">
-        <v>143.4061869906025</v>
+        <v>142.4742164270601</v>
       </c>
       <c r="O31">
-        <v>35.85154674765063</v>
+        <v>35.61855410676502</v>
       </c>
       <c r="P31">
-        <v>107.5546402429519</v>
+        <v>106.8556623202951</v>
       </c>
       <c r="Q31">
-        <v>183.9546402429519</v>
+        <v>183.2556623202951</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1285383808901337</v>
+        <v>0.1294941573347637</v>
       </c>
       <c r="T31">
-        <v>1.279936438412048</v>
+        <v>1.294721996037139</v>
       </c>
       <c r="U31">
         <v>0.07013097776675759</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.306005494330441</v>
+        <v>6.095805311186093</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.106425380131855</v>
+        <v>0.1065675221674454</v>
       </c>
       <c r="C32">
-        <v>1149.488781836166</v>
+        <v>1133.888174056536</v>
       </c>
       <c r="D32">
-        <v>1407.758781836166</v>
+        <v>1405.447174056536</v>
       </c>
       <c r="E32">
-        <v>-592.6299999999999</v>
+        <v>-579.3409999999999</v>
       </c>
       <c r="F32">
-        <v>398.67</v>
+        <v>411.959</v>
       </c>
       <c r="G32">
         <v>140.4</v>
@@ -4033,45 +4033,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M32">
-        <v>27.95911690627325</v>
+        <v>29.30304646981569</v>
       </c>
       <c r="N32">
-        <v>142.4742164270601</v>
+        <v>141.1302868635177</v>
       </c>
       <c r="O32">
-        <v>35.61855410676502</v>
+        <v>35.28257171587941</v>
       </c>
       <c r="P32">
-        <v>106.8556623202951</v>
+        <v>105.8477151476382</v>
       </c>
       <c r="Q32">
-        <v>183.2556623202951</v>
+        <v>182.2477151476382</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1294941573347637</v>
+        <v>0.1304776374444554</v>
       </c>
       <c r="T32">
-        <v>1.294721996037139</v>
+        <v>1.309936120549913</v>
       </c>
       <c r="U32">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.05259823332506819</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.095805311186093</v>
+        <v>5.81623257188949</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1065675221674454</v>
+        <v>0.1064846642030357</v>
       </c>
       <c r="C33">
-        <v>1133.888174056536</v>
+        <v>1121.945741340763</v>
       </c>
       <c r="D33">
-        <v>1405.447174056536</v>
+        <v>1406.793741340763</v>
       </c>
       <c r="E33">
-        <v>-579.3409999999999</v>
+        <v>-566.0519999999999</v>
       </c>
       <c r="F33">
-        <v>411.959</v>
+        <v>425.248</v>
       </c>
       <c r="G33">
         <v>140.4</v>
@@ -4115,28 +4115,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M33">
-        <v>29.30304646981569</v>
+        <v>30.24830603335813</v>
       </c>
       <c r="N33">
-        <v>141.1302868635177</v>
+        <v>140.1850272999752</v>
       </c>
       <c r="O33">
-        <v>35.28257171587941</v>
+        <v>35.0462568249938</v>
       </c>
       <c r="P33">
-        <v>105.8477151476382</v>
+        <v>105.1387704749814</v>
       </c>
       <c r="Q33">
-        <v>182.2477151476382</v>
+        <v>181.5387704749814</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1304776374444554</v>
+        <v>0.1314900434397263</v>
       </c>
       <c r="T33">
-        <v>1.309936120549913</v>
+        <v>1.325597719313064</v>
       </c>
       <c r="U33">
         <v>0.07113097776675759</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.81623257188949</v>
+        <v>5.634475304017943</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1064846642030357</v>
+        <v>0.106401806238626</v>
       </c>
       <c r="C34">
-        <v>1121.945741340763</v>
+        <v>1110.005891407794</v>
       </c>
       <c r="D34">
-        <v>1406.793741340763</v>
+        <v>1408.142891407794</v>
       </c>
       <c r="E34">
-        <v>-566.0519999999999</v>
+        <v>-552.7629999999999</v>
       </c>
       <c r="F34">
-        <v>425.248</v>
+        <v>438.537</v>
       </c>
       <c r="G34">
         <v>140.4</v>
@@ -4197,28 +4197,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M34">
-        <v>30.24830603335813</v>
+        <v>31.19356559690057</v>
       </c>
       <c r="N34">
-        <v>140.1850272999752</v>
+        <v>139.2397677364328</v>
       </c>
       <c r="O34">
-        <v>35.0462568249938</v>
+        <v>34.80994193410819</v>
       </c>
       <c r="P34">
-        <v>105.1387704749814</v>
+        <v>104.4298258023246</v>
       </c>
       <c r="Q34">
-        <v>181.5387704749814</v>
+        <v>180.8298258023246</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1314900434397263</v>
+        <v>0.1325326705094828</v>
       </c>
       <c r="T34">
-        <v>1.325597719313064</v>
+        <v>1.341726828487055</v>
       </c>
       <c r="U34">
         <v>0.07113097776675759</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.634475304017943</v>
+        <v>5.463733628138611</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.106401806238626</v>
+        <v>0.1063189482742163</v>
       </c>
       <c r="C35">
-        <v>1110.005891407794</v>
+        <v>1098.06863169562</v>
       </c>
       <c r="D35">
-        <v>1408.142891407794</v>
+        <v>1409.49463169562</v>
       </c>
       <c r="E35">
-        <v>-552.7629999999999</v>
+        <v>-539.4739999999999</v>
       </c>
       <c r="F35">
-        <v>438.537</v>
+        <v>451.8260000000001</v>
       </c>
       <c r="G35">
         <v>140.4</v>
@@ -4279,28 +4279,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M35">
-        <v>31.19356559690057</v>
+        <v>32.13882516044302</v>
       </c>
       <c r="N35">
-        <v>139.2397677364328</v>
+        <v>138.2945081728903</v>
       </c>
       <c r="O35">
-        <v>34.80994193410819</v>
+        <v>34.57362704322258</v>
       </c>
       <c r="P35">
-        <v>104.4298258023246</v>
+        <v>103.7208811296677</v>
       </c>
       <c r="Q35">
-        <v>180.8298258023246</v>
+        <v>180.1208811296677</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1325326705094828</v>
+        <v>0.133606892338929</v>
       </c>
       <c r="T35">
-        <v>1.341726828487055</v>
+        <v>1.358344698545106</v>
       </c>
       <c r="U35">
         <v>0.07113097776675759</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.463733628138611</v>
+        <v>5.303035580252181</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1063189482742163</v>
+        <v>0.1062360903098066</v>
       </c>
       <c r="C36">
-        <v>1098.06863169562</v>
+        <v>1086.133969670821</v>
       </c>
       <c r="D36">
-        <v>1409.49463169562</v>
+        <v>1410.84896967082</v>
       </c>
       <c r="E36">
-        <v>-539.4739999999999</v>
+        <v>-526.1849999999999</v>
       </c>
       <c r="F36">
-        <v>451.8260000000001</v>
+        <v>465.1150000000001</v>
       </c>
       <c r="G36">
         <v>140.4</v>
@@ -4361,28 +4361,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M36">
-        <v>32.13882516044302</v>
+        <v>33.08408472398546</v>
       </c>
       <c r="N36">
-        <v>138.2945081728903</v>
+        <v>137.3492486093479</v>
       </c>
       <c r="O36">
-        <v>34.57362704322258</v>
+        <v>34.33731215233697</v>
       </c>
       <c r="P36">
-        <v>103.7208811296677</v>
+        <v>103.0119364570109</v>
       </c>
       <c r="Q36">
-        <v>180.1208811296677</v>
+        <v>179.4119364570109</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.133606892338929</v>
+        <v>0.1347141671477427</v>
       </c>
       <c r="T36">
-        <v>1.358344698545106</v>
+        <v>1.375473887681867</v>
       </c>
       <c r="U36">
         <v>0.07113097776675759</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.303035580252181</v>
+        <v>5.151520277959261</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1062360903098066</v>
+        <v>0.1061532323453969</v>
       </c>
       <c r="C37">
-        <v>1086.133969670821</v>
+        <v>1074.2019128287</v>
       </c>
       <c r="D37">
-        <v>1410.84896967082</v>
+        <v>1412.2059128287</v>
       </c>
       <c r="E37">
-        <v>-526.1849999999999</v>
+        <v>-512.8959999999998</v>
       </c>
       <c r="F37">
-        <v>465.1150000000001</v>
+        <v>478.4040000000001</v>
       </c>
       <c r="G37">
         <v>140.4</v>
@@ -4443,28 +4443,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M37">
-        <v>33.08408472398546</v>
+        <v>34.02934428752791</v>
       </c>
       <c r="N37">
-        <v>137.3492486093479</v>
+        <v>136.4039890458054</v>
       </c>
       <c r="O37">
-        <v>34.33731215233697</v>
+        <v>34.10099726145135</v>
       </c>
       <c r="P37">
-        <v>103.0119364570109</v>
+        <v>102.3029917843541</v>
       </c>
       <c r="Q37">
-        <v>179.4119364570109</v>
+        <v>178.7029917843541</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1347141671477427</v>
+        <v>0.1358560442943319</v>
       </c>
       <c r="T37">
-        <v>1.375473887681867</v>
+        <v>1.393138363979151</v>
       </c>
       <c r="U37">
         <v>0.07113097776675759</v>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.151520277959261</v>
+        <v>5.008422492460392</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1061532323453969</v>
+        <v>0.1060703743809873</v>
       </c>
       <c r="C38">
-        <v>1074.2019128287</v>
+        <v>1062.272468693425</v>
       </c>
       <c r="D38">
-        <v>1412.205912828699</v>
+        <v>1413.565468693424</v>
       </c>
       <c r="E38">
-        <v>-512.896</v>
+        <v>-499.6069999999999</v>
       </c>
       <c r="F38">
-        <v>478.404</v>
+        <v>491.693</v>
       </c>
       <c r="G38">
         <v>140.4</v>
@@ -4525,28 +4525,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M38">
-        <v>34.0293442875279</v>
+        <v>34.97460385107034</v>
       </c>
       <c r="N38">
-        <v>136.4039890458054</v>
+        <v>135.458729482263</v>
       </c>
       <c r="O38">
-        <v>34.10099726145136</v>
+        <v>33.86468237056575</v>
       </c>
       <c r="P38">
-        <v>102.3029917843541</v>
+        <v>101.5940471116972</v>
       </c>
       <c r="Q38">
-        <v>178.7029917843541</v>
+        <v>177.9940471116972</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1358560442943319</v>
+        <v>0.1370341715090667</v>
       </c>
       <c r="T38">
-        <v>1.393138363979151</v>
+        <v>1.411363617301746</v>
       </c>
       <c r="U38">
         <v>0.07113097776675759</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.008422492460394</v>
+        <v>4.873059722393895</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1060703743809873</v>
+        <v>0.1059875164165776</v>
       </c>
       <c r="C39">
-        <v>1062.272468693425</v>
+        <v>1050.345644818166</v>
       </c>
       <c r="D39">
-        <v>1413.565468693424</v>
+        <v>1414.927644818166</v>
       </c>
       <c r="E39">
-        <v>-499.6069999999999</v>
+        <v>-486.3179999999999</v>
       </c>
       <c r="F39">
-        <v>491.693</v>
+        <v>504.982</v>
       </c>
       <c r="G39">
         <v>140.4</v>
@@ -4607,28 +4607,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M39">
-        <v>34.97460385107034</v>
+        <v>35.91986341461278</v>
       </c>
       <c r="N39">
-        <v>135.458729482263</v>
+        <v>134.5134699187205</v>
       </c>
       <c r="O39">
-        <v>33.86468237056575</v>
+        <v>33.62836747968014</v>
       </c>
       <c r="P39">
-        <v>101.5940471116972</v>
+        <v>100.8851024390404</v>
       </c>
       <c r="Q39">
-        <v>177.9940471116972</v>
+        <v>177.2851024390404</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1370341715090667</v>
+        <v>0.1382503028275027</v>
       </c>
       <c r="T39">
-        <v>1.411363617301746</v>
+        <v>1.430176782021844</v>
       </c>
       <c r="U39">
         <v>0.07113097776675759</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.873059722393895</v>
+        <v>4.744821308646689</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1059875164165776</v>
+        <v>0.1059046584521679</v>
       </c>
       <c r="C40">
-        <v>1050.345644818166</v>
+        <v>1038.421448785237</v>
       </c>
       <c r="D40">
-        <v>1414.927644818166</v>
+        <v>1416.292448785237</v>
       </c>
       <c r="E40">
-        <v>-486.3179999999999</v>
+        <v>-473.0289999999999</v>
       </c>
       <c r="F40">
-        <v>504.982</v>
+        <v>518.2710000000001</v>
       </c>
       <c r="G40">
         <v>140.4</v>
@@ -4689,28 +4689,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M40">
-        <v>35.91986341461278</v>
+        <v>36.86512297815523</v>
       </c>
       <c r="N40">
-        <v>134.5134699187205</v>
+        <v>133.5682103551781</v>
       </c>
       <c r="O40">
-        <v>33.62836747968014</v>
+        <v>33.39205258879453</v>
       </c>
       <c r="P40">
-        <v>100.8851024390404</v>
+        <v>100.1761577663836</v>
       </c>
       <c r="Q40">
-        <v>177.2851024390404</v>
+        <v>176.5761577663836</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1382503028275027</v>
+        <v>0.1395063073039202</v>
       </c>
       <c r="T40">
-        <v>1.430176782021844</v>
+        <v>1.449606771814732</v>
       </c>
       <c r="U40">
         <v>0.07113097776675759</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.744821308646689</v>
+        <v>4.623159223809594</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1059046584521679</v>
+        <v>0.1058218004877582</v>
       </c>
       <c r="C41">
-        <v>1038.421448785237</v>
+        <v>1026.499888206233</v>
       </c>
       <c r="D41">
-        <v>1416.292448785237</v>
+        <v>1417.659888206233</v>
       </c>
       <c r="E41">
-        <v>-473.0289999999999</v>
+        <v>-459.7399999999999</v>
       </c>
       <c r="F41">
-        <v>518.2710000000001</v>
+        <v>531.5600000000001</v>
       </c>
       <c r="G41">
         <v>140.4</v>
@@ -4771,28 +4771,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M41">
-        <v>36.86512297815523</v>
+        <v>37.81038254169766</v>
       </c>
       <c r="N41">
-        <v>133.5682103551781</v>
+        <v>132.6229507916357</v>
       </c>
       <c r="O41">
-        <v>33.39205258879453</v>
+        <v>33.15573769790892</v>
       </c>
       <c r="P41">
-        <v>100.1761577663836</v>
+        <v>99.46721309372676</v>
       </c>
       <c r="Q41">
-        <v>176.5761577663836</v>
+        <v>175.8672130937268</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1395063073039202</v>
+        <v>0.1408041785962182</v>
       </c>
       <c r="T41">
-        <v>1.449606771814732</v>
+        <v>1.469684427934049</v>
       </c>
       <c r="U41">
         <v>0.07113097776675759</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.623159223809594</v>
+        <v>4.507580243214354</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1058218004877582</v>
+        <v>0.1065076925233485</v>
       </c>
       <c r="C42">
-        <v>1026.499888206233</v>
+        <v>1001.970237451435</v>
       </c>
       <c r="D42">
-        <v>1417.659888206233</v>
+        <v>1406.419237451435</v>
       </c>
       <c r="E42">
-        <v>-459.7399999999999</v>
+        <v>-446.4509999999999</v>
       </c>
       <c r="F42">
-        <v>531.5600000000001</v>
+        <v>544.849</v>
       </c>
       <c r="G42">
         <v>140.4</v>
@@ -4853,45 +4853,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M42">
-        <v>37.81038254169766</v>
+        <v>40.1177646052401</v>
       </c>
       <c r="N42">
-        <v>132.6229507916357</v>
+        <v>130.3155687280932</v>
       </c>
       <c r="O42">
-        <v>33.15573769790892</v>
+        <v>32.57889218202331</v>
       </c>
       <c r="P42">
-        <v>99.46721309372676</v>
+        <v>97.73667654606993</v>
       </c>
       <c r="Q42">
-        <v>175.8672130937268</v>
+        <v>174.1366765460699</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1408041785962182</v>
+        <v>0.1421460455255434</v>
       </c>
       <c r="T42">
-        <v>1.469684427934049</v>
+        <v>1.490442682565886</v>
       </c>
       <c r="U42">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.05334823332506819</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.507580243214354</v>
+        <v>4.248325773143194</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1065076925233485</v>
+        <v>0.1064435845589388</v>
       </c>
       <c r="C43">
-        <v>1001.970237451435</v>
+        <v>989.7243049244289</v>
       </c>
       <c r="D43">
-        <v>1406.419237451435</v>
+        <v>1407.462304924429</v>
       </c>
       <c r="E43">
-        <v>-446.4509999999999</v>
+        <v>-433.1619999999998</v>
       </c>
       <c r="F43">
-        <v>544.849</v>
+        <v>558.1380000000001</v>
       </c>
       <c r="G43">
         <v>140.4</v>
@@ -4935,28 +4935,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M43">
-        <v>40.1177646052401</v>
+        <v>41.09624666878255</v>
       </c>
       <c r="N43">
-        <v>130.3155687280932</v>
+        <v>129.3370866645508</v>
       </c>
       <c r="O43">
-        <v>32.57889218202331</v>
+        <v>32.3342716661377</v>
       </c>
       <c r="P43">
-        <v>97.73667654606993</v>
+        <v>97.00281499841309</v>
       </c>
       <c r="Q43">
-        <v>174.1366765460699</v>
+        <v>173.4028149984131</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1421460455255434</v>
+        <v>0.1435341837282935</v>
       </c>
       <c r="T43">
-        <v>1.490442682565886</v>
+        <v>1.511916739081579</v>
       </c>
       <c r="U43">
         <v>0.07363097776675757</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.248325773143194</v>
+        <v>4.147175159496927</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1064435845589389</v>
+        <v>0.1063794765945292</v>
       </c>
       <c r="C44">
-        <v>989.7243049244286</v>
+        <v>977.4799207227408</v>
       </c>
       <c r="D44">
-        <v>1407.462304924429</v>
+        <v>1408.506920722741</v>
       </c>
       <c r="E44">
-        <v>-433.1619999999999</v>
+        <v>-419.8729999999999</v>
       </c>
       <c r="F44">
-        <v>558.138</v>
+        <v>571.427</v>
       </c>
       <c r="G44">
         <v>140.4</v>
@@ -5017,28 +5017,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M44">
-        <v>41.09624666878254</v>
+        <v>42.07472873232499</v>
       </c>
       <c r="N44">
-        <v>129.3370866645508</v>
+        <v>128.3586046010084</v>
       </c>
       <c r="O44">
-        <v>32.3342716661377</v>
+        <v>32.08965115025209</v>
       </c>
       <c r="P44">
-        <v>97.00281499841309</v>
+        <v>96.26895345075627</v>
       </c>
       <c r="Q44">
-        <v>173.4028149984131</v>
+        <v>172.6689534507563</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1435341837282935</v>
+        <v>0.1449710285346489</v>
       </c>
       <c r="T44">
-        <v>1.511916739081579</v>
+        <v>1.53414427126449</v>
       </c>
       <c r="U44">
         <v>0.07363097776675757</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.147175159496928</v>
+        <v>4.050729225555139</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1063794765945292</v>
+        <v>0.1074703686301195</v>
       </c>
       <c r="C45">
-        <v>977.4799207227408</v>
+        <v>946.6239058730747</v>
       </c>
       <c r="D45">
-        <v>1408.506920722741</v>
+        <v>1390.939905873075</v>
       </c>
       <c r="E45">
-        <v>-419.8729999999999</v>
+        <v>-406.5839999999999</v>
       </c>
       <c r="F45">
-        <v>571.427</v>
+        <v>584.716</v>
       </c>
       <c r="G45">
         <v>140.4</v>
@@ -5099,45 +5099,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M45">
-        <v>42.07472873232499</v>
+        <v>45.09971679586742</v>
       </c>
       <c r="N45">
-        <v>128.3586046010084</v>
+        <v>125.3336165374659</v>
       </c>
       <c r="O45">
-        <v>32.08965115025209</v>
+        <v>31.33340413436648</v>
       </c>
       <c r="P45">
-        <v>96.26895345075627</v>
+        <v>94.00021240309944</v>
       </c>
       <c r="Q45">
-        <v>172.6689534507563</v>
+        <v>170.4002124030994</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1449710285346489</v>
+        <v>0.1464591892269455</v>
       </c>
       <c r="T45">
-        <v>1.53414427126449</v>
+        <v>1.557165643882505</v>
       </c>
       <c r="U45">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05522323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.050729225555139</v>
+        <v>3.779033338607361</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1074703686301195</v>
+        <v>0.1074325106657098</v>
       </c>
       <c r="C46">
-        <v>946.6239058730747</v>
+        <v>933.937203085286</v>
       </c>
       <c r="D46">
-        <v>1390.939905873075</v>
+        <v>1391.542203085286</v>
       </c>
       <c r="E46">
-        <v>-406.5839999999999</v>
+        <v>-393.2949999999998</v>
       </c>
       <c r="F46">
-        <v>584.716</v>
+        <v>598.0050000000001</v>
       </c>
       <c r="G46">
         <v>140.4</v>
@@ -5181,28 +5181,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M46">
-        <v>45.09971679586742</v>
+        <v>46.12471035940987</v>
       </c>
       <c r="N46">
-        <v>125.3336165374659</v>
+        <v>124.3086229739235</v>
       </c>
       <c r="O46">
-        <v>31.33340413436648</v>
+        <v>31.07715574348087</v>
       </c>
       <c r="P46">
-        <v>94.00021240309944</v>
+        <v>93.2314672304426</v>
       </c>
       <c r="Q46">
-        <v>170.4002124030994</v>
+        <v>169.6314672304426</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1464591892269455</v>
+        <v>0.1480014648535075</v>
       </c>
       <c r="T46">
-        <v>1.557165643882505</v>
+        <v>1.581024157322992</v>
       </c>
       <c r="U46">
         <v>0.07713097776675758</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.779033338607361</v>
+        <v>3.695054819971641</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1074325106657098</v>
+        <v>0.1073946527013002</v>
       </c>
       <c r="C47">
-        <v>933.937203085286</v>
+        <v>921.2510221303671</v>
       </c>
       <c r="D47">
-        <v>1391.542203085286</v>
+        <v>1392.145022130367</v>
       </c>
       <c r="E47">
-        <v>-393.2949999999998</v>
+        <v>-380.0059999999999</v>
       </c>
       <c r="F47">
-        <v>598.0050000000001</v>
+        <v>611.2940000000001</v>
       </c>
       <c r="G47">
         <v>140.4</v>
@@ -5263,28 +5263,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M47">
-        <v>46.12471035940987</v>
+        <v>47.14970392295231</v>
       </c>
       <c r="N47">
-        <v>124.3086229739235</v>
+        <v>123.283629410381</v>
       </c>
       <c r="O47">
-        <v>31.07715574348087</v>
+        <v>30.82090735259526</v>
       </c>
       <c r="P47">
-        <v>93.2314672304426</v>
+        <v>92.46272205778577</v>
       </c>
       <c r="Q47">
-        <v>169.6314672304426</v>
+        <v>168.8627220577858</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1480014648535075</v>
+        <v>0.1496008617995718</v>
       </c>
       <c r="T47">
-        <v>1.581024157322992</v>
+        <v>1.605766319409424</v>
       </c>
       <c r="U47">
         <v>0.07713097776675758</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.695054819971641</v>
+        <v>3.614727541276606</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1073946527013002</v>
+        <v>0.1073567947368905</v>
       </c>
       <c r="C48">
-        <v>921.2510221303671</v>
+        <v>908.5653636867887</v>
       </c>
       <c r="D48">
-        <v>1392.145022130367</v>
+        <v>1392.748363686789</v>
       </c>
       <c r="E48">
-        <v>-380.0059999999999</v>
+        <v>-366.7169999999999</v>
       </c>
       <c r="F48">
-        <v>611.2940000000001</v>
+        <v>624.5830000000001</v>
       </c>
       <c r="G48">
         <v>140.4</v>
@@ -5345,28 +5345,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M48">
-        <v>47.14970392295231</v>
+        <v>48.17469748649476</v>
       </c>
       <c r="N48">
-        <v>123.283629410381</v>
+        <v>122.2586358468386</v>
       </c>
       <c r="O48">
-        <v>30.82090735259526</v>
+        <v>30.56465896170965</v>
       </c>
       <c r="P48">
-        <v>92.46272205778577</v>
+        <v>91.69397688512893</v>
       </c>
       <c r="Q48">
-        <v>168.8627220577858</v>
+        <v>168.0939768851289</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1496008617995718</v>
+        <v>0.1512606133473743</v>
       </c>
       <c r="T48">
-        <v>1.605766319409424</v>
+        <v>1.631442147989683</v>
       </c>
       <c r="U48">
         <v>0.07713097776675758</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.614727541276606</v>
+        <v>3.537818444653699</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1073567947368905</v>
+        <v>0.1083269367724808</v>
       </c>
       <c r="C49">
-        <v>908.5653636867887</v>
+        <v>879.9784289738579</v>
       </c>
       <c r="D49">
-        <v>1392.748363686789</v>
+        <v>1377.450428973858</v>
       </c>
       <c r="E49">
-        <v>-366.7169999999999</v>
+        <v>-353.4279999999999</v>
       </c>
       <c r="F49">
-        <v>624.5830000000001</v>
+        <v>637.8720000000001</v>
       </c>
       <c r="G49">
         <v>140.4</v>
@@ -5427,45 +5427,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M49">
-        <v>48.17469748649476</v>
+        <v>50.9857326500372</v>
       </c>
       <c r="N49">
-        <v>122.2586358468386</v>
+        <v>119.4476006832961</v>
       </c>
       <c r="O49">
-        <v>30.56465896170965</v>
+        <v>29.86190017082404</v>
       </c>
       <c r="P49">
-        <v>91.69397688512893</v>
+        <v>89.5857005124721</v>
       </c>
       <c r="Q49">
-        <v>168.0939768851289</v>
+        <v>165.9857005124721</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1512606133473743</v>
+        <v>0.1529842014931693</v>
       </c>
       <c r="T49">
-        <v>1.631442147989683</v>
+        <v>1.658105508438414</v>
       </c>
       <c r="U49">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05784823332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.537818444653699</v>
+        <v>3.342765210479112</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1083269367724808</v>
+        <v>0.1083100788080711</v>
       </c>
       <c r="C50">
-        <v>879.9784289738579</v>
+        <v>866.9523884555531</v>
       </c>
       <c r="D50">
-        <v>1377.450428973858</v>
+        <v>1377.713388455553</v>
       </c>
       <c r="E50">
-        <v>-353.4279999999999</v>
+        <v>-340.1389999999999</v>
       </c>
       <c r="F50">
-        <v>637.8720000000001</v>
+        <v>651.1610000000001</v>
       </c>
       <c r="G50">
         <v>140.4</v>
@@ -5509,28 +5509,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M50">
-        <v>50.9857326500372</v>
+        <v>52.04793541357964</v>
       </c>
       <c r="N50">
-        <v>119.4476006832961</v>
+        <v>118.3853979197537</v>
       </c>
       <c r="O50">
-        <v>29.86190017082404</v>
+        <v>29.59634947993843</v>
       </c>
       <c r="P50">
-        <v>89.5857005124721</v>
+        <v>88.78904843981528</v>
       </c>
       <c r="Q50">
-        <v>165.9857005124721</v>
+        <v>165.1890484398153</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1529842014931693</v>
+        <v>0.1547753813309562</v>
       </c>
       <c r="T50">
-        <v>1.658105508438414</v>
+        <v>1.685814490865527</v>
       </c>
       <c r="U50">
         <v>0.07993097776675759</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.342765210479112</v>
+        <v>3.274545512306069</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1083100788080711</v>
+        <v>0.1082932208436614</v>
       </c>
       <c r="C51">
-        <v>866.9523884555531</v>
+        <v>853.9264483559502</v>
       </c>
       <c r="D51">
-        <v>1377.713388455553</v>
+        <v>1377.97644835595</v>
       </c>
       <c r="E51">
-        <v>-340.1389999999999</v>
+        <v>-326.8499999999999</v>
       </c>
       <c r="F51">
-        <v>651.1610000000001</v>
+        <v>664.45</v>
       </c>
       <c r="G51">
         <v>140.4</v>
@@ -5591,28 +5591,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M51">
-        <v>52.04793541357964</v>
+        <v>53.11013817712208</v>
       </c>
       <c r="N51">
-        <v>118.3853979197537</v>
+        <v>117.3231951562113</v>
       </c>
       <c r="O51">
-        <v>29.59634947993843</v>
+        <v>29.33079878905281</v>
       </c>
       <c r="P51">
-        <v>88.78904843981528</v>
+        <v>87.99239636715845</v>
       </c>
       <c r="Q51">
-        <v>165.1890484398153</v>
+        <v>164.3923963671585</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1547753813309562</v>
+        <v>0.1566382083622546</v>
       </c>
       <c r="T51">
-        <v>1.685814490865527</v>
+        <v>1.714631832589724</v>
       </c>
       <c r="U51">
         <v>0.07993097776675759</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.274545512306069</v>
+        <v>3.209054602059948</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1082932208436614</v>
+        <v>0.1082763628792517</v>
       </c>
       <c r="C52">
-        <v>853.9264483559502</v>
+        <v>840.9006087325818</v>
       </c>
       <c r="D52">
-        <v>1377.97644835595</v>
+        <v>1378.239608732582</v>
       </c>
       <c r="E52">
-        <v>-326.8499999999999</v>
+        <v>-313.5609999999999</v>
       </c>
       <c r="F52">
-        <v>664.45</v>
+        <v>677.739</v>
       </c>
       <c r="G52">
         <v>140.4</v>
@@ -5673,28 +5673,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M52">
-        <v>53.11013817712208</v>
+        <v>54.17234094066453</v>
       </c>
       <c r="N52">
-        <v>117.3231951562113</v>
+        <v>116.2609923926688</v>
       </c>
       <c r="O52">
-        <v>29.33079878905281</v>
+        <v>29.0652480981672</v>
       </c>
       <c r="P52">
-        <v>87.99239636715845</v>
+        <v>87.19574429450161</v>
       </c>
       <c r="Q52">
-        <v>164.3923963671585</v>
+        <v>163.5957442945016</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1566382083622546</v>
+        <v>0.1585770691499326</v>
       </c>
       <c r="T52">
-        <v>1.714631832589724</v>
+        <v>1.74462539234348</v>
       </c>
       <c r="U52">
         <v>0.07993097776675759</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.209054602059948</v>
+        <v>3.14613196280387</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1082763628792517</v>
+        <v>0.108259504914842</v>
       </c>
       <c r="C53">
-        <v>840.9006087325818</v>
+        <v>827.874869643025</v>
       </c>
       <c r="D53">
-        <v>1378.239608732582</v>
+        <v>1378.502869643025</v>
       </c>
       <c r="E53">
-        <v>-313.5609999999999</v>
+        <v>-300.2719999999999</v>
       </c>
       <c r="F53">
-        <v>677.739</v>
+        <v>691.028</v>
       </c>
       <c r="G53">
         <v>140.4</v>
@@ -5755,28 +5755,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M53">
-        <v>54.17234094066453</v>
+        <v>55.23454370420696</v>
       </c>
       <c r="N53">
-        <v>116.2609923926688</v>
+        <v>115.1987896291264</v>
       </c>
       <c r="O53">
-        <v>29.0652480981672</v>
+        <v>28.79969740728159</v>
       </c>
       <c r="P53">
-        <v>87.19574429450161</v>
+        <v>86.39909222184477</v>
       </c>
       <c r="Q53">
-        <v>163.5957442945016</v>
+        <v>162.7990922218448</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1585770691499326</v>
+        <v>0.1605967158037637</v>
       </c>
       <c r="T53">
-        <v>1.74462539234348</v>
+        <v>1.775868683753643</v>
       </c>
       <c r="U53">
         <v>0.07993097776675759</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.14613196280387</v>
+        <v>3.085629425057642</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.108259504914842</v>
+        <v>0.1082426469504324</v>
       </c>
       <c r="C54">
-        <v>827.874869643025</v>
+        <v>814.8492311448998</v>
       </c>
       <c r="D54">
-        <v>1378.502869643025</v>
+        <v>1378.7662311449</v>
       </c>
       <c r="E54">
-        <v>-300.2719999999999</v>
+        <v>-286.9829999999998</v>
       </c>
       <c r="F54">
-        <v>691.028</v>
+        <v>704.3170000000001</v>
       </c>
       <c r="G54">
         <v>140.4</v>
@@ -5837,28 +5837,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M54">
-        <v>55.23454370420696</v>
+        <v>56.29674646774941</v>
       </c>
       <c r="N54">
-        <v>115.1987896291264</v>
+        <v>114.1365868655839</v>
       </c>
       <c r="O54">
-        <v>28.79969740728159</v>
+        <v>28.53414671639598</v>
       </c>
       <c r="P54">
-        <v>86.39909222184477</v>
+        <v>85.60244014918794</v>
       </c>
       <c r="Q54">
-        <v>162.7990922218448</v>
+        <v>162.0024401491879</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1605967158037637</v>
+        <v>0.1627023048683962</v>
       </c>
       <c r="T54">
-        <v>1.775868683753643</v>
+        <v>1.80844147692594</v>
       </c>
       <c r="U54">
         <v>0.07993097776675759</v>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.085629425057642</v>
+        <v>3.027410001943347</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1082426469504324</v>
+        <v>0.1113847889860227</v>
       </c>
       <c r="C55">
-        <v>814.8492311448998</v>
+        <v>754.1513257573268</v>
       </c>
       <c r="D55">
-        <v>1378.7662311449</v>
+        <v>1331.357325757327</v>
       </c>
       <c r="E55">
-        <v>-286.9829999999998</v>
+        <v>-273.6939999999998</v>
       </c>
       <c r="F55">
-        <v>704.3170000000001</v>
+        <v>717.6060000000001</v>
       </c>
       <c r="G55">
         <v>140.4</v>
@@ -5919,45 +5919,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M55">
-        <v>56.29674646774941</v>
+        <v>62.95627603129186</v>
       </c>
       <c r="N55">
-        <v>114.1365868655839</v>
+        <v>107.4770573020415</v>
       </c>
       <c r="O55">
-        <v>28.53414671639598</v>
+        <v>26.86926432551037</v>
       </c>
       <c r="P55">
-        <v>85.60244014918794</v>
+        <v>80.60779297653112</v>
       </c>
       <c r="Q55">
-        <v>162.0024401491879</v>
+        <v>157.0077929765311</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1627023048683962</v>
+        <v>0.1648994412836649</v>
       </c>
       <c r="T55">
-        <v>1.80844147692594</v>
+        <v>1.842430478497033</v>
       </c>
       <c r="U55">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.05994823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.027410001943347</v>
+        <v>2.707169865775113</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1113847889860227</v>
+        <v>0.111426431021613</v>
       </c>
       <c r="C56">
-        <v>754.1513257573268</v>
+        <v>740.2559075959601</v>
       </c>
       <c r="D56">
-        <v>1331.357325757327</v>
+        <v>1330.75090759596</v>
       </c>
       <c r="E56">
-        <v>-273.6939999999998</v>
+        <v>-260.4049999999999</v>
       </c>
       <c r="F56">
-        <v>717.6060000000001</v>
+        <v>730.8950000000001</v>
       </c>
       <c r="G56">
         <v>140.4</v>
@@ -6001,28 +6001,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M56">
-        <v>62.95627603129186</v>
+        <v>64.1221329948343</v>
       </c>
       <c r="N56">
-        <v>107.4770573020415</v>
+        <v>106.311200338499</v>
       </c>
       <c r="O56">
-        <v>26.86926432551037</v>
+        <v>26.57780008462476</v>
       </c>
       <c r="P56">
-        <v>80.60779297653112</v>
+        <v>79.73340025387428</v>
       </c>
       <c r="Q56">
-        <v>157.0077929765311</v>
+        <v>156.1334002538743</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1648994412836649</v>
+        <v>0.1671942282062789</v>
       </c>
       <c r="T56">
-        <v>1.842430478497033</v>
+        <v>1.877930102360174</v>
       </c>
       <c r="U56">
         <v>0.08773097776675759</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.707169865775113</v>
+        <v>2.657948595488293</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.111426431021613</v>
+        <v>0.1114680730572033</v>
       </c>
       <c r="C57">
-        <v>740.2559075959601</v>
+        <v>726.3610416162697</v>
       </c>
       <c r="D57">
-        <v>1330.75090759596</v>
+        <v>1330.14504161627</v>
       </c>
       <c r="E57">
-        <v>-260.4049999999999</v>
+        <v>-247.1159999999999</v>
       </c>
       <c r="F57">
-        <v>730.8950000000001</v>
+        <v>744.1840000000001</v>
       </c>
       <c r="G57">
         <v>140.4</v>
@@ -6083,28 +6083,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M57">
-        <v>64.1221329948343</v>
+        <v>65.28798995837674</v>
       </c>
       <c r="N57">
-        <v>106.311200338499</v>
+        <v>105.1453433749566</v>
       </c>
       <c r="O57">
-        <v>26.57780008462476</v>
+        <v>26.28633584373915</v>
       </c>
       <c r="P57">
-        <v>79.73340025387428</v>
+        <v>78.85900753121744</v>
       </c>
       <c r="Q57">
-        <v>156.1334002538743</v>
+        <v>155.2590075312174</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1671942282062789</v>
+        <v>0.1695933236253753</v>
       </c>
       <c r="T57">
-        <v>1.877930102360174</v>
+        <v>1.915043345489822</v>
       </c>
       <c r="U57">
         <v>0.08773097776675759</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.657948595488293</v>
+        <v>2.610485227711716</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1114680730572033</v>
+        <v>0.1115097150927936</v>
       </c>
       <c r="C58">
-        <v>726.3610416162697</v>
+        <v>712.4667270644049</v>
       </c>
       <c r="D58">
-        <v>1330.14504161627</v>
+        <v>1329.539727064405</v>
       </c>
       <c r="E58">
-        <v>-247.1159999999999</v>
+        <v>-233.8269999999998</v>
       </c>
       <c r="F58">
-        <v>744.1840000000001</v>
+        <v>757.4730000000002</v>
       </c>
       <c r="G58">
         <v>140.4</v>
@@ -6165,28 +6165,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M58">
-        <v>65.28798995837674</v>
+        <v>66.45384692191919</v>
       </c>
       <c r="N58">
-        <v>105.1453433749566</v>
+        <v>103.9794864114141</v>
       </c>
       <c r="O58">
-        <v>26.28633584373915</v>
+        <v>25.99487160285354</v>
       </c>
       <c r="P58">
-        <v>78.85900753121744</v>
+        <v>77.98461480856061</v>
       </c>
       <c r="Q58">
-        <v>155.2590075312174</v>
+        <v>154.3846148085606</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1695933236253753</v>
+        <v>0.1721040048779181</v>
       </c>
       <c r="T58">
-        <v>1.915043345489822</v>
+        <v>1.953882785974337</v>
       </c>
       <c r="U58">
         <v>0.08773097776675759</v>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.610485227711716</v>
+        <v>2.564687241260633</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1115097150927936</v>
+        <v>0.111551357128384</v>
       </c>
       <c r="C59">
-        <v>712.4667270644049</v>
+        <v>698.5729631878869</v>
       </c>
       <c r="D59">
-        <v>1329.539727064405</v>
+        <v>1328.934963187887</v>
       </c>
       <c r="E59">
-        <v>-233.8269999999998</v>
+        <v>-220.5379999999998</v>
       </c>
       <c r="F59">
-        <v>757.4730000000002</v>
+        <v>770.7620000000002</v>
       </c>
       <c r="G59">
         <v>140.4</v>
@@ -6247,28 +6247,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M59">
-        <v>66.45384692191919</v>
+        <v>67.61970388546163</v>
       </c>
       <c r="N59">
-        <v>103.9794864114141</v>
+        <v>102.8136294478717</v>
       </c>
       <c r="O59">
-        <v>25.99487160285354</v>
+        <v>25.70340736196793</v>
       </c>
       <c r="P59">
-        <v>77.98461480856061</v>
+        <v>77.11022208590379</v>
       </c>
       <c r="Q59">
-        <v>154.3846148085606</v>
+        <v>153.5102220859038</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1721040048779181</v>
+        <v>0.1747342423805819</v>
       </c>
       <c r="T59">
-        <v>1.953882785974337</v>
+        <v>1.994571723624781</v>
       </c>
       <c r="U59">
         <v>0.08773097776675759</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.564687241260633</v>
+        <v>2.520468495721657</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.111551357128384</v>
+        <v>0.1133187491639743</v>
       </c>
       <c r="C60">
-        <v>698.5729631878871</v>
+        <v>660.1138746969417</v>
       </c>
       <c r="D60">
-        <v>1328.934963187887</v>
+        <v>1303.764874696942</v>
       </c>
       <c r="E60">
-        <v>-220.538</v>
+        <v>-207.2489999999999</v>
       </c>
       <c r="F60">
-        <v>770.7619999999999</v>
+        <v>784.051</v>
       </c>
       <c r="G60">
         <v>140.4</v>
@@ -6329,45 +6329,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M60">
-        <v>67.6197038854616</v>
+        <v>71.84335974900405</v>
       </c>
       <c r="N60">
-        <v>102.8136294478717</v>
+        <v>98.58997358432929</v>
       </c>
       <c r="O60">
-        <v>25.70340736196793</v>
+        <v>24.64749339608232</v>
       </c>
       <c r="P60">
-        <v>77.1102220859038</v>
+        <v>73.94248018824696</v>
       </c>
       <c r="Q60">
-        <v>153.5102220859038</v>
+        <v>150.342480188247</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1747342423805819</v>
+        <v>0.1774927841516684</v>
       </c>
       <c r="T60">
-        <v>1.994571723624781</v>
+        <v>2.037245487502076</v>
       </c>
       <c r="U60">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.06579823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.520468495721658</v>
+        <v>2.372290688085422</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1133187491639743</v>
+        <v>0.1133896411995646</v>
       </c>
       <c r="C61">
-        <v>660.1138746969417</v>
+        <v>645.8351485731163</v>
       </c>
       <c r="D61">
-        <v>1303.764874696942</v>
+        <v>1302.775148573116</v>
       </c>
       <c r="E61">
-        <v>-207.2489999999999</v>
+        <v>-193.9599999999999</v>
       </c>
       <c r="F61">
-        <v>784.051</v>
+        <v>797.34</v>
       </c>
       <c r="G61">
         <v>140.4</v>
@@ -6411,28 +6411,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M61">
-        <v>71.84335974900405</v>
+        <v>73.06104381254649</v>
       </c>
       <c r="N61">
-        <v>98.58997358432929</v>
+        <v>97.37228952078685</v>
       </c>
       <c r="O61">
-        <v>24.64749339608232</v>
+        <v>24.34307238019671</v>
       </c>
       <c r="P61">
-        <v>73.94248018824696</v>
+        <v>73.02921714059013</v>
       </c>
       <c r="Q61">
-        <v>150.342480188247</v>
+        <v>149.4292171405901</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1774927841516684</v>
+        <v>0.1803892530113092</v>
       </c>
       <c r="T61">
-        <v>2.037245487502076</v>
+        <v>2.082052939573236</v>
       </c>
       <c r="U61">
         <v>0.09163097776675758</v>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.372290688085422</v>
+        <v>2.332752509950665</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1133896411995646</v>
+        <v>0.1134605332351549</v>
       </c>
       <c r="C62">
-        <v>645.8351485731163</v>
+        <v>631.557923969653</v>
       </c>
       <c r="D62">
-        <v>1302.775148573116</v>
+        <v>1301.786923969653</v>
       </c>
       <c r="E62">
-        <v>-193.9599999999999</v>
+        <v>-180.6709999999999</v>
       </c>
       <c r="F62">
-        <v>797.34</v>
+        <v>810.629</v>
       </c>
       <c r="G62">
         <v>140.4</v>
@@ -6493,28 +6493,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M62">
-        <v>73.06104381254649</v>
+        <v>74.27872787608892</v>
       </c>
       <c r="N62">
-        <v>97.37228952078685</v>
+        <v>96.15460545724441</v>
       </c>
       <c r="O62">
-        <v>24.34307238019671</v>
+        <v>24.0386513643111</v>
       </c>
       <c r="P62">
-        <v>73.02921714059013</v>
+        <v>72.11595409293331</v>
       </c>
       <c r="Q62">
-        <v>149.4292171405901</v>
+        <v>148.5159540929333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1803892530113092</v>
+        <v>0.183434258735547</v>
       </c>
       <c r="T62">
-        <v>2.082052939573236</v>
+        <v>2.129158209699328</v>
       </c>
       <c r="U62">
         <v>0.09163097776675758</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.332752509950665</v>
+        <v>2.294510665525245</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1134605332351549</v>
+        <v>0.1135314252707452</v>
       </c>
       <c r="C63">
-        <v>631.557923969653</v>
+        <v>617.2821974721909</v>
       </c>
       <c r="D63">
-        <v>1301.786923969653</v>
+        <v>1300.800197472191</v>
       </c>
       <c r="E63">
-        <v>-180.6709999999999</v>
+        <v>-167.3819999999999</v>
       </c>
       <c r="F63">
-        <v>810.629</v>
+        <v>823.918</v>
       </c>
       <c r="G63">
         <v>140.4</v>
@@ -6575,28 +6575,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M63">
-        <v>74.27872787608892</v>
+        <v>75.49641193963137</v>
       </c>
       <c r="N63">
-        <v>96.15460545724441</v>
+        <v>94.93692139370197</v>
       </c>
       <c r="O63">
-        <v>24.0386513643111</v>
+        <v>23.73423034842549</v>
       </c>
       <c r="P63">
-        <v>72.11595409293331</v>
+        <v>71.20269104527648</v>
       </c>
       <c r="Q63">
-        <v>148.5159540929333</v>
+        <v>147.6026910452765</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.183434258735547</v>
+        <v>0.1866395279189551</v>
       </c>
       <c r="T63">
-        <v>2.129158209699328</v>
+        <v>2.178742704568898</v>
       </c>
       <c r="U63">
         <v>0.09163097776675758</v>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.294510665525245</v>
+        <v>2.257502428984515</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1135314252707452</v>
+        <v>0.1136023173063355</v>
       </c>
       <c r="C64">
-        <v>617.2821974721909</v>
+        <v>603.0079656767136</v>
       </c>
       <c r="D64">
-        <v>1300.800197472191</v>
+        <v>1299.814965676714</v>
       </c>
       <c r="E64">
-        <v>-167.3819999999999</v>
+        <v>-154.0929999999998</v>
       </c>
       <c r="F64">
-        <v>823.918</v>
+        <v>837.2070000000001</v>
       </c>
       <c r="G64">
         <v>140.4</v>
@@ -6657,28 +6657,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M64">
-        <v>75.49641193963137</v>
+        <v>76.71409600317382</v>
       </c>
       <c r="N64">
-        <v>94.93692139370197</v>
+        <v>93.71923733015952</v>
       </c>
       <c r="O64">
-        <v>23.73423034842549</v>
+        <v>23.42980933253988</v>
       </c>
       <c r="P64">
-        <v>71.20269104527648</v>
+        <v>70.28942799761964</v>
       </c>
       <c r="Q64">
-        <v>147.6026910452765</v>
+        <v>146.6894279976196</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1866395279189551</v>
+        <v>0.1900180548960611</v>
       </c>
       <c r="T64">
-        <v>2.178742704568898</v>
+        <v>2.23100744240439</v>
       </c>
       <c r="U64">
         <v>0.09163097776675758</v>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.257502428984515</v>
+        <v>2.221669057095871</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1136023173063355</v>
+        <v>0.1136732093419259</v>
       </c>
       <c r="C65">
-        <v>603.0079656767136</v>
+        <v>588.7352251895104</v>
       </c>
       <c r="D65">
-        <v>1299.814965676714</v>
+        <v>1298.83122518951</v>
       </c>
       <c r="E65">
-        <v>-154.0929999999998</v>
+        <v>-140.8039999999999</v>
       </c>
       <c r="F65">
-        <v>837.2070000000001</v>
+        <v>850.4960000000001</v>
       </c>
       <c r="G65">
         <v>140.4</v>
@@ -6739,28 +6739,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M65">
-        <v>76.71409600317382</v>
+        <v>77.93178006671626</v>
       </c>
       <c r="N65">
-        <v>93.71923733015952</v>
+        <v>92.50155326661708</v>
       </c>
       <c r="O65">
-        <v>23.42980933253988</v>
+        <v>23.12538831665427</v>
       </c>
       <c r="P65">
-        <v>70.28942799761964</v>
+        <v>69.37616494996281</v>
       </c>
       <c r="Q65">
-        <v>146.6894279976196</v>
+        <v>145.7761649499628</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1900180548960611</v>
+        <v>0.1935842778163395</v>
       </c>
       <c r="T65">
-        <v>2.23100744240439</v>
+        <v>2.286175776786299</v>
       </c>
       <c r="U65">
         <v>0.09163097776675758</v>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.221669057095871</v>
+        <v>2.186955478078748</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1136732093419259</v>
+        <v>0.1137441013775162</v>
       </c>
       <c r="C66">
-        <v>588.7352251895104</v>
+        <v>574.4639726271366</v>
       </c>
       <c r="D66">
-        <v>1298.83122518951</v>
+        <v>1297.848972627137</v>
       </c>
       <c r="E66">
-        <v>-140.8039999999999</v>
+        <v>-127.5149999999999</v>
       </c>
       <c r="F66">
-        <v>850.4960000000001</v>
+        <v>863.7850000000001</v>
       </c>
       <c r="G66">
         <v>140.4</v>
@@ -6821,28 +6821,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M66">
-        <v>77.93178006671626</v>
+        <v>79.14946413025871</v>
       </c>
       <c r="N66">
-        <v>92.50155326661708</v>
+        <v>91.28386920307463</v>
       </c>
       <c r="O66">
-        <v>23.12538831665427</v>
+        <v>22.82096730076866</v>
       </c>
       <c r="P66">
-        <v>69.37616494996281</v>
+        <v>68.46290190230597</v>
       </c>
       <c r="Q66">
-        <v>145.7761649499628</v>
+        <v>144.862901902306</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1935842778163395</v>
+        <v>0.1973542849034911</v>
       </c>
       <c r="T66">
-        <v>2.286175776786299</v>
+        <v>2.344496587418603</v>
       </c>
       <c r="U66">
         <v>0.09163097776675758</v>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.186955478078748</v>
+        <v>2.153310009185229</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1137441013775162</v>
+        <v>0.1138149934131065</v>
       </c>
       <c r="C67">
-        <v>574.4639726271366</v>
+        <v>560.1942046163738</v>
       </c>
       <c r="D67">
-        <v>1297.848972627137</v>
+        <v>1296.868204616374</v>
       </c>
       <c r="E67">
-        <v>-127.5149999999999</v>
+        <v>-114.2259999999999</v>
       </c>
       <c r="F67">
-        <v>863.7850000000001</v>
+        <v>877.0740000000001</v>
       </c>
       <c r="G67">
         <v>140.4</v>
@@ -6903,28 +6903,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M67">
-        <v>79.14946413025871</v>
+        <v>80.36714819380114</v>
       </c>
       <c r="N67">
-        <v>91.28386920307463</v>
+        <v>90.06618513953219</v>
       </c>
       <c r="O67">
-        <v>22.82096730076866</v>
+        <v>22.51654628488305</v>
       </c>
       <c r="P67">
-        <v>68.46290190230597</v>
+        <v>67.54963885464915</v>
       </c>
       <c r="Q67">
-        <v>144.862901902306</v>
+        <v>143.9496388546492</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1973542849034911</v>
+        <v>0.2013460571134162</v>
       </c>
       <c r="T67">
-        <v>2.344496587418603</v>
+        <v>2.406248033970453</v>
       </c>
       <c r="U67">
         <v>0.09163097776675758</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.153310009185229</v>
+        <v>2.12068409995515</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1138149934131065</v>
+        <v>0.1138858854486968</v>
       </c>
       <c r="C68">
-        <v>560.1942046163738</v>
+        <v>545.9259177941927</v>
       </c>
       <c r="D68">
-        <v>1296.868204616374</v>
+        <v>1295.888917794193</v>
       </c>
       <c r="E68">
-        <v>-114.2259999999999</v>
+        <v>-100.9369999999998</v>
       </c>
       <c r="F68">
-        <v>877.0740000000001</v>
+        <v>890.3630000000002</v>
       </c>
       <c r="G68">
         <v>140.4</v>
@@ -6985,28 +6985,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M68">
-        <v>80.36714819380114</v>
+        <v>81.58483225734359</v>
       </c>
       <c r="N68">
-        <v>90.06618513953219</v>
+        <v>88.84850107598974</v>
       </c>
       <c r="O68">
-        <v>22.51654628488305</v>
+        <v>22.21212526899744</v>
       </c>
       <c r="P68">
-        <v>67.54963885464915</v>
+        <v>66.63637580699231</v>
       </c>
       <c r="Q68">
-        <v>143.9496388546492</v>
+        <v>143.0363758069923</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2013460571134162</v>
+        <v>0.2055797549118216</v>
       </c>
       <c r="T68">
-        <v>2.406248033970453</v>
+        <v>2.471741992434537</v>
       </c>
       <c r="U68">
         <v>0.09163097776675758</v>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.12068409995515</v>
+        <v>2.089032098463282</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1138858854486968</v>
+        <v>0.1139567774842871</v>
       </c>
       <c r="C69">
-        <v>545.9259177941927</v>
+        <v>531.6591088077149</v>
       </c>
       <c r="D69">
-        <v>1295.888917794193</v>
+        <v>1294.911108807715</v>
       </c>
       <c r="E69">
-        <v>-100.9369999999998</v>
+        <v>-87.6479999999998</v>
       </c>
       <c r="F69">
-        <v>890.3630000000002</v>
+        <v>903.6520000000002</v>
       </c>
       <c r="G69">
         <v>140.4</v>
@@ -7067,28 +7067,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M69">
-        <v>81.58483225734359</v>
+        <v>82.80251632088603</v>
       </c>
       <c r="N69">
-        <v>88.84850107598974</v>
+        <v>87.63081701244731</v>
       </c>
       <c r="O69">
-        <v>22.21212526899744</v>
+        <v>21.90770425311183</v>
       </c>
       <c r="P69">
-        <v>66.63637580699231</v>
+        <v>65.72311275933548</v>
       </c>
       <c r="Q69">
-        <v>143.0363758069923</v>
+        <v>142.1231127593355</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2055797549118216</v>
+        <v>0.2100780588226274</v>
       </c>
       <c r="T69">
-        <v>2.471741992434537</v>
+        <v>2.541329323302627</v>
       </c>
       <c r="U69">
         <v>0.09163097776675758</v>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.089032098463282</v>
+        <v>2.058311038191763</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1139567774842871</v>
+        <v>0.1140276695198774</v>
       </c>
       <c r="C70">
-        <v>531.6591088077149</v>
+        <v>517.3937743141738</v>
       </c>
       <c r="D70">
-        <v>1294.911108807715</v>
+        <v>1293.934774314174</v>
       </c>
       <c r="E70">
-        <v>-87.6479999999998</v>
+        <v>-74.35899999999981</v>
       </c>
       <c r="F70">
-        <v>903.6520000000002</v>
+        <v>916.9410000000001</v>
       </c>
       <c r="G70">
         <v>140.4</v>
@@ -7149,28 +7149,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M70">
-        <v>82.80251632088603</v>
+        <v>84.02020038442848</v>
       </c>
       <c r="N70">
-        <v>87.63081701244731</v>
+        <v>86.41313294890486</v>
       </c>
       <c r="O70">
-        <v>21.90770425311183</v>
+        <v>21.60328323722621</v>
       </c>
       <c r="P70">
-        <v>65.72311275933548</v>
+        <v>64.80984971167865</v>
       </c>
       <c r="Q70">
-        <v>142.1231127593355</v>
+        <v>141.2098497116787</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2100780588226274</v>
+        <v>0.2148665758889691</v>
       </c>
       <c r="T70">
-        <v>2.541329323302627</v>
+        <v>2.615406159388013</v>
       </c>
       <c r="U70">
         <v>0.09163097776675758</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.058311038191763</v>
+        <v>2.02848044343536</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1140276695198774</v>
+        <v>0.1215535615554678</v>
       </c>
       <c r="C71">
-        <v>517.3937743141738</v>
+        <v>408.2109014988674</v>
       </c>
       <c r="D71">
-        <v>1293.934774314174</v>
+        <v>1198.040901498867</v>
       </c>
       <c r="E71">
-        <v>-74.35899999999981</v>
+        <v>-61.06999999999982</v>
       </c>
       <c r="F71">
-        <v>916.9410000000001</v>
+        <v>930.2300000000001</v>
       </c>
       <c r="G71">
         <v>140.4</v>
@@ -7231,45 +7231,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M71">
-        <v>84.02020038442848</v>
+        <v>98.44715044797091</v>
       </c>
       <c r="N71">
-        <v>86.41313294890486</v>
+        <v>71.98618288536242</v>
       </c>
       <c r="O71">
-        <v>21.60328323722621</v>
+        <v>17.99654572134061</v>
       </c>
       <c r="P71">
-        <v>64.80984971167865</v>
+        <v>53.98963716402181</v>
       </c>
       <c r="Q71">
-        <v>141.2098497116787</v>
+        <v>130.3896371640218</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2148665758889691</v>
+        <v>0.2199743274264002</v>
       </c>
       <c r="T71">
-        <v>2.615406159388013</v>
+        <v>2.694421451212424</v>
       </c>
       <c r="U71">
-        <v>0.09163097776675758</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.06872323332506819</v>
+        <v>0.07937323332506818</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.02848044343536</v>
+        <v>1.731216521329451</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1215535615554678</v>
+        <v>0.1217309535910581</v>
       </c>
       <c r="C72">
-        <v>408.2109014988674</v>
+        <v>392.8327580129395</v>
       </c>
       <c r="D72">
-        <v>1198.040901498867</v>
+        <v>1195.95175801294</v>
       </c>
       <c r="E72">
-        <v>-61.06999999999982</v>
+        <v>-47.78099999999984</v>
       </c>
       <c r="F72">
-        <v>930.2300000000001</v>
+        <v>943.5190000000001</v>
       </c>
       <c r="G72">
         <v>140.4</v>
@@ -7313,28 +7313,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M72">
-        <v>98.44715044797091</v>
+        <v>99.85353831151336</v>
       </c>
       <c r="N72">
-        <v>71.98618288536242</v>
+        <v>70.57979502181998</v>
       </c>
       <c r="O72">
-        <v>17.99654572134061</v>
+        <v>17.64494875545499</v>
       </c>
       <c r="P72">
-        <v>53.98963716402181</v>
+        <v>52.93484626636499</v>
       </c>
       <c r="Q72">
-        <v>130.3896371640218</v>
+        <v>129.334846266365</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2199743274264002</v>
+        <v>0.2254343376905507</v>
       </c>
       <c r="T72">
-        <v>2.694421451212424</v>
+        <v>2.778886073507485</v>
       </c>
       <c r="U72">
         <v>0.1058309777667576</v>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.731216521329451</v>
+        <v>1.706833190043121</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1217309535910581</v>
+        <v>0.1219083456266484</v>
       </c>
       <c r="C73">
-        <v>392.8327580129396</v>
+        <v>377.461887939628</v>
       </c>
       <c r="D73">
-        <v>1195.95175801294</v>
+        <v>1193.869887939628</v>
       </c>
       <c r="E73">
-        <v>-47.78099999999995</v>
+        <v>-34.49199999999996</v>
       </c>
       <c r="F73">
-        <v>943.519</v>
+        <v>956.808</v>
       </c>
       <c r="G73">
         <v>140.4</v>
@@ -7395,28 +7395,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M73">
-        <v>99.85353831151335</v>
+        <v>101.2599261750558</v>
       </c>
       <c r="N73">
-        <v>70.57979502181999</v>
+        <v>69.17340715827756</v>
       </c>
       <c r="O73">
-        <v>17.644948755455</v>
+        <v>17.29335178956939</v>
       </c>
       <c r="P73">
-        <v>52.93484626636499</v>
+        <v>51.88005536870817</v>
       </c>
       <c r="Q73">
-        <v>129.334846266365</v>
+        <v>128.2800553687082</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2254343376905506</v>
+        <v>0.2312843486878547</v>
       </c>
       <c r="T73">
-        <v>2.778886073507484</v>
+        <v>2.869383883109334</v>
       </c>
       <c r="U73">
         <v>0.1058309777667576</v>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.706833190043121</v>
+        <v>1.683127173514745</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1219083456266484</v>
+        <v>0.1220857376622387</v>
       </c>
       <c r="C74">
-        <v>377.461887939628</v>
+        <v>362.0982533610473</v>
       </c>
       <c r="D74">
-        <v>1193.869887939628</v>
+        <v>1191.795253361047</v>
       </c>
       <c r="E74">
-        <v>-34.49199999999996</v>
+        <v>-21.20299999999986</v>
       </c>
       <c r="F74">
-        <v>956.808</v>
+        <v>970.0970000000001</v>
       </c>
       <c r="G74">
         <v>140.4</v>
@@ -7477,28 +7477,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M74">
-        <v>101.2599261750558</v>
+        <v>102.6663140385982</v>
       </c>
       <c r="N74">
-        <v>69.17340715827756</v>
+        <v>67.76701929473509</v>
       </c>
       <c r="O74">
-        <v>17.29335178956939</v>
+        <v>16.94175482368377</v>
       </c>
       <c r="P74">
-        <v>51.88005536870817</v>
+        <v>50.82526447105132</v>
       </c>
       <c r="Q74">
-        <v>128.2800553687082</v>
+        <v>127.2252644710513</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2312843486878547</v>
+        <v>0.2375676938331072</v>
       </c>
       <c r="T74">
-        <v>2.869383883109334</v>
+        <v>2.966585234163173</v>
       </c>
       <c r="U74">
         <v>0.1058309777667576</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.683127173514745</v>
+        <v>1.660070636891255</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1220857376622387</v>
+        <v>0.122263129697829</v>
       </c>
       <c r="C75">
-        <v>362.0982533610473</v>
+        <v>346.741816622423</v>
       </c>
       <c r="D75">
-        <v>1191.795253361047</v>
+        <v>1189.727816622423</v>
       </c>
       <c r="E75">
-        <v>-21.20299999999986</v>
+        <v>-7.913999999999874</v>
       </c>
       <c r="F75">
-        <v>970.0970000000001</v>
+        <v>983.3860000000001</v>
       </c>
       <c r="G75">
         <v>140.4</v>
@@ -7559,28 +7559,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M75">
-        <v>102.6663140385982</v>
+        <v>104.0727019021407</v>
       </c>
       <c r="N75">
-        <v>67.76701929473509</v>
+        <v>66.36063143119266</v>
       </c>
       <c r="O75">
-        <v>16.94175482368377</v>
+        <v>16.59015785779816</v>
       </c>
       <c r="P75">
-        <v>50.82526447105132</v>
+        <v>49.7704735733945</v>
       </c>
       <c r="Q75">
-        <v>127.2252644710513</v>
+        <v>126.1704735733945</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2375676938331072</v>
+        <v>0.2443343732203022</v>
       </c>
       <c r="T75">
-        <v>2.966585234163173</v>
+        <v>3.071263612221153</v>
       </c>
       <c r="U75">
         <v>0.1058309777667576</v>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.660070636891255</v>
+        <v>1.637637249906238</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.122263129697829</v>
+        <v>0.1224405217334193</v>
       </c>
       <c r="C76">
-        <v>346.741816622423</v>
+        <v>331.3925403298091</v>
       </c>
       <c r="D76">
-        <v>1189.727816622423</v>
+        <v>1187.667540329809</v>
       </c>
       <c r="E76">
-        <v>-7.913999999999874</v>
+        <v>5.375000000000114</v>
       </c>
       <c r="F76">
-        <v>983.3860000000001</v>
+        <v>996.6750000000001</v>
       </c>
       <c r="G76">
         <v>140.4</v>
@@ -7641,28 +7641,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M76">
-        <v>104.0727019021407</v>
+        <v>105.4790897656831</v>
       </c>
       <c r="N76">
-        <v>66.36063143119266</v>
+        <v>64.95424356765022</v>
       </c>
       <c r="O76">
-        <v>16.59015785779816</v>
+        <v>16.23856089191256</v>
       </c>
       <c r="P76">
-        <v>49.7704735733945</v>
+        <v>48.71568267573767</v>
       </c>
       <c r="Q76">
-        <v>126.1704735733945</v>
+        <v>125.1156826757377</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2443343732203022</v>
+        <v>0.2516423869584729</v>
       </c>
       <c r="T76">
-        <v>3.071263612221153</v>
+        <v>3.184316260523773</v>
       </c>
       <c r="U76">
         <v>0.1058309777667576</v>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.637637249906238</v>
+        <v>1.615802086574155</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1224405217334193</v>
+        <v>0.1226179137690097</v>
       </c>
       <c r="C77">
-        <v>331.3925403298091</v>
+        <v>316.0503873478361</v>
       </c>
       <c r="D77">
-        <v>1187.667540329809</v>
+        <v>1185.614387347836</v>
       </c>
       <c r="E77">
-        <v>5.375000000000114</v>
+        <v>18.6640000000001</v>
       </c>
       <c r="F77">
-        <v>996.6750000000001</v>
+        <v>1009.964</v>
       </c>
       <c r="G77">
         <v>140.4</v>
@@ -7723,28 +7723,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M77">
-        <v>105.4790897656831</v>
+        <v>106.8854776292256</v>
       </c>
       <c r="N77">
-        <v>64.95424356765022</v>
+        <v>63.54785570410777</v>
       </c>
       <c r="O77">
-        <v>16.23856089191256</v>
+        <v>15.88696392602694</v>
       </c>
       <c r="P77">
-        <v>48.71568267573767</v>
+        <v>47.66089177808083</v>
       </c>
       <c r="Q77">
-        <v>125.1156826757377</v>
+        <v>124.0608917780808</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2516423869584729</v>
+        <v>0.2595594018414911</v>
       </c>
       <c r="T77">
-        <v>3.184316260523773</v>
+        <v>3.306789962851611</v>
       </c>
       <c r="U77">
         <v>0.1058309777667576</v>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.615802086574155</v>
+        <v>1.594541532803442</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1226179137690097</v>
+        <v>0.1227953058046</v>
       </c>
       <c r="C78">
-        <v>316.0503873478361</v>
+        <v>300.7153207974785</v>
       </c>
       <c r="D78">
-        <v>1185.614387347836</v>
+        <v>1183.568320797478</v>
       </c>
       <c r="E78">
-        <v>18.6640000000001</v>
+        <v>31.95300000000009</v>
       </c>
       <c r="F78">
-        <v>1009.964</v>
+        <v>1023.253</v>
       </c>
       <c r="G78">
         <v>140.4</v>
@@ -7805,28 +7805,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M78">
-        <v>106.8854776292256</v>
+        <v>108.291865492768</v>
       </c>
       <c r="N78">
-        <v>63.54785570410777</v>
+        <v>62.14146784056534</v>
       </c>
       <c r="O78">
-        <v>15.88696392602694</v>
+        <v>15.53536696014134</v>
       </c>
       <c r="P78">
-        <v>47.66089177808083</v>
+        <v>46.60610088042401</v>
       </c>
       <c r="Q78">
-        <v>124.0608917780808</v>
+        <v>123.006100880424</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2595594018414911</v>
+        <v>0.2681648528012934</v>
       </c>
       <c r="T78">
-        <v>3.306789962851611</v>
+        <v>3.439913552338391</v>
       </c>
       <c r="U78">
         <v>0.1058309777667576</v>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.594541532803442</v>
+        <v>1.573833201208592</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1227953058046</v>
+        <v>0.1229726978401903</v>
       </c>
       <c r="C79">
-        <v>300.7153207974785</v>
+        <v>285.3873040538479</v>
       </c>
       <c r="D79">
-        <v>1183.568320797478</v>
+        <v>1181.529304053848</v>
       </c>
       <c r="E79">
-        <v>31.95300000000009</v>
+        <v>45.24200000000019</v>
       </c>
       <c r="F79">
-        <v>1023.253</v>
+        <v>1036.542</v>
       </c>
       <c r="G79">
         <v>140.4</v>
@@ -7887,28 +7887,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M79">
-        <v>108.291865492768</v>
+        <v>109.6982533563104</v>
       </c>
       <c r="N79">
-        <v>62.14146784056534</v>
+        <v>60.73507997702289</v>
       </c>
       <c r="O79">
-        <v>15.53536696014134</v>
+        <v>15.18376999425572</v>
       </c>
       <c r="P79">
-        <v>46.60610088042401</v>
+        <v>45.55130998276717</v>
       </c>
       <c r="Q79">
-        <v>123.006100880424</v>
+        <v>121.9513099827672</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2681648528012934</v>
+        <v>0.2775526174847142</v>
       </c>
       <c r="T79">
-        <v>3.439913552338391</v>
+        <v>3.585139286323968</v>
       </c>
       <c r="U79">
         <v>0.1058309777667576</v>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.573833201208592</v>
+        <v>1.553655852475149</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1229726978401903</v>
+        <v>0.1231500898757806</v>
       </c>
       <c r="C80">
-        <v>285.3873040538479</v>
+        <v>270.066300744006</v>
       </c>
       <c r="D80">
-        <v>1181.529304053848</v>
+        <v>1179.497300744006</v>
       </c>
       <c r="E80">
-        <v>45.24200000000019</v>
+        <v>58.53100000000018</v>
       </c>
       <c r="F80">
-        <v>1036.542</v>
+        <v>1049.831</v>
       </c>
       <c r="G80">
         <v>140.4</v>
@@ -7969,28 +7969,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M80">
-        <v>109.6982533563104</v>
+        <v>111.1046412198529</v>
       </c>
       <c r="N80">
-        <v>60.73507997702289</v>
+        <v>59.32869211348044</v>
       </c>
       <c r="O80">
-        <v>15.18376999425572</v>
+        <v>14.83217302837011</v>
       </c>
       <c r="P80">
-        <v>45.55130998276717</v>
+        <v>44.49651908511034</v>
       </c>
       <c r="Q80">
-        <v>121.9513099827672</v>
+        <v>120.8965190851103</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2775526174847142</v>
+        <v>0.2878344549951274</v>
       </c>
       <c r="T80">
-        <v>3.585139286323968</v>
+        <v>3.744196042593888</v>
       </c>
       <c r="U80">
         <v>0.1058309777667576</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.553655852475149</v>
+        <v>1.533989322696982</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1231500898757806</v>
+        <v>0.123327481911371</v>
       </c>
       <c r="C81">
-        <v>270.066300744006</v>
+        <v>254.7522747448036</v>
       </c>
       <c r="D81">
-        <v>1179.497300744006</v>
+        <v>1177.472274744804</v>
       </c>
       <c r="E81">
-        <v>58.53100000000018</v>
+        <v>71.82000000000016</v>
       </c>
       <c r="F81">
-        <v>1049.831</v>
+        <v>1063.12</v>
       </c>
       <c r="G81">
         <v>140.4</v>
@@ -8051,28 +8051,28 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M81">
-        <v>111.1046412198529</v>
+        <v>112.5110290833953</v>
       </c>
       <c r="N81">
-        <v>59.32869211348044</v>
+        <v>57.92230424993801</v>
       </c>
       <c r="O81">
-        <v>14.83217302837011</v>
+        <v>14.4805760624845</v>
       </c>
       <c r="P81">
-        <v>44.49651908511034</v>
+        <v>43.44172818745351</v>
       </c>
       <c r="Q81">
-        <v>120.8965190851103</v>
+        <v>119.8417281874535</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2878344549951274</v>
+        <v>0.2991444762565821</v>
       </c>
       <c r="T81">
-        <v>3.744196042593888</v>
+        <v>3.919158474490799</v>
       </c>
       <c r="U81">
         <v>0.1058309777667576</v>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.533989322696982</v>
+        <v>1.51481445616327</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.123327481911371</v>
+        <v>0.1592195731865994</v>
       </c>
       <c r="C82">
-        <v>254.7522747448036</v>
+        <v>-62.10792753547059</v>
       </c>
       <c r="D82">
-        <v>1177.472274744804</v>
+        <v>873.9010724645295</v>
       </c>
       <c r="E82">
-        <v>71.82000000000016</v>
+        <v>85.10900000000015</v>
       </c>
       <c r="F82">
-        <v>1063.12</v>
+        <v>1076.409</v>
       </c>
       <c r="G82">
         <v>140.4</v>
@@ -8133,45 +8133,45 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M82">
-        <v>112.5110290833953</v>
+        <v>175.0574481469378</v>
       </c>
       <c r="N82">
-        <v>57.92230424993801</v>
+        <v>-4.62411481360445</v>
       </c>
       <c r="O82">
-        <v>14.4805760624845</v>
+        <v>-1.156028703401113</v>
       </c>
       <c r="P82">
-        <v>43.44172818745351</v>
+        <v>-3.468086110203338</v>
       </c>
       <c r="Q82">
-        <v>119.8417281874535</v>
+        <v>72.93191388979668</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2991444762565821</v>
+        <v>0.3134281063248494</v>
       </c>
       <c r="T82">
-        <v>3.919158474490799</v>
+        <v>4.140121688908177</v>
       </c>
       <c r="U82">
-        <v>0.1058309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V82">
-        <v>0.25</v>
+        <v>0.2433962895287336</v>
       </c>
       <c r="W82">
-        <v>0.07937323332506818</v>
+        <v>0.1230472012158988</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.51481445616327</v>
+        <v>0.9735851581149343</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1592195731865994</v>
+        <v>0.160387882964267</v>
       </c>
       <c r="C83">
-        <v>-62.10792753547059</v>
+        <v>-82.66973313233234</v>
       </c>
       <c r="D83">
-        <v>873.9010724645295</v>
+        <v>866.6282668676678</v>
       </c>
       <c r="E83">
-        <v>85.10900000000015</v>
+        <v>98.39800000000014</v>
       </c>
       <c r="F83">
-        <v>1076.409</v>
+        <v>1089.698</v>
       </c>
       <c r="G83">
         <v>140.4</v>
@@ -8215,37 +8215,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M83">
-        <v>175.0574481469378</v>
+        <v>177.2186512104802</v>
       </c>
       <c r="N83">
-        <v>-4.62411481360445</v>
+        <v>-6.785317877146895</v>
       </c>
       <c r="O83">
-        <v>-1.156028703401113</v>
+        <v>-1.696329469286724</v>
       </c>
       <c r="P83">
-        <v>-3.468086110203338</v>
+        <v>-5.088988407860171</v>
       </c>
       <c r="Q83">
-        <v>72.93191388979668</v>
+        <v>71.31101159213983</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3134281063248494</v>
+        <v>0.3282963344540078</v>
       </c>
       <c r="T83">
-        <v>4.140121688908177</v>
+        <v>4.370128449403077</v>
       </c>
       <c r="U83">
         <v>0.1626309777667576</v>
       </c>
       <c r="V83">
-        <v>0.2433962895287336</v>
+        <v>0.2404280420954563</v>
       </c>
       <c r="W83">
-        <v>0.1230472012158988</v>
+        <v>0.1235299301982264</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9735851581149343</v>
+        <v>0.9617121683818253</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.160387882964267</v>
+        <v>0.1615561927419346</v>
       </c>
       <c r="C84">
-        <v>-82.66973313233234</v>
+        <v>-103.1114859165384</v>
       </c>
       <c r="D84">
-        <v>866.6282668676678</v>
+        <v>859.4755140834617</v>
       </c>
       <c r="E84">
-        <v>98.39800000000014</v>
+        <v>111.6870000000001</v>
       </c>
       <c r="F84">
-        <v>1089.698</v>
+        <v>1102.987</v>
       </c>
       <c r="G84">
         <v>140.4</v>
@@ -8297,37 +8297,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M84">
-        <v>177.2186512104802</v>
+        <v>179.3798542740226</v>
       </c>
       <c r="N84">
-        <v>-6.785317877146895</v>
+        <v>-8.946520940689311</v>
       </c>
       <c r="O84">
-        <v>-1.696329469286724</v>
+        <v>-2.236630235172328</v>
       </c>
       <c r="P84">
-        <v>-5.088988407860171</v>
+        <v>-6.709890705516983</v>
       </c>
       <c r="Q84">
-        <v>71.31101159213983</v>
+        <v>69.69010929448302</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3282963344540078</v>
+        <v>0.3449137658924789</v>
       </c>
       <c r="T84">
-        <v>4.370128449403077</v>
+        <v>4.627194828779729</v>
       </c>
       <c r="U84">
         <v>0.1626309777667576</v>
       </c>
       <c r="V84">
-        <v>0.2404280420954563</v>
+        <v>0.2375313186967159</v>
       </c>
       <c r="W84">
-        <v>0.1235299301982264</v>
+        <v>0.1240010271568834</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9617121683818253</v>
+        <v>0.9501252747868637</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1615561927419346</v>
+        <v>0.1627245025196022</v>
       </c>
       <c r="C85">
-        <v>-103.1114859165384</v>
+        <v>-123.4361341373788</v>
       </c>
       <c r="D85">
-        <v>859.4755140834617</v>
+        <v>852.4398658626216</v>
       </c>
       <c r="E85">
-        <v>111.6870000000001</v>
+        <v>124.9760000000003</v>
       </c>
       <c r="F85">
-        <v>1102.987</v>
+        <v>1116.276</v>
       </c>
       <c r="G85">
         <v>140.4</v>
@@ -8379,37 +8379,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M85">
-        <v>179.3798542740226</v>
+        <v>181.5410573375651</v>
       </c>
       <c r="N85">
-        <v>-8.946520940689311</v>
+        <v>-11.10772400423181</v>
       </c>
       <c r="O85">
-        <v>-2.236630235172328</v>
+        <v>-2.776931001057953</v>
       </c>
       <c r="P85">
-        <v>-6.709890705516983</v>
+        <v>-8.330793003173859</v>
       </c>
       <c r="Q85">
-        <v>69.69010929448302</v>
+        <v>68.06920699682615</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3449137658924789</v>
+        <v>0.3636083762607589</v>
       </c>
       <c r="T85">
-        <v>4.627194828779729</v>
+        <v>4.916394505578463</v>
       </c>
       <c r="U85">
         <v>0.1626309777667576</v>
       </c>
       <c r="V85">
-        <v>0.2375313186967159</v>
+        <v>0.2347035649027073</v>
       </c>
       <c r="W85">
-        <v>0.1240010271568834</v>
+        <v>0.1244609075212866</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9501252747868637</v>
+        <v>0.9388142596108293</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1627245025196022</v>
+        <v>0.1638928122972697</v>
       </c>
       <c r="C86">
-        <v>-123.4361341373785</v>
+        <v>-143.6465302907535</v>
       </c>
       <c r="D86">
-        <v>852.4398658626216</v>
+        <v>845.5184697092466</v>
       </c>
       <c r="E86">
-        <v>124.9760000000001</v>
+        <v>138.2650000000001</v>
       </c>
       <c r="F86">
-        <v>1116.276</v>
+        <v>1129.565</v>
       </c>
       <c r="G86">
         <v>140.4</v>
@@ -8461,37 +8461,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M86">
-        <v>181.5410573375651</v>
+        <v>183.7022604011075</v>
       </c>
       <c r="N86">
-        <v>-11.10772400423176</v>
+        <v>-13.2689270677742</v>
       </c>
       <c r="O86">
-        <v>-2.776931001057939</v>
+        <v>-3.31723176694355</v>
       </c>
       <c r="P86">
-        <v>-8.330793003173817</v>
+        <v>-9.95169530083065</v>
       </c>
       <c r="Q86">
-        <v>68.06920699682618</v>
+        <v>66.44830469916936</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3636083762607586</v>
+        <v>0.3847956013448092</v>
       </c>
       <c r="T86">
-        <v>4.916394505578459</v>
+        <v>5.24415413928369</v>
       </c>
       <c r="U86">
         <v>0.1626309777667576</v>
       </c>
       <c r="V86">
-        <v>0.2347035649027074</v>
+        <v>0.2319423464920873</v>
       </c>
       <c r="W86">
-        <v>0.1244609075212866</v>
+        <v>0.1249099671712333</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9388142596108296</v>
+        <v>0.9277693859683492</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1638928122972697</v>
+        <v>0.1650611220749373</v>
       </c>
       <c r="C87">
-        <v>-143.6465302907535</v>
+        <v>-163.7454349752217</v>
       </c>
       <c r="D87">
-        <v>845.5184697092466</v>
+        <v>838.7085650247784</v>
       </c>
       <c r="E87">
-        <v>138.2650000000001</v>
+        <v>151.5540000000001</v>
       </c>
       <c r="F87">
-        <v>1129.565</v>
+        <v>1142.854</v>
       </c>
       <c r="G87">
         <v>140.4</v>
@@ -8543,37 +8543,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M87">
-        <v>183.7022604011075</v>
+        <v>185.86346346465</v>
       </c>
       <c r="N87">
-        <v>-13.2689270677742</v>
+        <v>-15.43013013131664</v>
       </c>
       <c r="O87">
-        <v>-3.31723176694355</v>
+        <v>-3.857532532829161</v>
       </c>
       <c r="P87">
-        <v>-9.95169530083065</v>
+        <v>-11.57259759848748</v>
       </c>
       <c r="Q87">
-        <v>66.44830469916936</v>
+        <v>64.82740240151253</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3847956013448092</v>
+        <v>0.4090095728694385</v>
       </c>
       <c r="T87">
-        <v>5.24415413928369</v>
+        <v>5.618736577803954</v>
       </c>
       <c r="U87">
         <v>0.1626309777667576</v>
       </c>
       <c r="V87">
-        <v>0.2319423464920873</v>
+        <v>0.2292453424631095</v>
       </c>
       <c r="W87">
-        <v>0.1249099671712333</v>
+        <v>0.1253485835735069</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9277693859683492</v>
+        <v>0.9169813698524382</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1650611220749373</v>
+        <v>0.1662294318526049</v>
       </c>
       <c r="C88">
-        <v>-163.7454349752217</v>
+        <v>-183.7355205631895</v>
       </c>
       <c r="D88">
-        <v>838.7085650247784</v>
+        <v>832.0074794368105</v>
       </c>
       <c r="E88">
-        <v>151.5540000000001</v>
+        <v>164.8430000000001</v>
       </c>
       <c r="F88">
-        <v>1142.854</v>
+        <v>1156.143</v>
       </c>
       <c r="G88">
         <v>140.4</v>
@@ -8625,37 +8625,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M88">
-        <v>185.86346346465</v>
+        <v>188.0246665281924</v>
       </c>
       <c r="N88">
-        <v>-15.43013013131664</v>
+        <v>-17.59133319485909</v>
       </c>
       <c r="O88">
-        <v>-3.857532532829161</v>
+        <v>-4.397833298714772</v>
       </c>
       <c r="P88">
-        <v>-11.57259759848748</v>
+        <v>-13.19349989614432</v>
       </c>
       <c r="Q88">
-        <v>64.82740240151253</v>
+        <v>63.20650010385569</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4090095728694385</v>
+        <v>0.4369487707824722</v>
       </c>
       <c r="T88">
-        <v>5.618736577803954</v>
+        <v>6.050947083788873</v>
       </c>
       <c r="U88">
         <v>0.1626309777667576</v>
       </c>
       <c r="V88">
-        <v>0.2292453424631095</v>
+        <v>0.226610338526752</v>
       </c>
       <c r="W88">
-        <v>0.1253485835735069</v>
+        <v>0.125777116840096</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9169813698524382</v>
+        <v>0.9064413541070079</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1662294318526049</v>
+        <v>0.1673977416302725</v>
       </c>
       <c r="C89">
-        <v>-183.7355205631895</v>
+        <v>-203.6193746975069</v>
       </c>
       <c r="D89">
-        <v>832.0074794368105</v>
+        <v>825.4126253024931</v>
       </c>
       <c r="E89">
-        <v>164.8430000000001</v>
+        <v>178.1320000000001</v>
       </c>
       <c r="F89">
-        <v>1156.143</v>
+        <v>1169.432</v>
       </c>
       <c r="G89">
         <v>140.4</v>
@@ -8707,37 +8707,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M89">
-        <v>188.0246665281924</v>
+        <v>190.1858695917349</v>
       </c>
       <c r="N89">
-        <v>-17.59133319485909</v>
+        <v>-19.75253625840153</v>
       </c>
       <c r="O89">
-        <v>-4.397833298714772</v>
+        <v>-4.938134064600384</v>
       </c>
       <c r="P89">
-        <v>-13.19349989614432</v>
+        <v>-14.81440219380115</v>
       </c>
       <c r="Q89">
-        <v>63.20650010385569</v>
+        <v>61.58559780619886</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4369487707824722</v>
+        <v>0.4695445016810116</v>
       </c>
       <c r="T89">
-        <v>6.050947083788873</v>
+        <v>6.555192674104614</v>
       </c>
       <c r="U89">
         <v>0.1626309777667576</v>
       </c>
       <c r="V89">
-        <v>0.226610338526752</v>
+        <v>0.2240352210434934</v>
       </c>
       <c r="W89">
-        <v>0.125777116840096</v>
+        <v>0.1261959107142626</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9064413541070079</v>
+        <v>0.8961408841739736</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1673977416302725</v>
+        <v>0.16856605140794</v>
       </c>
       <c r="C90">
-        <v>-203.6193746975069</v>
+        <v>-223.399503623077</v>
       </c>
       <c r="D90">
-        <v>825.4126253024931</v>
+        <v>818.9214963769231</v>
       </c>
       <c r="E90">
-        <v>178.1320000000001</v>
+        <v>191.421</v>
       </c>
       <c r="F90">
-        <v>1169.432</v>
+        <v>1182.721</v>
       </c>
       <c r="G90">
         <v>140.4</v>
@@ -8789,37 +8789,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M90">
-        <v>190.1858695917349</v>
+        <v>192.3470726552773</v>
       </c>
       <c r="N90">
-        <v>-19.75253625840153</v>
+        <v>-21.91373932194395</v>
       </c>
       <c r="O90">
-        <v>-4.938134064600384</v>
+        <v>-5.478434830485988</v>
       </c>
       <c r="P90">
-        <v>-14.81440219380115</v>
+        <v>-16.43530449145796</v>
       </c>
       <c r="Q90">
-        <v>61.58559780619886</v>
+        <v>59.96469550854204</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4695445016810116</v>
+        <v>0.508066729106558</v>
       </c>
       <c r="T90">
-        <v>6.555192674104614</v>
+        <v>7.151119280841397</v>
       </c>
       <c r="U90">
         <v>0.1626309777667576</v>
       </c>
       <c r="V90">
-        <v>0.2240352210434934</v>
+        <v>0.2215179713688475</v>
       </c>
       <c r="W90">
-        <v>0.1261959107142626</v>
+        <v>0.1266052934901333</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8961408841739736</v>
+        <v>0.8860718854753898</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.16856605140794</v>
+        <v>0.1697343611856076</v>
       </c>
       <c r="C91">
-        <v>-223.399503623077</v>
+        <v>-243.0783353624903</v>
       </c>
       <c r="D91">
-        <v>818.9214963769231</v>
+        <v>812.5316646375099</v>
       </c>
       <c r="E91">
-        <v>191.421</v>
+        <v>204.7100000000003</v>
       </c>
       <c r="F91">
-        <v>1182.721</v>
+        <v>1196.01</v>
       </c>
       <c r="G91">
         <v>140.4</v>
@@ -8871,37 +8871,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M91">
-        <v>192.3470726552773</v>
+        <v>194.5082757188198</v>
       </c>
       <c r="N91">
-        <v>-21.91373932194395</v>
+        <v>-24.07494238548642</v>
       </c>
       <c r="O91">
-        <v>-5.478434830485988</v>
+        <v>-6.018735596371606</v>
       </c>
       <c r="P91">
-        <v>-16.43530449145796</v>
+        <v>-18.05620678911482</v>
       </c>
       <c r="Q91">
-        <v>59.96469550854204</v>
+        <v>58.34379321088519</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.508066729106558</v>
+        <v>0.5542934020172139</v>
       </c>
       <c r="T91">
-        <v>7.151119280841397</v>
+        <v>7.866231208925538</v>
       </c>
       <c r="U91">
         <v>0.1626309777667576</v>
       </c>
       <c r="V91">
-        <v>0.2215179713688475</v>
+        <v>0.2190566605758602</v>
       </c>
       <c r="W91">
-        <v>0.1266052934901333</v>
+        <v>0.1270055788709847</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8860718854753898</v>
+        <v>0.8762266423034408</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1697343611856076</v>
+        <v>0.1709026709632752</v>
       </c>
       <c r="C92">
-        <v>-243.0783353624903</v>
+        <v>-262.6582227441392</v>
       </c>
       <c r="D92">
-        <v>812.5316646375099</v>
+        <v>806.2407772558611</v>
       </c>
       <c r="E92">
-        <v>204.7100000000003</v>
+        <v>217.9990000000003</v>
       </c>
       <c r="F92">
-        <v>1196.01</v>
+        <v>1209.299</v>
       </c>
       <c r="G92">
         <v>140.4</v>
@@ -8953,37 +8953,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M92">
-        <v>194.5082757188198</v>
+        <v>196.6694787823622</v>
       </c>
       <c r="N92">
-        <v>-24.07494238548642</v>
+        <v>-26.23614544902887</v>
       </c>
       <c r="O92">
-        <v>-6.018735596371606</v>
+        <v>-6.559036362257217</v>
       </c>
       <c r="P92">
-        <v>-18.05620678911482</v>
+        <v>-19.67710908677165</v>
       </c>
       <c r="Q92">
-        <v>58.34379321088519</v>
+        <v>56.72289091322835</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5542934020172139</v>
+        <v>0.6107926689080155</v>
       </c>
       <c r="T92">
-        <v>7.866231208925538</v>
+        <v>8.740256898806154</v>
       </c>
       <c r="U92">
         <v>0.1626309777667576</v>
       </c>
       <c r="V92">
-        <v>0.2190566605758602</v>
+        <v>0.2166494445255761</v>
       </c>
       <c r="W92">
-        <v>0.1270055788709847</v>
+        <v>0.1273970667709383</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8762266423034408</v>
+        <v>0.8665977781023042</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1709026709632752</v>
+        <v>0.1720709807409428</v>
       </c>
       <c r="C93">
-        <v>-262.6582227441392</v>
+        <v>-282.1414462907459</v>
       </c>
       <c r="D93">
-        <v>806.2407772558611</v>
+        <v>800.0465537092543</v>
       </c>
       <c r="E93">
-        <v>217.9990000000003</v>
+        <v>231.2880000000002</v>
       </c>
       <c r="F93">
-        <v>1209.299</v>
+        <v>1222.588</v>
       </c>
       <c r="G93">
         <v>140.4</v>
@@ -9035,37 +9035,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M93">
-        <v>196.6694787823622</v>
+        <v>198.8306818459046</v>
       </c>
       <c r="N93">
-        <v>-26.23614544902887</v>
+        <v>-28.39734851257131</v>
       </c>
       <c r="O93">
-        <v>-6.559036362257217</v>
+        <v>-7.099337128142828</v>
       </c>
       <c r="P93">
-        <v>-19.67710908677165</v>
+        <v>-21.29801138442848</v>
       </c>
       <c r="Q93">
-        <v>56.72289091322835</v>
+        <v>55.10198861557152</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6107926689080155</v>
+        <v>0.6814167525215177</v>
       </c>
       <c r="T93">
-        <v>8.740256898806154</v>
+        <v>9.832789011156926</v>
       </c>
       <c r="U93">
         <v>0.1626309777667576</v>
       </c>
       <c r="V93">
-        <v>0.2166494445255761</v>
+        <v>0.2142945592589937</v>
       </c>
       <c r="W93">
-        <v>0.1273970667709383</v>
+        <v>0.1277800440643711</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8665977781023042</v>
+        <v>0.8571782370359747</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1720709807409428</v>
+        <v>0.1732392905186104</v>
       </c>
       <c r="C94">
-        <v>-282.1414462907459</v>
+        <v>-301.5302169757514</v>
       </c>
       <c r="D94">
-        <v>800.0465537092543</v>
+        <v>793.9467830242488</v>
       </c>
       <c r="E94">
-        <v>231.2880000000002</v>
+        <v>244.5770000000002</v>
       </c>
       <c r="F94">
-        <v>1222.588</v>
+        <v>1235.877</v>
       </c>
       <c r="G94">
         <v>140.4</v>
@@ -9117,37 +9117,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M94">
-        <v>198.8306818459046</v>
+        <v>200.9918849094471</v>
       </c>
       <c r="N94">
-        <v>-28.39734851257131</v>
+        <v>-30.55855157611376</v>
       </c>
       <c r="O94">
-        <v>-7.099337128142828</v>
+        <v>-7.639637894028439</v>
       </c>
       <c r="P94">
-        <v>-21.29801138442848</v>
+        <v>-22.91891368208532</v>
       </c>
       <c r="Q94">
-        <v>55.10198861557152</v>
+        <v>53.48108631791469</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6814167525215177</v>
+        <v>0.7722191457388774</v>
       </c>
       <c r="T94">
-        <v>9.832789011156926</v>
+        <v>11.23747315560792</v>
       </c>
       <c r="U94">
         <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.2142945592589937</v>
+        <v>0.2119903166863163</v>
       </c>
       <c r="W94">
-        <v>0.1277800440643711</v>
+        <v>0.1281547852869774</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8571782370359747</v>
+        <v>0.8479612667452654</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1732392905186104</v>
+        <v>0.1744076002962779</v>
       </c>
       <c r="C95">
-        <v>-301.5302169757514</v>
+        <v>-320.826678854567</v>
       </c>
       <c r="D95">
-        <v>793.9467830242488</v>
+        <v>787.9393211454332</v>
       </c>
       <c r="E95">
-        <v>244.5770000000002</v>
+        <v>257.8660000000002</v>
       </c>
       <c r="F95">
-        <v>1235.877</v>
+        <v>1249.166</v>
       </c>
       <c r="G95">
         <v>140.4</v>
@@ -9199,37 +9199,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M95">
-        <v>200.9918849094471</v>
+        <v>203.1530879729895</v>
       </c>
       <c r="N95">
-        <v>-30.55855157611376</v>
+        <v>-32.7197546396562</v>
       </c>
       <c r="O95">
-        <v>-7.639637894028439</v>
+        <v>-8.17993865991405</v>
       </c>
       <c r="P95">
-        <v>-22.91891368208532</v>
+        <v>-24.53981597974215</v>
       </c>
       <c r="Q95">
-        <v>53.48108631791469</v>
+        <v>51.86018402025785</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7722191457388774</v>
+        <v>0.8932890033620239</v>
       </c>
       <c r="T95">
-        <v>11.23747315560792</v>
+        <v>13.11038534820924</v>
       </c>
       <c r="U95">
         <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.2119903166863163</v>
+        <v>0.2097351005513555</v>
       </c>
       <c r="W95">
-        <v>0.1281547852869774</v>
+        <v>0.1285215532920814</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8479612667452654</v>
+        <v>0.8389404022054221</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1744076002962779</v>
+        <v>0.1755759100739455</v>
       </c>
       <c r="C96">
-        <v>-320.826678854567</v>
+        <v>-340.032911577264</v>
       </c>
       <c r="D96">
-        <v>787.9393211454332</v>
+        <v>782.0220884227361</v>
       </c>
       <c r="E96">
-        <v>257.8660000000002</v>
+        <v>271.1550000000002</v>
       </c>
       <c r="F96">
-        <v>1249.166</v>
+        <v>1262.455</v>
       </c>
       <c r="G96">
         <v>140.4</v>
@@ -9281,37 +9281,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M96">
-        <v>203.1530879729895</v>
+        <v>205.314291036532</v>
       </c>
       <c r="N96">
-        <v>-32.7197546396562</v>
+        <v>-34.88095770319865</v>
       </c>
       <c r="O96">
-        <v>-8.17993865991405</v>
+        <v>-8.720239425799662</v>
       </c>
       <c r="P96">
-        <v>-24.53981597974215</v>
+        <v>-26.16071827739898</v>
       </c>
       <c r="Q96">
-        <v>51.86018402025785</v>
+        <v>50.23928172260102</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8932890033620239</v>
+        <v>1.062786804034429</v>
       </c>
       <c r="T96">
-        <v>13.11038534820924</v>
+        <v>15.73246241785109</v>
       </c>
       <c r="U96">
         <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.2097351005513555</v>
+        <v>0.2075273626508149</v>
       </c>
       <c r="W96">
-        <v>0.1285215532920814</v>
+        <v>0.128880599865499</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8389404022054221</v>
+        <v>0.8301094506032597</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1755759100739455</v>
+        <v>0.1767442198516131</v>
       </c>
       <c r="C97">
-        <v>-340.032911577264</v>
+        <v>-359.1509327888919</v>
       </c>
       <c r="D97">
-        <v>782.0220884227361</v>
+        <v>776.1930672111083</v>
       </c>
       <c r="E97">
-        <v>271.1550000000002</v>
+        <v>284.4440000000002</v>
       </c>
       <c r="F97">
-        <v>1262.455</v>
+        <v>1275.744</v>
       </c>
       <c r="G97">
         <v>140.4</v>
@@ -9363,37 +9363,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M97">
-        <v>205.314291036532</v>
+        <v>207.4754941000744</v>
       </c>
       <c r="N97">
-        <v>-34.88095770319865</v>
+        <v>-37.04216076674106</v>
       </c>
       <c r="O97">
-        <v>-8.720239425799662</v>
+        <v>-9.260540191685266</v>
       </c>
       <c r="P97">
-        <v>-26.16071827739898</v>
+        <v>-27.7816205750558</v>
       </c>
       <c r="Q97">
-        <v>50.23928172260102</v>
+        <v>48.61837942494421</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.062786804034429</v>
+        <v>1.317033505043037</v>
       </c>
       <c r="T97">
-        <v>15.73246241785109</v>
+        <v>19.66557802231388</v>
       </c>
       <c r="U97">
         <v>0.1626309777667576</v>
       </c>
       <c r="V97">
-        <v>0.2075273626508149</v>
+        <v>0.205365619289869</v>
       </c>
       <c r="W97">
-        <v>0.128880599865499</v>
+        <v>0.1292321663019705</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8301094506032597</v>
+        <v>0.8214624771594758</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1767442198516131</v>
+        <v>0.1779125296292806</v>
       </c>
       <c r="C98">
-        <v>-359.1509327888919</v>
+        <v>-378.1827004232379</v>
       </c>
       <c r="D98">
-        <v>776.1930672111083</v>
+        <v>770.4502995767623</v>
       </c>
       <c r="E98">
-        <v>284.4440000000002</v>
+        <v>297.7330000000002</v>
       </c>
       <c r="F98">
-        <v>1275.744</v>
+        <v>1289.033</v>
       </c>
       <c r="G98">
         <v>140.4</v>
@@ -9445,37 +9445,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M98">
-        <v>207.4754941000744</v>
+        <v>209.6366971636168</v>
       </c>
       <c r="N98">
-        <v>-37.04216076674106</v>
+        <v>-39.20336383028351</v>
       </c>
       <c r="O98">
-        <v>-9.260540191685266</v>
+        <v>-9.800840957570877</v>
       </c>
       <c r="P98">
-        <v>-27.7816205750558</v>
+        <v>-29.40252287271263</v>
       </c>
       <c r="Q98">
-        <v>48.61837942494421</v>
+        <v>46.99747712728738</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.317033505043034</v>
+        <v>1.740778006724045</v>
       </c>
       <c r="T98">
-        <v>19.66557802231382</v>
+        <v>26.22077069641844</v>
       </c>
       <c r="U98">
         <v>0.1626309777667576</v>
       </c>
       <c r="V98">
-        <v>0.205365619289869</v>
+        <v>0.2032484479569837</v>
       </c>
       <c r="W98">
-        <v>0.1292321663019705</v>
+        <v>0.1295764839459374</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8214624771594758</v>
+        <v>0.8129937918279349</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1779125296292806</v>
+        <v>0.1790808394069482</v>
       </c>
       <c r="C99">
-        <v>-378.1827004232379</v>
+        <v>-397.1301148955151</v>
       </c>
       <c r="D99">
-        <v>770.4502995767623</v>
+        <v>764.791885104485</v>
       </c>
       <c r="E99">
-        <v>297.7330000000002</v>
+        <v>311.0220000000002</v>
       </c>
       <c r="F99">
-        <v>1289.033</v>
+        <v>1302.322</v>
       </c>
       <c r="G99">
         <v>140.4</v>
@@ -9527,37 +9527,37 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M99">
-        <v>209.6366971636168</v>
+        <v>211.7979002271593</v>
       </c>
       <c r="N99">
-        <v>-39.20336383028351</v>
+        <v>-41.36456689382595</v>
       </c>
       <c r="O99">
-        <v>-9.800840957570877</v>
+        <v>-10.34114172345649</v>
       </c>
       <c r="P99">
-        <v>-29.40252287271263</v>
+        <v>-31.02342517036946</v>
       </c>
       <c r="Q99">
-        <v>46.99747712728738</v>
+        <v>45.37657482963054</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.740778006724045</v>
+        <v>2.588267010086066</v>
       </c>
       <c r="T99">
-        <v>26.22077069641844</v>
+        <v>39.33115604462764</v>
       </c>
       <c r="U99">
         <v>0.1626309777667576</v>
       </c>
       <c r="V99">
-        <v>0.2032484479569837</v>
+        <v>0.2011744842023206</v>
       </c>
       <c r="W99">
-        <v>0.1295764839459374</v>
+        <v>0.1299137746992111</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8129937918279349</v>
+        <v>0.8046979368092825</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1790808394069482</v>
+        <v>0.2368217513873206</v>
       </c>
       <c r="C100">
-        <v>-397.1301148955151</v>
+        <v>-614.0911447212956</v>
       </c>
       <c r="D100">
-        <v>764.791885104485</v>
+        <v>561.1198552787046</v>
       </c>
       <c r="E100">
-        <v>311.0220000000002</v>
+        <v>324.3110000000001</v>
       </c>
       <c r="F100">
-        <v>1302.322</v>
+        <v>1315.611</v>
       </c>
       <c r="G100">
         <v>140.4</v>
@@ -9609,129 +9609,47 @@
         <v>170.4333333333333</v>
       </c>
       <c r="M100">
-        <v>211.7979002271593</v>
+        <v>285.0020972907017</v>
       </c>
       <c r="N100">
-        <v>-41.36456689382595</v>
+        <v>-114.5687639573684</v>
       </c>
       <c r="O100">
-        <v>-10.34114172345649</v>
+        <v>-28.6421909893421</v>
       </c>
       <c r="P100">
-        <v>-31.02342517036946</v>
+        <v>-85.92657296802629</v>
       </c>
       <c r="Q100">
-        <v>45.37657482963054</v>
+        <v>-9.526572968026287</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.588267010086066</v>
+        <v>5.441994240442613</v>
       </c>
       <c r="T100">
-        <v>39.33115604462764</v>
+        <v>83.47740870422729</v>
       </c>
       <c r="U100">
-        <v>0.1626309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.2011744842023206</v>
+        <v>0.1495018238054329</v>
       </c>
       <c r="W100">
-        <v>0.1299137746992111</v>
+        <v>0.1842442514978731</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8046979368092825</v>
+        <v>0.5980072952217316</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2368217513873206</v>
-      </c>
-      <c r="C101">
-        <v>-614.0911447212956</v>
-      </c>
-      <c r="D101">
-        <v>561.1198552787046</v>
-      </c>
-      <c r="E101">
-        <v>324.3110000000001</v>
-      </c>
-      <c r="F101">
-        <v>1315.611</v>
-      </c>
-      <c r="G101">
-        <v>140.4</v>
-      </c>
-      <c r="H101">
-        <v>337.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>246.8333333333333</v>
-      </c>
-      <c r="K101">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="L101">
-        <v>170.4333333333333</v>
-      </c>
-      <c r="M101">
-        <v>285.0020972907017</v>
-      </c>
-      <c r="N101">
-        <v>-114.5687639573684</v>
-      </c>
-      <c r="O101">
-        <v>-28.6421909893421</v>
-      </c>
-      <c r="P101">
-        <v>-85.92657296802629</v>
-      </c>
-      <c r="Q101">
-        <v>-9.526572968026287</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.441994240442613</v>
-      </c>
-      <c r="T101">
-        <v>83.47740870422729</v>
-      </c>
-      <c r="U101">
-        <v>0.2166309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.1495018238054329</v>
-      </c>
-      <c r="W101">
-        <v>0.1842442514978731</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5980072952217316</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
